--- a/research/traditional_assets/database/data/ukraine/ukraine_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/ukraine/ukraine_farming_agriculture.xlsx
@@ -644,10 +644,10 @@
         <v>0.181611546766678</v>
       </c>
       <c r="X2">
-        <v>0.2824352152073603</v>
+        <v>0.2824932831349551</v>
       </c>
       <c r="Y2">
-        <v>-0.1008236684406823</v>
+        <v>-0.1008817363682771</v>
       </c>
       <c r="Z2">
         <v>1.532853429314138</v>
@@ -656,10 +656,10 @@
         <v>0.2011524967733726</v>
       </c>
       <c r="AB2">
-        <v>0.2347742355137338</v>
+        <v>0.2348007559540485</v>
       </c>
       <c r="AC2">
-        <v>-0.03362173874036115</v>
+        <v>-0.0336482591806759</v>
       </c>
       <c r="AD2">
         <v>1111.4</v>
@@ -775,10 +775,10 @@
         <v>0.181611546766678</v>
       </c>
       <c r="X3">
-        <v>0.2824352152073603</v>
+        <v>0.2824932831349551</v>
       </c>
       <c r="Y3">
-        <v>-0.1008236684406823</v>
+        <v>-0.1008817363682771</v>
       </c>
       <c r="Z3">
         <v>1.532853429314138</v>
@@ -787,10 +787,10 @@
         <v>0.2011524967733726</v>
       </c>
       <c r="AB3">
-        <v>0.2347742355137338</v>
+        <v>0.2348007559540485</v>
       </c>
       <c r="AC3">
-        <v>-0.03362173874036115</v>
+        <v>-0.0336482591806759</v>
       </c>
       <c r="AD3">
         <v>1111.4</v>
@@ -1145,13 +1145,13 @@
         <v>934.3</v>
       </c>
       <c r="L2">
-        <v>2441.51698635422</v>
+        <v>2441.48365817095</v>
       </c>
       <c r="M2">
         <v>1178</v>
       </c>
       <c r="N2">
-        <v>1573.81698635422</v>
+        <v>1573.78365817095</v>
       </c>
       <c r="O2">
         <v>1111.4</v>
@@ -1160,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.234774235513734</v>
+        <v>0.234800755954049</v>
       </c>
       <c r="R2">
-        <v>0.165588974695195</v>
+        <v>0.165618369717838</v>
       </c>
       <c r="S2">
         <v>0.194707964749153</v>
       </c>
       <c r="T2">
-        <v>0.139849964749153</v>
+        <v>0.138701964749153</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.28243521520736</v>
+        <v>0.282493283134955</v>
       </c>
       <c r="X2">
-        <v>0.165588974695195</v>
+        <v>0.165618369717838</v>
       </c>
       <c r="Y2">
         <v>1.16296219377227</v>
@@ -1224,7 +1224,7 @@
         <v>934.3</v>
       </c>
       <c r="AK2">
-        <v>0.2034762750453591</v>
+        <v>0.2035262060989271</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1655889746951947</v>
+        <v>0.1656183697178382</v>
       </c>
       <c r="C2">
-        <v>2441.516986354221</v>
+        <v>2441.483658170947</v>
       </c>
       <c r="D2">
-        <v>1573.816986354221</v>
+        <v>1573.783658170947</v>
       </c>
       <c r="E2">
         <v>-1111.4</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1655889746951947</v>
+        <v>0.1656183697178382</v>
       </c>
       <c r="T2">
         <v>0.5887122450442503</v>
       </c>
       <c r="U2">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V2">
         <v>0.18</v>
       </c>
       <c r="W2">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1663138541882349</v>
+        <v>0.1663317162998375</v>
       </c>
       <c r="C3">
-        <v>2415.538838739492</v>
+        <v>2415.593395360408</v>
       </c>
       <c r="D3">
-        <v>1568.295838739492</v>
+        <v>1568.350395360407</v>
       </c>
       <c r="E3">
         <v>-1090.943</v>
@@ -1527,37 +1527,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M3">
-        <v>3.488915523016365</v>
+        <v>3.460275723016365</v>
       </c>
       <c r="N3">
-        <v>592.5886354973918</v>
+        <v>592.6172752973918</v>
       </c>
       <c r="O3">
-        <v>106.6659543895305</v>
+        <v>106.6711095535305</v>
       </c>
       <c r="P3">
-        <v>485.9226811078613</v>
+        <v>485.9461657438612</v>
       </c>
       <c r="Q3">
-        <v>573.7226811078614</v>
+        <v>573.7461657438613</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1665811662027711</v>
+        <v>0.1666108046993394</v>
       </c>
       <c r="T3">
         <v>0.5935884474779501</v>
       </c>
       <c r="U3">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V3">
         <v>0.18</v>
       </c>
       <c r="W3">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>170.848949218772</v>
+        <v>172.2630214278994</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1670387336812751</v>
+        <v>0.167045062881837</v>
       </c>
       <c r="C4">
-        <v>2389.599293461182</v>
+        <v>2389.740518604152</v>
       </c>
       <c r="D4">
-        <v>1562.813293461182</v>
+        <v>1562.954518604152</v>
       </c>
       <c r="E4">
         <v>-1070.486</v>
@@ -1609,37 +1609,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M4">
-        <v>6.97783104603273</v>
+        <v>6.92055144603273</v>
       </c>
       <c r="N4">
-        <v>589.0997199743754</v>
+        <v>589.1569995743754</v>
       </c>
       <c r="O4">
-        <v>106.0379495953876</v>
+        <v>106.0482599233876</v>
       </c>
       <c r="P4">
-        <v>483.0617703789878</v>
+        <v>483.1087396509878</v>
       </c>
       <c r="Q4">
-        <v>570.8617703789879</v>
+        <v>570.9087396509879</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1675936065166245</v>
+        <v>0.1676234934559734</v>
       </c>
       <c r="T4">
         <v>0.5985641642470316</v>
       </c>
       <c r="U4">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V4">
         <v>0.18</v>
       </c>
       <c r="W4">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>85.42447460938598</v>
+        <v>86.13151071394968</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1677636131743153</v>
+        <v>0.1677584094638364</v>
       </c>
       <c r="C5">
-        <v>2363.697947084361</v>
+        <v>2363.924643347421</v>
       </c>
       <c r="D5">
-        <v>1557.368947084361</v>
+        <v>1557.595643347421</v>
       </c>
       <c r="E5">
         <v>-1050.029</v>
@@ -1691,37 +1691,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M5">
-        <v>10.46674656904909</v>
+        <v>10.38082716904909</v>
       </c>
       <c r="N5">
-        <v>585.6108044513591</v>
+        <v>585.696723851359</v>
       </c>
       <c r="O5">
-        <v>105.4099448012446</v>
+        <v>105.4254102932446</v>
       </c>
       <c r="P5">
-        <v>480.2008596501145</v>
+        <v>480.2713135581144</v>
       </c>
       <c r="Q5">
-        <v>568.0008596501145</v>
+        <v>568.0713135581145</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1686269218884955</v>
+        <v>0.1686570623931565</v>
       </c>
       <c r="T5">
         <v>0.6036424731144447</v>
       </c>
       <c r="U5">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V5">
         <v>0.18</v>
       </c>
       <c r="W5">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.94964973959065</v>
+        <v>57.42100714263313</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1684884926673554</v>
+        <v>0.1684717560458358</v>
       </c>
       <c r="C6">
-        <v>2337.834401776342</v>
+        <v>2338.145390291494</v>
       </c>
       <c r="D6">
-        <v>1551.962401776341</v>
+        <v>1552.273390291494</v>
       </c>
       <c r="E6">
         <v>-1029.572</v>
@@ -1773,37 +1773,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M6">
-        <v>13.95566209206546</v>
+        <v>13.84110289206546</v>
       </c>
       <c r="N6">
-        <v>582.1218889283426</v>
+        <v>582.2364481283427</v>
       </c>
       <c r="O6">
-        <v>104.7819400071017</v>
+        <v>104.8025606631017</v>
       </c>
       <c r="P6">
-        <v>477.339948921241</v>
+        <v>477.433887465241</v>
       </c>
       <c r="Q6">
-        <v>565.1399489212411</v>
+        <v>565.2338874652411</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1696817646639472</v>
+        <v>0.169712164016531</v>
       </c>
       <c r="T6">
         <v>0.6088265800832623</v>
       </c>
       <c r="U6">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V6">
         <v>0.18</v>
       </c>
       <c r="W6">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.71223730469298</v>
+        <v>43.06575535697484</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1692133721603956</v>
+        <v>0.1691851026278353</v>
       </c>
       <c r="C7">
-        <v>2312.00826520977</v>
+        <v>2312.402385304204</v>
       </c>
       <c r="D7">
-        <v>1546.59326520977</v>
+        <v>1546.987385304204</v>
       </c>
       <c r="E7">
         <v>-1009.115</v>
@@ -1855,37 +1855,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M7">
-        <v>17.44457761508183</v>
+        <v>17.30137861508183</v>
       </c>
       <c r="N7">
-        <v>578.6329734053263</v>
+        <v>578.7761724053263</v>
       </c>
       <c r="O7">
-        <v>104.1539352129587</v>
+        <v>104.1797110329587</v>
       </c>
       <c r="P7">
-        <v>474.4790381923676</v>
+        <v>474.5964613723676</v>
       </c>
       <c r="Q7">
-        <v>562.2790381923676</v>
+        <v>562.3964613723676</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1707588146557242</v>
+        <v>0.1707894783056607</v>
       </c>
       <c r="T7">
         <v>0.6141198261461601</v>
       </c>
       <c r="U7">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V7">
         <v>0.18</v>
       </c>
       <c r="W7">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.16978984375439</v>
+        <v>34.45260428557987</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1699382516534358</v>
+        <v>0.1698984492098347</v>
       </c>
       <c r="C8">
-        <v>2286.219150467723</v>
+        <v>2286.695259332263</v>
       </c>
       <c r="D8">
-        <v>1541.261150467724</v>
+        <v>1541.737259332263</v>
       </c>
       <c r="E8">
         <v>-988.6580000000001</v>
@@ -1937,37 +1937,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M8">
-        <v>20.93349313809819</v>
+        <v>20.76165433809819</v>
       </c>
       <c r="N8">
-        <v>575.1440578823099</v>
+        <v>575.3158966823099</v>
       </c>
       <c r="O8">
-        <v>103.5259304188158</v>
+        <v>103.5568614028158</v>
       </c>
       <c r="P8">
-        <v>471.6181274634941</v>
+        <v>471.7590352794941</v>
       </c>
       <c r="Q8">
-        <v>559.4181274634941</v>
+        <v>559.5590352794942</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.171858780604773</v>
+        <v>0.1718897141754101</v>
       </c>
       <c r="T8">
         <v>0.6195256944657154</v>
       </c>
       <c r="U8">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V8">
         <v>0.18</v>
       </c>
       <c r="W8">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.47482486979532</v>
+        <v>28.71050357131656</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.170663131146476</v>
+        <v>0.1706117957918341</v>
       </c>
       <c r="C9">
-        <v>2260.466675950768</v>
+        <v>2261.023648315374</v>
       </c>
       <c r="D9">
-        <v>1535.965675950768</v>
+        <v>1536.522648315374</v>
       </c>
       <c r="E9">
         <v>-968.201</v>
@@ -2019,37 +2019,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M9">
-        <v>24.42240866111456</v>
+        <v>24.22193006111456</v>
       </c>
       <c r="N9">
-        <v>571.6551423592936</v>
+        <v>571.8556209592936</v>
       </c>
       <c r="O9">
-        <v>102.8979256246728</v>
+        <v>102.9340117726728</v>
       </c>
       <c r="P9">
-        <v>468.7572167346207</v>
+        <v>468.9216091866207</v>
       </c>
       <c r="Q9">
-        <v>556.5572167346209</v>
+        <v>556.7216091866208</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1729824017355218</v>
+        <v>0.1730136110316058</v>
       </c>
       <c r="T9">
         <v>0.6250478180179493</v>
       </c>
       <c r="U9">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V9">
         <v>0.18</v>
       </c>
       <c r="W9">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.40699274553885</v>
+        <v>24.60900306112848</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1713880106395161</v>
+        <v>0.1713251423738335</v>
       </c>
       <c r="C10">
-        <v>2234.750465285916</v>
+        <v>2235.387193102074</v>
       </c>
       <c r="D10">
-        <v>1530.706465285916</v>
+        <v>1531.343193102074</v>
       </c>
       <c r="E10">
         <v>-947.7440000000001</v>
@@ -2101,37 +2101,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M10">
-        <v>27.91132418413092</v>
+        <v>27.68220578413092</v>
       </c>
       <c r="N10">
-        <v>568.1662268362772</v>
+        <v>568.3953452362772</v>
       </c>
       <c r="O10">
-        <v>102.2699208305299</v>
+        <v>102.3111621425299</v>
       </c>
       <c r="P10">
-        <v>465.8963060057474</v>
+        <v>466.0841830937473</v>
       </c>
       <c r="Q10">
-        <v>553.6963060057474</v>
+        <v>553.8841830937474</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1741304494125912</v>
+        <v>0.1741619404281536</v>
       </c>
       <c r="T10">
         <v>0.6306899877343621</v>
       </c>
       <c r="U10">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V10">
         <v>0.18</v>
       </c>
       <c r="W10">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.3561186523465</v>
+        <v>21.53287767848742</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1721128901325563</v>
+        <v>0.172038488955833</v>
       </c>
       <c r="C11">
-        <v>2209.07014723746</v>
+        <v>2209.785539367277</v>
       </c>
       <c r="D11">
-        <v>1525.48314723746</v>
+        <v>1526.198539367277</v>
       </c>
       <c r="E11">
         <v>-927.287</v>
@@ -2183,37 +2183,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M11">
-        <v>31.40023970714728</v>
+        <v>31.14248150714728</v>
       </c>
       <c r="N11">
-        <v>564.6773113132608</v>
+        <v>564.9350695132608</v>
       </c>
       <c r="O11">
-        <v>101.6419160363869</v>
+        <v>101.6883125123869</v>
       </c>
       <c r="P11">
-        <v>463.0353952768739</v>
+        <v>463.2467570008739</v>
       </c>
       <c r="Q11">
-        <v>550.8353952768739</v>
+        <v>551.046757000874</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1753037289067391</v>
+        <v>0.1753355078334167</v>
       </c>
       <c r="T11">
         <v>0.6364561611808061</v>
       </c>
       <c r="U11">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V11">
         <v>0.18</v>
       </c>
       <c r="W11">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.98321657986355</v>
+        <v>19.14033571421104</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1728377696255965</v>
+        <v>0.1727518355378324</v>
       </c>
       <c r="C12">
-        <v>2183.425355619615</v>
+        <v>2184.218337531471</v>
       </c>
       <c r="D12">
-        <v>1520.295355619615</v>
+        <v>1521.088337531471</v>
       </c>
       <c r="E12">
         <v>-906.83</v>
@@ -2265,37 +2265,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M12">
-        <v>34.88915523016365</v>
+        <v>34.60275723016365</v>
       </c>
       <c r="N12">
-        <v>561.1883957902445</v>
+        <v>561.4747937902445</v>
       </c>
       <c r="O12">
-        <v>101.013911242244</v>
+        <v>101.065462882244</v>
       </c>
       <c r="P12">
-        <v>460.1744845480005</v>
+        <v>460.4093309080005</v>
       </c>
       <c r="Q12">
-        <v>547.9744845480005</v>
+        <v>548.2093309080005</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1765030812785347</v>
+        <v>0.1765351545143523</v>
       </c>
       <c r="T12">
         <v>0.6423504718149488</v>
       </c>
       <c r="U12">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V12">
         <v>0.18</v>
       </c>
       <c r="W12">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.08489492187719</v>
+        <v>17.22630214278994</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1735626491186367</v>
+        <v>0.1734651821198318</v>
       </c>
       <c r="C13">
-        <v>2157.815729210944</v>
+        <v>2158.68524268154</v>
       </c>
       <c r="D13">
-        <v>1515.142729210943</v>
+        <v>1516.01224268154</v>
       </c>
       <c r="E13">
         <v>-886.373</v>
@@ -2347,37 +2347,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M13">
-        <v>38.37807075318001</v>
+        <v>38.06303295318002</v>
       </c>
       <c r="N13">
-        <v>557.6994802672281</v>
+        <v>558.0145180672281</v>
       </c>
       <c r="O13">
-        <v>100.3859064481011</v>
+        <v>100.4426132521011</v>
       </c>
       <c r="P13">
-        <v>457.313573819127</v>
+        <v>457.571904815127</v>
       </c>
       <c r="Q13">
-        <v>545.1135738191271</v>
+        <v>545.3719048151271</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1777293853890223</v>
+        <v>0.1777617595476685</v>
       </c>
       <c r="T13">
         <v>0.6483772388678362</v>
       </c>
       <c r="U13">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V13">
         <v>0.18</v>
       </c>
       <c r="W13">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.531722656252</v>
+        <v>15.66027467526358</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1742875286116768</v>
+        <v>0.1741785287018312</v>
       </c>
       <c r="C14">
-        <v>2132.240911670513</v>
+        <v>2133.185914493155</v>
       </c>
       <c r="D14">
-        <v>1510.024911670512</v>
+        <v>1510.969914493154</v>
       </c>
       <c r="E14">
         <v>-865.9160000000001</v>
@@ -2429,37 +2429,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M14">
-        <v>41.86698627619638</v>
+        <v>41.52330867619638</v>
       </c>
       <c r="N14">
-        <v>554.2105647442118</v>
+        <v>554.5542423442117</v>
       </c>
       <c r="O14">
-        <v>99.75790165395811</v>
+        <v>99.8197636219581</v>
       </c>
       <c r="P14">
-        <v>454.4526630902536</v>
+        <v>454.7344787222536</v>
       </c>
       <c r="Q14">
-        <v>542.2526630902537</v>
+        <v>542.5344787222537</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1789835600474756</v>
+        <v>0.1790162419681055</v>
       </c>
       <c r="T14">
         <v>0.6545409778991983</v>
       </c>
       <c r="U14">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V14">
         <v>0.18</v>
       </c>
       <c r="W14">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.23741243489766</v>
+        <v>14.35525178565828</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.175012408104717</v>
+        <v>0.1748918752838306</v>
       </c>
       <c r="C15">
-        <v>2106.700551455746</v>
+        <v>2107.720017154715</v>
       </c>
       <c r="D15">
-        <v>1504.941551455746</v>
+        <v>1505.961017154715</v>
       </c>
       <c r="E15">
         <v>-845.4590000000001</v>
@@ -2511,37 +2511,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M15">
-        <v>45.35590179921275</v>
+        <v>44.98358439921275</v>
       </c>
       <c r="N15">
-        <v>550.7216492211953</v>
+        <v>551.0939666211954</v>
       </c>
       <c r="O15">
-        <v>99.12989685981515</v>
+        <v>99.19691399181517</v>
       </c>
       <c r="P15">
-        <v>451.5917523613801</v>
+        <v>451.8970526293802</v>
       </c>
       <c r="Q15">
-        <v>539.3917523613802</v>
+        <v>539.6970526293803</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1802665663072726</v>
+        <v>0.1802995630648744</v>
       </c>
       <c r="T15">
         <v>0.6608464120807068</v>
       </c>
       <c r="U15">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V15">
         <v>0.18</v>
       </c>
       <c r="W15">
-        <v>0.1398499647491528</v>
+        <v>0.1387019647491528</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.14222686298246</v>
+        <v>13.25100164829995</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1758635675977572</v>
+        <v>0.17577742186583</v>
       </c>
       <c r="C16">
-        <v>2080.318144034026</v>
+        <v>2081.090997459398</v>
       </c>
       <c r="D16">
-        <v>1499.016144034026</v>
+        <v>1499.788997459398</v>
       </c>
       <c r="E16">
         <v>-825.0020000000001</v>
@@ -2593,37 +2593,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M16">
-        <v>49.15985512222912</v>
+        <v>48.87345712222911</v>
       </c>
       <c r="N16">
-        <v>546.917695898179</v>
+        <v>547.2040938981791</v>
       </c>
       <c r="O16">
-        <v>98.44518526167221</v>
+        <v>98.49673690167222</v>
       </c>
       <c r="P16">
-        <v>448.4725106365067</v>
+        <v>448.7073569965069</v>
       </c>
       <c r="Q16">
-        <v>536.2725106365068</v>
+        <v>536.5073569965069</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1815794099219486</v>
+        <v>0.1816127288383124</v>
       </c>
       <c r="T16">
         <v>0.6672984842664363</v>
       </c>
       <c r="U16">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V16">
         <v>0.18</v>
       </c>
       <c r="W16">
-        <v>0.1407519647491528</v>
+        <v>0.1399319647491528</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.12529104364414</v>
+        <v>12.19634513534943</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1765974670907974</v>
+        <v>0.1765030684478295</v>
       </c>
       <c r="C17">
-        <v>2054.789384497053</v>
+        <v>2055.614024178899</v>
       </c>
       <c r="D17">
-        <v>1493.944384497053</v>
+        <v>1494.7690241789</v>
       </c>
       <c r="E17">
         <v>-804.5450000000001</v>
@@ -2675,37 +2675,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M17">
-        <v>52.67127334524548</v>
+        <v>52.36441834524548</v>
       </c>
       <c r="N17">
-        <v>543.4062776751626</v>
+        <v>543.7131326751627</v>
       </c>
       <c r="O17">
-        <v>97.81312998152927</v>
+        <v>97.86836388152928</v>
       </c>
       <c r="P17">
-        <v>445.5931476936333</v>
+        <v>445.8447687936334</v>
       </c>
       <c r="Q17">
-        <v>533.3931476936334</v>
+        <v>533.6447687936335</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.182923143974617</v>
+        <v>0.1829567926299489</v>
       </c>
       <c r="T17">
         <v>0.6739023699153596</v>
       </c>
       <c r="U17">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.1407519647491528</v>
+        <v>0.1399319647491528</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.3169383074012</v>
+        <v>11.38325545965947</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1773313665838376</v>
+        <v>0.1772287150298289</v>
       </c>
       <c r="C18">
-        <v>2029.294828738648</v>
+        <v>2030.170543696792</v>
       </c>
       <c r="D18">
-        <v>1488.906828738648</v>
+        <v>1489.782543696792</v>
       </c>
       <c r="E18">
         <v>-784.0880000000001</v>
@@ -2757,37 +2757,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M18">
-        <v>56.18269156826184</v>
+        <v>55.85537956826185</v>
       </c>
       <c r="N18">
-        <v>539.8948594521463</v>
+        <v>540.2221714521463</v>
       </c>
       <c r="O18">
-        <v>97.18107470138634</v>
+        <v>97.23999086138633</v>
       </c>
       <c r="P18">
-        <v>442.7137847507599</v>
+        <v>442.98218059076</v>
       </c>
       <c r="Q18">
-        <v>530.51378475076</v>
+        <v>530.78218059076</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1842988716952061</v>
+        <v>0.1843328579404339</v>
       </c>
       <c r="T18">
         <v>0.6806634909368762</v>
       </c>
       <c r="U18">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.1407519647491528</v>
+        <v>0.1399319647491528</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.60962966318862</v>
+        <v>10.67180199343075</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1780652660768777</v>
+        <v>0.1779543616118283</v>
       </c>
       <c r="C19">
-        <v>2003.834131917883</v>
+        <v>2004.760221936251</v>
       </c>
       <c r="D19">
-        <v>1483.903131917883</v>
+        <v>1484.829221936251</v>
       </c>
       <c r="E19">
         <v>-763.6310000000001</v>
@@ -2839,37 +2839,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M19">
-        <v>59.69410979127821</v>
+        <v>59.34634079127821</v>
       </c>
       <c r="N19">
-        <v>536.3834412291299</v>
+        <v>536.7312102291299</v>
       </c>
       <c r="O19">
-        <v>96.54901942124337</v>
+        <v>96.61161784124339</v>
       </c>
       <c r="P19">
-        <v>439.8344218078865</v>
+        <v>440.1195923878865</v>
       </c>
       <c r="Q19">
-        <v>527.6344218078866</v>
+        <v>527.9195923878866</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1857077494813515</v>
+        <v>0.1857420814511715</v>
       </c>
       <c r="T19">
         <v>0.6875875305372244</v>
       </c>
       <c r="U19">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V19">
         <v>0.18</v>
       </c>
       <c r="W19">
-        <v>0.1407519647491528</v>
+        <v>0.1399319647491528</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.985533800648113</v>
+        <v>10.04404893499365</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1791238855699179</v>
+        <v>0.1789309281938277</v>
       </c>
       <c r="C20">
-        <v>1976.218465646381</v>
+        <v>1977.6888604298</v>
       </c>
       <c r="D20">
-        <v>1476.744465646382</v>
+        <v>1478.2148604298</v>
       </c>
       <c r="E20">
         <v>-743.1740000000001</v>
@@ -2921,37 +2921,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M20">
-        <v>64.01562521429456</v>
+        <v>63.46328621429458</v>
       </c>
       <c r="N20">
-        <v>532.0619258061135</v>
+        <v>532.6142648061135</v>
       </c>
       <c r="O20">
-        <v>95.77114664510043</v>
+        <v>95.87056766510042</v>
       </c>
       <c r="P20">
-        <v>436.2907791610131</v>
+        <v>436.7436971410131</v>
       </c>
       <c r="Q20">
-        <v>524.0907791610132</v>
+        <v>524.5436971410131</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1871509901403298</v>
+        <v>0.187185676267049</v>
       </c>
       <c r="T20">
         <v>0.6946804491522154</v>
       </c>
       <c r="U20">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V20">
         <v>0.18</v>
       </c>
       <c r="W20">
-        <v>0.1425559647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.311438403124511</v>
+        <v>9.392478495482425</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1798758250629581</v>
+        <v>0.1796705147758272</v>
       </c>
       <c r="C21">
-        <v>1950.718461851221</v>
+        <v>1952.261665028265</v>
       </c>
       <c r="D21">
-        <v>1471.701461851221</v>
+        <v>1473.244665028265</v>
       </c>
       <c r="E21">
         <v>-722.7170000000001</v>
@@ -3003,37 +3003,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M21">
-        <v>67.57204883731093</v>
+        <v>66.98902433731094</v>
       </c>
       <c r="N21">
-        <v>528.5055021830972</v>
+        <v>529.0885266830971</v>
       </c>
       <c r="O21">
-        <v>95.13099039295749</v>
+        <v>95.23593480295749</v>
       </c>
       <c r="P21">
-        <v>433.3745117901397</v>
+        <v>433.8525918801396</v>
       </c>
       <c r="Q21">
-        <v>521.1745117901398</v>
+        <v>521.6525918801397</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1886298663711347</v>
+        <v>0.188664915399368</v>
       </c>
       <c r="T21">
         <v>0.7019485015601691</v>
       </c>
       <c r="U21">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V21">
         <v>0.18</v>
       </c>
       <c r="W21">
-        <v>0.1425559647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.821362697696905</v>
+        <v>8.898137522035983</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1806277645559983</v>
+        <v>0.1804101013578266</v>
       </c>
       <c r="C22">
-        <v>1925.252784014138</v>
+        <v>1926.867780159672</v>
       </c>
       <c r="D22">
-        <v>1466.692784014138</v>
+        <v>1468.307780159672</v>
       </c>
       <c r="E22">
         <v>-702.26</v>
@@ -3085,37 +3085,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M22">
-        <v>71.1284724603273</v>
+        <v>70.51476246032732</v>
       </c>
       <c r="N22">
-        <v>524.9490785600808</v>
+        <v>525.5627885600808</v>
       </c>
       <c r="O22">
-        <v>94.49083414081454</v>
+        <v>94.60130194081454</v>
       </c>
       <c r="P22">
-        <v>430.4582444192663</v>
+        <v>430.9614866192662</v>
       </c>
       <c r="Q22">
-        <v>518.2582444192664</v>
+        <v>518.7614866192663</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1901457145077096</v>
+        <v>0.190181135509995</v>
       </c>
       <c r="T22">
         <v>0.7093982552783217</v>
       </c>
       <c r="U22">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.1425559647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.380294562812058</v>
+        <v>8.453230645934182</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1813797040490385</v>
+        <v>0.181149687939826</v>
       </c>
       <c r="C23">
-        <v>1899.821082856704</v>
+        <v>1901.506872068805</v>
       </c>
       <c r="D23">
-        <v>1461.718082856704</v>
+        <v>1463.403872068805</v>
       </c>
       <c r="E23">
         <v>-681.8030000000001</v>
@@ -3167,37 +3167,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M23">
-        <v>74.68489608334366</v>
+        <v>74.04050058334367</v>
       </c>
       <c r="N23">
-        <v>521.3926549370644</v>
+        <v>522.0370504370644</v>
       </c>
       <c r="O23">
-        <v>93.8506778886716</v>
+        <v>93.96666907867159</v>
       </c>
       <c r="P23">
-        <v>427.5419770483928</v>
+        <v>428.0703813583928</v>
       </c>
       <c r="Q23">
-        <v>515.3419770483929</v>
+        <v>515.8703813583929</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1916999385464764</v>
+        <v>0.1917357409398783</v>
       </c>
       <c r="T23">
         <v>0.7170366103564274</v>
       </c>
       <c r="U23">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V23">
         <v>0.18</v>
       </c>
       <c r="W23">
-        <v>0.1425559647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.981232916963865</v>
+        <v>8.05069585327065</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1821316435420786</v>
+        <v>0.1818892745218254</v>
       </c>
       <c r="C24">
-        <v>1874.423013823178</v>
+        <v>1876.178611444363</v>
       </c>
       <c r="D24">
-        <v>1456.777013823178</v>
+        <v>1458.532611444363</v>
       </c>
       <c r="E24">
         <v>-661.346</v>
@@ -3249,37 +3249,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M24">
-        <v>78.24131970636003</v>
+        <v>77.56623870636004</v>
       </c>
       <c r="N24">
-        <v>517.8362313140481</v>
+        <v>518.511312314048</v>
       </c>
       <c r="O24">
-        <v>93.21052163652865</v>
+        <v>93.33203621652865</v>
       </c>
       <c r="P24">
-        <v>424.6257096775194</v>
+        <v>425.1792760975194</v>
       </c>
       <c r="Q24">
-        <v>512.4257096775195</v>
+        <v>512.9792760975195</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1932940144836731</v>
+        <v>0.193330208047451</v>
       </c>
       <c r="T24">
         <v>0.7248708206929462</v>
       </c>
       <c r="U24">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V24">
         <v>0.18</v>
       </c>
       <c r="W24">
-        <v>0.1425559647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.618449602556416</v>
+        <v>7.684755132667439</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1831664830351188</v>
+        <v>0.1827797411038248</v>
       </c>
       <c r="C25">
-        <v>1847.22034846551</v>
+        <v>1849.899442186641</v>
       </c>
       <c r="D25">
-        <v>1450.031348465509</v>
+        <v>1452.710442186641</v>
       </c>
       <c r="E25">
         <v>-640.8890000000001</v>
@@ -3331,37 +3331,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M25">
-        <v>82.5035098293764</v>
+        <v>81.4683856293764</v>
       </c>
       <c r="N25">
-        <v>513.5740411910317</v>
+        <v>514.6091653910318</v>
       </c>
       <c r="O25">
-        <v>92.44332741438571</v>
+        <v>92.62964977038571</v>
       </c>
       <c r="P25">
-        <v>421.130713776646</v>
+        <v>421.9795156206461</v>
       </c>
       <c r="Q25">
-        <v>508.9307137766461</v>
+        <v>509.7795156206461</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1949294949906671</v>
+        <v>0.1949660898850905</v>
       </c>
       <c r="T25">
         <v>0.7329085170122317</v>
       </c>
       <c r="U25">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V25">
         <v>0.18</v>
       </c>
       <c r="W25">
-        <v>0.1437859647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.224875065959525</v>
+        <v>7.316673166105683</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.183930722528159</v>
+        <v>0.1835258876858242</v>
       </c>
       <c r="C26">
-        <v>1821.821573531869</v>
+        <v>1824.599558391944</v>
       </c>
       <c r="D26">
-        <v>1445.089573531869</v>
+        <v>1447.867558391944</v>
       </c>
       <c r="E26">
         <v>-620.432</v>
@@ -3413,37 +3413,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M26">
-        <v>86.09061895239276</v>
+        <v>85.01048935239277</v>
       </c>
       <c r="N26">
-        <v>509.9869320680153</v>
+        <v>511.0670616680154</v>
       </c>
       <c r="O26">
-        <v>91.79764777224275</v>
+        <v>91.99207110024275</v>
       </c>
       <c r="P26">
-        <v>418.1892842957726</v>
+        <v>419.0749905677726</v>
       </c>
       <c r="Q26">
-        <v>505.9892842957727</v>
+        <v>506.8749905677727</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1966080144583715</v>
+        <v>0.1966450212447731</v>
       </c>
       <c r="T26">
         <v>0.7411577316557089</v>
       </c>
       <c r="U26">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V26">
         <v>0.18</v>
       </c>
       <c r="W26">
-        <v>0.1437859647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.923838604877878</v>
+        <v>7.011811784184612</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1846949620211992</v>
+        <v>0.1842720342678237</v>
       </c>
       <c r="C27">
-        <v>1796.45636779494</v>
+        <v>1799.331856642364</v>
       </c>
       <c r="D27">
-        <v>1440.18136779494</v>
+        <v>1443.056856642364</v>
       </c>
       <c r="E27">
         <v>-599.9750000000001</v>
@@ -3495,37 +3495,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M27">
-        <v>89.67772807540912</v>
+        <v>88.55259307540913</v>
       </c>
       <c r="N27">
-        <v>506.399822944999</v>
+        <v>507.524957944999</v>
       </c>
       <c r="O27">
-        <v>91.15196813009982</v>
+        <v>91.35449243009981</v>
       </c>
       <c r="P27">
-        <v>415.2478548148992</v>
+        <v>416.1704655148991</v>
       </c>
       <c r="Q27">
-        <v>503.0478548148993</v>
+        <v>503.9704655148992</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1983312944452146</v>
+        <v>0.1983687241073806</v>
       </c>
       <c r="T27">
         <v>0.7496269253563455</v>
       </c>
       <c r="U27">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V27">
         <v>0.18</v>
       </c>
       <c r="W27">
-        <v>0.1437859647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.646885060682764</v>
+        <v>6.731339312817227</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1854592015142393</v>
+        <v>0.1850181808498231</v>
       </c>
       <c r="C28">
-        <v>1771.124390362082</v>
+        <v>1774.096017214895</v>
       </c>
       <c r="D28">
-        <v>1435.306390362082</v>
+        <v>1438.278017214895</v>
       </c>
       <c r="E28">
         <v>-579.518</v>
@@ -3577,37 +3577,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M28">
-        <v>93.2648371984255</v>
+        <v>92.0946967984255</v>
       </c>
       <c r="N28">
-        <v>502.8127138219826</v>
+        <v>503.9828542219826</v>
       </c>
       <c r="O28">
-        <v>90.50628848795687</v>
+        <v>90.71691375995687</v>
       </c>
       <c r="P28">
-        <v>412.3064253340258</v>
+        <v>413.2659404620258</v>
       </c>
       <c r="Q28">
-        <v>500.1064253340259</v>
+        <v>501.0659404620258</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.2001011495668373</v>
+        <v>0.2001390135338423</v>
       </c>
       <c r="T28">
         <v>0.7583250161840263</v>
       </c>
       <c r="U28">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V28">
         <v>0.18</v>
       </c>
       <c r="W28">
-        <v>0.1437859647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.391235635271888</v>
+        <v>6.472441646939642</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1862234410072795</v>
+        <v>0.1857643274318225</v>
       </c>
       <c r="C29">
-        <v>1745.825304940736</v>
+        <v>1748.891724607738</v>
       </c>
       <c r="D29">
-        <v>1430.464304940736</v>
+        <v>1433.530724607738</v>
       </c>
       <c r="E29">
         <v>-559.061</v>
@@ -3659,37 +3659,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M29">
-        <v>96.85194632144186</v>
+        <v>95.63680052144187</v>
       </c>
       <c r="N29">
-        <v>499.2256046989663</v>
+        <v>500.4407504989663</v>
       </c>
       <c r="O29">
-        <v>89.86060884581393</v>
+        <v>90.07933508981392</v>
       </c>
       <c r="P29">
-        <v>409.3649958531523</v>
+        <v>410.3614154091524</v>
       </c>
       <c r="Q29">
-        <v>497.1649958531524</v>
+        <v>498.1614154091524</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.2019194938698743</v>
+        <v>0.2019578040404811</v>
       </c>
       <c r="T29">
         <v>0.7672614108699997</v>
       </c>
       <c r="U29">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V29">
         <v>0.18</v>
       </c>
       <c r="W29">
-        <v>0.1437859647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.154523204335892</v>
+        <v>6.232721585941878</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1873091205003197</v>
+        <v>0.1867400740138219</v>
       </c>
       <c r="C30">
-        <v>1718.545536421562</v>
+        <v>1722.273706031259</v>
       </c>
       <c r="D30">
-        <v>1423.641536421562</v>
+        <v>1427.369706031259</v>
       </c>
       <c r="E30">
         <v>-538.604</v>
@@ -3741,37 +3741,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M30">
-        <v>101.2409698444582</v>
+        <v>99.75170024445823</v>
       </c>
       <c r="N30">
-        <v>494.8365811759499</v>
+        <v>496.3258507759499</v>
       </c>
       <c r="O30">
-        <v>89.07058461167098</v>
+        <v>89.33865313967098</v>
       </c>
       <c r="P30">
-        <v>405.7659965642789</v>
+        <v>406.9871976362789</v>
       </c>
       <c r="Q30">
-        <v>493.565996564279</v>
+        <v>494.787197636279</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.2037883477368846</v>
+        <v>0.2038271165056377</v>
       </c>
       <c r="T30">
         <v>0.7764460387416947</v>
       </c>
       <c r="U30">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V30">
         <v>0.18</v>
       </c>
       <c r="W30">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.887710794712784</v>
+        <v>5.975612942532512</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1880848399933599</v>
+        <v>0.1874944205958213</v>
       </c>
       <c r="C31">
-        <v>1693.253387918627</v>
+        <v>1697.089818415862</v>
       </c>
       <c r="D31">
-        <v>1418.806387918627</v>
+        <v>1422.642818415862</v>
       </c>
       <c r="E31">
         <v>-518.1470000000002</v>
@@ -3823,37 +3823,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M31">
-        <v>104.8567187674746</v>
+        <v>103.3142609674746</v>
       </c>
       <c r="N31">
-        <v>491.2208322529335</v>
+        <v>492.7632900529335</v>
       </c>
       <c r="O31">
-        <v>88.41974980552803</v>
+        <v>88.69739220952803</v>
       </c>
       <c r="P31">
-        <v>402.8010824474055</v>
+        <v>404.0658978434055</v>
       </c>
       <c r="Q31">
-        <v>490.6010824474056</v>
+        <v>491.8658978434056</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.2057098453747966</v>
+        <v>0.2057490856599535</v>
       </c>
       <c r="T31">
         <v>0.7858893885252682</v>
       </c>
       <c r="U31">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V31">
         <v>0.18</v>
       </c>
       <c r="W31">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.684686284550275</v>
+        <v>5.769557323824495</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1888605594864001</v>
+        <v>0.1882487671778207</v>
       </c>
       <c r="C32">
-        <v>1667.993971711979</v>
+        <v>1671.93713465449</v>
       </c>
       <c r="D32">
-        <v>1414.003971711979</v>
+        <v>1417.94713465449</v>
       </c>
       <c r="E32">
         <v>-497.6900000000001</v>
@@ -3905,37 +3905,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M32">
-        <v>108.472467690491</v>
+        <v>106.876821690491</v>
       </c>
       <c r="N32">
-        <v>487.6050833299172</v>
+        <v>489.2007293299172</v>
       </c>
       <c r="O32">
-        <v>87.76891499938509</v>
+        <v>88.05613127938508</v>
       </c>
       <c r="P32">
-        <v>399.8361683305321</v>
+        <v>401.1445980505321</v>
       </c>
       <c r="Q32">
-        <v>487.6361683305322</v>
+        <v>488.9445980505321</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.2076862429452203</v>
+        <v>0.2077259682186784</v>
       </c>
       <c r="T32">
         <v>0.7956025483026583</v>
       </c>
       <c r="U32">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V32">
         <v>0.18</v>
       </c>
       <c r="W32">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.495196741731932</v>
+        <v>5.577238746363678</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1896362789794402</v>
+        <v>0.1890031137598202</v>
       </c>
       <c r="C33">
-        <v>1642.76695654325</v>
+        <v>1646.815346782149</v>
       </c>
       <c r="D33">
-        <v>1409.23395654325</v>
+        <v>1413.282346782149</v>
       </c>
       <c r="E33">
         <v>-477.2330000000001</v>
@@ -3987,37 +3987,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M33">
-        <v>112.0882166135073</v>
+        <v>110.4393824135073</v>
       </c>
       <c r="N33">
-        <v>483.9893344069008</v>
+        <v>485.6381686069008</v>
       </c>
       <c r="O33">
-        <v>87.11808019324214</v>
+        <v>87.41487034924214</v>
       </c>
       <c r="P33">
-        <v>396.8712542136587</v>
+        <v>398.2232982576586</v>
       </c>
       <c r="Q33">
-        <v>484.6712542136588</v>
+        <v>486.0232982576587</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.2097199274017433</v>
+        <v>0.2097601517211345</v>
       </c>
       <c r="T33">
         <v>0.8055972489431612</v>
       </c>
       <c r="U33">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V33">
         <v>0.18</v>
       </c>
       <c r="W33">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.317932330708321</v>
+        <v>5.397327819061623</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1904119984724804</v>
+        <v>0.1897574603418196</v>
       </c>
       <c r="C34">
-        <v>1617.572015608924</v>
+        <v>1621.724150873154</v>
       </c>
       <c r="D34">
-        <v>1404.496015608924</v>
+        <v>1408.648150873154</v>
       </c>
       <c r="E34">
         <v>-456.7760000000001</v>
@@ -4069,37 +4069,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M34">
-        <v>115.7039655365237</v>
+        <v>114.0019431365237</v>
       </c>
       <c r="N34">
-        <v>480.3735854838844</v>
+        <v>482.0756078838845</v>
       </c>
       <c r="O34">
-        <v>86.4672453870992</v>
+        <v>86.7736094190992</v>
       </c>
       <c r="P34">
-        <v>393.9063400967852</v>
+        <v>395.3019984647852</v>
       </c>
       <c r="Q34">
-        <v>481.7063400967853</v>
+        <v>483.1019984647853</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.2118134261069875</v>
+        <v>0.2118541641501334</v>
       </c>
       <c r="T34">
         <v>0.8158859113672082</v>
       </c>
       <c r="U34">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V34">
         <v>0.18</v>
       </c>
       <c r="W34">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.151746945373686</v>
+        <v>5.228661324715948</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1911877179655206</v>
+        <v>0.190511806923819</v>
       </c>
       <c r="C35">
-        <v>1592.408826485701</v>
+        <v>1596.663246975114</v>
       </c>
       <c r="D35">
-        <v>1399.789826485701</v>
+        <v>1404.044246975114</v>
       </c>
       <c r="E35">
         <v>-436.3190000000001</v>
@@ -4151,37 +4151,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M35">
-        <v>119.3197144595401</v>
+        <v>117.5645038595401</v>
       </c>
       <c r="N35">
-        <v>476.7578365608681</v>
+        <v>478.513047160868</v>
       </c>
       <c r="O35">
-        <v>85.81641058095626</v>
+        <v>86.13234848895624</v>
       </c>
       <c r="P35">
-        <v>390.9414259799119</v>
+        <v>392.3806986719118</v>
       </c>
       <c r="Q35">
-        <v>478.7414259799119</v>
+        <v>480.1806986719118</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.2139694173108958</v>
+        <v>0.2140106844128337</v>
       </c>
       <c r="T35">
         <v>0.8264816980427193</v>
       </c>
       <c r="U35">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V35">
         <v>0.18</v>
       </c>
       <c r="W35">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.995633401574484</v>
+        <v>5.070217042148798</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1919634374585608</v>
+        <v>0.1912661535058184</v>
       </c>
       <c r="C36">
-        <v>1567.277071057358</v>
+        <v>1571.632339044221</v>
       </c>
       <c r="D36">
-        <v>1395.115071057358</v>
+        <v>1399.470339044221</v>
       </c>
       <c r="E36">
         <v>-415.8620000000001</v>
@@ -4233,37 +4233,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M36">
-        <v>122.9354633825564</v>
+        <v>121.1270645825564</v>
       </c>
       <c r="N36">
-        <v>473.1420876378517</v>
+        <v>474.9504864378517</v>
       </c>
       <c r="O36">
-        <v>85.16557577481331</v>
+        <v>85.49108755881331</v>
       </c>
       <c r="P36">
-        <v>387.9765118630384</v>
+        <v>389.4593988790384</v>
       </c>
       <c r="Q36">
-        <v>475.7765118630385</v>
+        <v>477.2593988790385</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.2161907415815891</v>
+        <v>0.2162325537744038</v>
       </c>
       <c r="T36">
         <v>0.8373985691629429</v>
       </c>
       <c r="U36">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V36">
         <v>0.18</v>
       </c>
       <c r="W36">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.848703007410528</v>
+        <v>4.921093011497364</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1927391569516009</v>
+        <v>0.1920205000878178</v>
       </c>
       <c r="C37">
-        <v>1542.176435443065</v>
+        <v>1546.631134881786</v>
       </c>
       <c r="D37">
-        <v>1390.471435443065</v>
+        <v>1394.926134881787</v>
       </c>
       <c r="E37">
         <v>-395.405</v>
@@ -4315,37 +4315,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M37">
-        <v>126.5512123055728</v>
+        <v>124.6896253055728</v>
       </c>
       <c r="N37">
-        <v>469.5263387148353</v>
+        <v>471.3879257148353</v>
       </c>
       <c r="O37">
-        <v>84.51474096867035</v>
+        <v>84.84982662867036</v>
       </c>
       <c r="P37">
-        <v>385.011597746165</v>
+        <v>386.5380990861649</v>
       </c>
       <c r="Q37">
-        <v>472.811597746165</v>
+        <v>474.338099086165</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.2184804142913807</v>
+        <v>0.218522788347099</v>
       </c>
       <c r="T37">
         <v>0.8486513440099425</v>
       </c>
       <c r="U37">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V37">
         <v>0.18</v>
       </c>
       <c r="W37">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.710168635770227</v>
+        <v>4.780490354026009</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1935148764446411</v>
+        <v>0.1927748466698173</v>
       </c>
       <c r="C38">
-        <v>1517.106609927135</v>
+        <v>1521.659346072021</v>
       </c>
       <c r="D38">
-        <v>1385.858609927135</v>
+        <v>1390.411346072021</v>
       </c>
       <c r="E38">
         <v>-374.9480000000001</v>
@@ -4397,37 +4397,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M38">
-        <v>130.1669612285891</v>
+        <v>128.2521860285891</v>
       </c>
       <c r="N38">
-        <v>465.910589791819</v>
+        <v>467.825364991819</v>
       </c>
       <c r="O38">
-        <v>83.86390616252741</v>
+        <v>84.20856569852742</v>
       </c>
       <c r="P38">
-        <v>382.0466836292916</v>
+        <v>383.6167992932916</v>
       </c>
       <c r="Q38">
-        <v>469.8466836292916</v>
+        <v>471.4167992932917</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.2208416392733533</v>
+        <v>0.220884592750191</v>
       </c>
       <c r="T38">
         <v>0.8602557680709109</v>
       </c>
       <c r="U38">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V38">
         <v>0.18</v>
       </c>
       <c r="W38">
-        <v>0.1449339647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.579330618109943</v>
+        <v>4.647698955303065</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1950794359376813</v>
+        <v>0.1935291932518167</v>
       </c>
       <c r="C39">
-        <v>1487.438434308208</v>
+        <v>1496.716687921008</v>
       </c>
       <c r="D39">
-        <v>1376.647434308208</v>
+        <v>1385.925687921008</v>
       </c>
       <c r="E39">
         <v>-354.4910000000001</v>
@@ -4479,45 +4479,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M39">
-        <v>135.7506735516055</v>
+        <v>131.8147467516055</v>
       </c>
       <c r="N39">
-        <v>460.3268774688026</v>
+        <v>464.2628042688026</v>
       </c>
       <c r="O39">
-        <v>82.85883794438448</v>
+        <v>83.56730476838446</v>
       </c>
       <c r="P39">
-        <v>377.4680395244181</v>
+        <v>380.6954995004181</v>
       </c>
       <c r="Q39">
-        <v>465.2680395244182</v>
+        <v>468.4954995004182</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.2232778237785631</v>
+        <v>0.2233213750708415</v>
       </c>
       <c r="T39">
         <v>0.8722285865465131</v>
       </c>
       <c r="U39">
-        <v>0.1793487374989668</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V39">
         <v>0.18</v>
       </c>
       <c r="W39">
-        <v>0.1470659647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.390973064261149</v>
+        <v>4.522085470024605</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1958764754307215</v>
+        <v>0.1950625398338161</v>
       </c>
       <c r="C40">
-        <v>1462.335868675401</v>
+        <v>1467.230399269107</v>
       </c>
       <c r="D40">
-        <v>1372.001868675401</v>
+        <v>1376.896399269106</v>
       </c>
       <c r="E40">
         <v>-334.0340000000001</v>
@@ -4561,37 +4561,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M40">
-        <v>139.4196106746219</v>
+        <v>137.3207224746219</v>
       </c>
       <c r="N40">
-        <v>456.6579403457863</v>
+        <v>458.7568285457862</v>
       </c>
       <c r="O40">
-        <v>82.19842926224153</v>
+        <v>82.57622913824152</v>
       </c>
       <c r="P40">
-        <v>374.4595110835448</v>
+        <v>376.1805994075447</v>
       </c>
       <c r="Q40">
-        <v>462.2595110835449</v>
+        <v>463.9805994075448</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.2257925948807152</v>
+        <v>0.2258367632728033</v>
       </c>
       <c r="T40">
         <v>0.8845876249729414</v>
       </c>
       <c r="U40">
-        <v>0.1793487374989668</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V40">
         <v>0.18</v>
       </c>
       <c r="W40">
-        <v>0.1470659647491528</v>
+        <v>0.1448519647491529</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.275421141517436</v>
+        <v>4.340769115386562</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1966735149237617</v>
+        <v>0.1958373864158155</v>
       </c>
       <c r="C41">
-        <v>1437.264550982096</v>
+        <v>1442.255226810376</v>
       </c>
       <c r="D41">
-        <v>1367.387550982096</v>
+        <v>1372.378226810376</v>
       </c>
       <c r="E41">
         <v>-313.577</v>
@@ -4643,37 +4643,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M41">
-        <v>143.0885477976383</v>
+        <v>140.9344256976383</v>
       </c>
       <c r="N41">
-        <v>452.9890032227698</v>
+        <v>455.1431253227698</v>
       </c>
       <c r="O41">
-        <v>81.53802058009857</v>
+        <v>81.92576255809857</v>
       </c>
       <c r="P41">
-        <v>371.4509826426712</v>
+        <v>373.2173627646713</v>
       </c>
       <c r="Q41">
-        <v>459.2509826426713</v>
+        <v>461.0173627646714</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.2283898174944132</v>
+        <v>0.2284346232190917</v>
       </c>
       <c r="T41">
         <v>0.8973518777740066</v>
       </c>
       <c r="U41">
-        <v>0.1793487374989668</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V41">
         <v>0.18</v>
       </c>
       <c r="W41">
-        <v>0.1470659647491528</v>
+        <v>0.1448519647491529</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.165794958401602</v>
+        <v>4.229467343197163</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1974705544168018</v>
+        <v>0.196612232997815</v>
       </c>
       <c r="C42">
-        <v>1412.224167005807</v>
+        <v>1417.309609392954</v>
       </c>
       <c r="D42">
-        <v>1362.804167005808</v>
+        <v>1367.889609392954</v>
       </c>
       <c r="E42">
         <v>-293.12</v>
@@ -4725,37 +4725,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M42">
-        <v>146.7574849206546</v>
+        <v>144.5481289206546</v>
       </c>
       <c r="N42">
-        <v>449.3200660997535</v>
+        <v>451.5294220997535</v>
       </c>
       <c r="O42">
-        <v>80.87761189795563</v>
+        <v>81.27529597795562</v>
       </c>
       <c r="P42">
-        <v>368.4424542017979</v>
+        <v>370.2541261217979</v>
       </c>
       <c r="Q42">
-        <v>456.242454201798</v>
+        <v>458.0541261217979</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.2310736141952345</v>
+        <v>0.231119078496923</v>
       </c>
       <c r="T42">
         <v>0.9105416056684407</v>
       </c>
       <c r="U42">
-        <v>0.1793487374989668</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V42">
         <v>0.18</v>
       </c>
       <c r="W42">
-        <v>0.1470659647491528</v>
+        <v>0.1448519647491529</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.061650084441562</v>
+        <v>4.123730659617234</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.199175333909842</v>
+        <v>0.1973870795798144</v>
       </c>
       <c r="C43">
-        <v>1382.066224716508</v>
+        <v>1392.393257966511</v>
       </c>
       <c r="D43">
-        <v>1353.103224716508</v>
+        <v>1363.43025796651</v>
       </c>
       <c r="E43">
         <v>-272.663</v>
@@ -4807,45 +4807,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M43">
-        <v>152.691011943671</v>
+        <v>148.161832143671</v>
       </c>
       <c r="N43">
-        <v>443.3865390767371</v>
+        <v>447.9157188767372</v>
       </c>
       <c r="O43">
-        <v>79.80957703381267</v>
+        <v>80.62482939781269</v>
       </c>
       <c r="P43">
-        <v>363.5769620429244</v>
+        <v>367.2908894789245</v>
       </c>
       <c r="Q43">
-        <v>451.3769620429245</v>
+        <v>455.0908894789246</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.2338483870554057</v>
+        <v>0.2338945322587486</v>
       </c>
       <c r="T43">
         <v>0.9241784429830249</v>
       </c>
       <c r="U43">
-        <v>0.1820487374989669</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V43">
         <v>0.18</v>
       </c>
       <c r="W43">
-        <v>0.1492799647491528</v>
+        <v>0.1448519647491529</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.903815577830516</v>
+        <v>4.023151863041205</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1999945134028822</v>
+        <v>0.1993673261618138</v>
       </c>
       <c r="C44">
-        <v>1356.996693895815</v>
+        <v>1360.670672050217</v>
       </c>
       <c r="D44">
-        <v>1348.490693895815</v>
+        <v>1352.164672050217</v>
       </c>
       <c r="E44">
         <v>-252.2060000000001</v>
@@ -4889,37 +4889,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M44">
-        <v>156.4151829666873</v>
+        <v>154.7827143666873</v>
       </c>
       <c r="N44">
-        <v>439.6623680537208</v>
+        <v>441.2948366537208</v>
       </c>
       <c r="O44">
-        <v>79.13922624966975</v>
+        <v>79.43307059766974</v>
       </c>
       <c r="P44">
-        <v>360.5231418040511</v>
+        <v>361.861766056051</v>
       </c>
       <c r="Q44">
-        <v>448.3231418040511</v>
+        <v>449.6617660560511</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.2367188417383414</v>
+        <v>0.2367656913227062</v>
       </c>
       <c r="T44">
         <v>0.9382855160670777</v>
       </c>
       <c r="U44">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V44">
         <v>0.18</v>
       </c>
       <c r="W44">
-        <v>0.1492799647491528</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.810867587882171</v>
+        <v>3.851060200483841</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.2008136928959224</v>
+        <v>0.2001708727438132</v>
       </c>
       <c r="C45">
-        <v>1331.958503126213</v>
+        <v>1335.695231805429</v>
       </c>
       <c r="D45">
-        <v>1343.909503126213</v>
+        <v>1347.646231805429</v>
       </c>
       <c r="E45">
         <v>-231.7490000000001</v>
@@ -4971,37 +4971,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M45">
-        <v>160.1393539897037</v>
+        <v>158.4680170897037</v>
       </c>
       <c r="N45">
-        <v>435.9381970307044</v>
+        <v>437.6095339307044</v>
       </c>
       <c r="O45">
-        <v>78.46887546552679</v>
+        <v>78.76971610752679</v>
       </c>
       <c r="P45">
-        <v>357.4693215651777</v>
+        <v>358.8398178231776</v>
       </c>
       <c r="Q45">
-        <v>445.2693215651777</v>
+        <v>446.6398178231777</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.2396900141294503</v>
+        <v>0.2397375928099605</v>
       </c>
       <c r="T45">
         <v>0.9528875741716234</v>
       </c>
       <c r="U45">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V45">
         <v>0.18</v>
       </c>
       <c r="W45">
-        <v>0.1492799647491528</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.722242760257004</v>
+        <v>3.761500660937706</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.2016328723889625</v>
+        <v>0.2009744193258127</v>
       </c>
       <c r="C46">
-        <v>1306.951334077045</v>
+        <v>1310.749888938665</v>
       </c>
       <c r="D46">
-        <v>1339.359334077046</v>
+        <v>1343.157888938665</v>
       </c>
       <c r="E46">
         <v>-211.292</v>
@@ -5053,37 +5053,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M46">
-        <v>163.8635250127201</v>
+        <v>162.1533198127201</v>
       </c>
       <c r="N46">
-        <v>432.2140260076881</v>
+        <v>433.9242312076881</v>
       </c>
       <c r="O46">
-        <v>77.79852468138385</v>
+        <v>78.10636161738385</v>
       </c>
       <c r="P46">
-        <v>354.4155013263042</v>
+        <v>355.8178695903042</v>
       </c>
       <c r="Q46">
-        <v>442.2155013263043</v>
+        <v>443.6178695903043</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.2427672998202416</v>
+        <v>0.2428156336360453</v>
       </c>
       <c r="T46">
         <v>0.9680111343513317</v>
       </c>
       <c r="U46">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V46">
         <v>0.18</v>
       </c>
       <c r="W46">
-        <v>0.1492799647491528</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.637646333887527</v>
+        <v>3.676012009552758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.2024520518820027</v>
+        <v>0.2017779659078121</v>
       </c>
       <c r="C47">
-        <v>1281.97487271429</v>
+        <v>1285.83434372972</v>
       </c>
       <c r="D47">
-        <v>1334.83987271429</v>
+        <v>1338.69934372972</v>
       </c>
       <c r="E47">
         <v>-190.835</v>
@@ -5135,37 +5135,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M47">
-        <v>167.5876960357364</v>
+        <v>165.8386225357364</v>
       </c>
       <c r="N47">
-        <v>428.4898549846717</v>
+        <v>430.2389284846716</v>
       </c>
       <c r="O47">
-        <v>77.1281738972409</v>
+        <v>77.44300712724089</v>
       </c>
       <c r="P47">
-        <v>351.3616810874308</v>
+        <v>352.7959213574308</v>
       </c>
       <c r="Q47">
-        <v>439.1616810874308</v>
+        <v>440.5959213574308</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.2459564868088799</v>
+        <v>0.2460056032194423</v>
       </c>
       <c r="T47">
         <v>0.9836846421739383</v>
       </c>
       <c r="U47">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V47">
         <v>0.18</v>
       </c>
       <c r="W47">
-        <v>0.1492799647491528</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.556809748690026</v>
+        <v>3.594322853784918</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.2050440713750429</v>
+        <v>0.2025815124898115</v>
       </c>
       <c r="C48">
-        <v>1247.416364843768</v>
+        <v>1260.948300424842</v>
       </c>
       <c r="D48">
-        <v>1320.738364843768</v>
+        <v>1334.270300424842</v>
       </c>
       <c r="E48">
         <v>-170.378</v>
@@ -5217,45 +5217,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M48">
-        <v>175.7346704587528</v>
+        <v>169.5239252587528</v>
       </c>
       <c r="N48">
-        <v>420.3428805616553</v>
+        <v>426.5536257616553</v>
       </c>
       <c r="O48">
-        <v>75.66171850109795</v>
+        <v>76.77965263709795</v>
       </c>
       <c r="P48">
-        <v>344.6811620605574</v>
+        <v>349.7739731245574</v>
       </c>
       <c r="Q48">
-        <v>432.4811620605574</v>
+        <v>437.5739731245574</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.2492637918341344</v>
+        <v>0.2493137198244466</v>
       </c>
       <c r="T48">
         <v>0.9999386502862712</v>
       </c>
       <c r="U48">
-        <v>0.1867487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V48">
         <v>0.18</v>
       </c>
       <c r="W48">
-        <v>0.1531339647491528</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.391917767076675</v>
+        <v>3.516185400441768</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.2059017908680831</v>
+        <v>0.2044641790718109</v>
       </c>
       <c r="C49">
-        <v>1222.35844522902</v>
+        <v>1230.228176547125</v>
       </c>
       <c r="D49">
-        <v>1316.13744522902</v>
+        <v>1324.007176547125</v>
       </c>
       <c r="E49">
         <v>-149.921</v>
@@ -5299,37 +5299,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M49">
-        <v>179.5549893817692</v>
+        <v>175.9013691817692</v>
       </c>
       <c r="N49">
-        <v>416.522561638639</v>
+        <v>420.176181838639</v>
       </c>
       <c r="O49">
-        <v>74.97406109495502</v>
+        <v>75.63171273095502</v>
       </c>
       <c r="P49">
-        <v>341.548500543684</v>
+        <v>344.5444691076839</v>
       </c>
       <c r="Q49">
-        <v>429.3485005436841</v>
+        <v>432.344469107684</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.2526959008226061</v>
+        <v>0.2527466710183189</v>
       </c>
       <c r="T49">
         <v>1.016806017195296</v>
       </c>
       <c r="U49">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V49">
         <v>0.18</v>
       </c>
       <c r="W49">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.319749303947384</v>
+        <v>3.388703304545892</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.2067595103611232</v>
+        <v>0.2052906856538103</v>
       </c>
       <c r="C50">
-        <v>1197.332469828935</v>
+        <v>1205.315281763363</v>
       </c>
       <c r="D50">
-        <v>1311.568469828935</v>
+        <v>1319.551281763363</v>
       </c>
       <c r="E50">
         <v>-129.4640000000001</v>
@@ -5381,37 +5381,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M50">
-        <v>183.3753083047855</v>
+        <v>179.6439515047855</v>
       </c>
       <c r="N50">
-        <v>412.7022427156226</v>
+        <v>416.4335995156226</v>
       </c>
       <c r="O50">
-        <v>74.28640368881206</v>
+        <v>74.95804791281206</v>
       </c>
       <c r="P50">
-        <v>338.4158390268105</v>
+        <v>341.4755516028105</v>
       </c>
       <c r="Q50">
-        <v>426.2158390268106</v>
+        <v>429.2755516028106</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.2562600140029421</v>
+        <v>0.256311658796571</v>
       </c>
       <c r="T50">
         <v>1.034322128985437</v>
       </c>
       <c r="U50">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V50">
         <v>0.18</v>
       </c>
       <c r="W50">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.250587860115147</v>
+        <v>3.318105319034519</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.2076172298541635</v>
+        <v>0.2061171922358097</v>
       </c>
       <c r="C51">
-        <v>1172.338107111093</v>
+        <v>1180.432278662332</v>
       </c>
       <c r="D51">
-        <v>1307.031107111093</v>
+        <v>1315.125278662332</v>
       </c>
       <c r="E51">
         <v>-109.0070000000001</v>
@@ -5463,37 +5463,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M51">
-        <v>187.1956272278019</v>
+        <v>183.3865338278019</v>
       </c>
       <c r="N51">
-        <v>408.8819237926062</v>
+        <v>412.6910171926062</v>
       </c>
       <c r="O51">
-        <v>73.59874628266913</v>
+        <v>74.28438309466911</v>
       </c>
       <c r="P51">
-        <v>335.2831775099371</v>
+        <v>338.4066340979371</v>
       </c>
       <c r="Q51">
-        <v>423.0831775099372</v>
+        <v>426.2066340979371</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.259963896327605</v>
+        <v>0.2600164500171075</v>
       </c>
       <c r="T51">
         <v>1.052525147120289</v>
       </c>
       <c r="U51">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V51">
         <v>0.18</v>
       </c>
       <c r="W51">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.184249332357695</v>
+        <v>3.250388883952182</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.2084749493472036</v>
+        <v>0.2069436988178092</v>
       </c>
       <c r="C52">
-        <v>1147.375030114999</v>
+        <v>1155.578867463933</v>
       </c>
       <c r="D52">
-        <v>1302.525030114999</v>
+        <v>1310.728867463933</v>
       </c>
       <c r="E52">
         <v>-88.55000000000007</v>
@@ -5545,37 +5545,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M52">
-        <v>191.0159461508183</v>
+        <v>187.1291161508183</v>
       </c>
       <c r="N52">
-        <v>405.0616048695899</v>
+        <v>408.9484348695898</v>
       </c>
       <c r="O52">
-        <v>72.91108887652618</v>
+        <v>73.61071827652617</v>
       </c>
       <c r="P52">
-        <v>332.1505159930637</v>
+        <v>335.3377165930636</v>
       </c>
       <c r="Q52">
-        <v>419.9505159930637</v>
+        <v>423.1377165930637</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.2638159339452544</v>
+        <v>0.2638694328864655</v>
       </c>
       <c r="T52">
         <v>1.071456285980536</v>
       </c>
       <c r="U52">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V52">
         <v>0.18</v>
       </c>
       <c r="W52">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.120564345710541</v>
+        <v>3.185381106273138</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2093326688402438</v>
+        <v>0.2077702053998086</v>
       </c>
       <c r="C53">
-        <v>1122.442916373535</v>
+        <v>1130.754752383323</v>
       </c>
       <c r="D53">
-        <v>1298.049916373535</v>
+        <v>1306.361752383322</v>
       </c>
       <c r="E53">
         <v>-68.09300000000007</v>
@@ -5627,37 +5627,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M53">
-        <v>194.8362650738346</v>
+        <v>190.8716984738346</v>
       </c>
       <c r="N53">
-        <v>401.2412859465735</v>
+        <v>405.2058525465735</v>
       </c>
       <c r="O53">
-        <v>72.22343147038323</v>
+        <v>72.93705345838323</v>
       </c>
       <c r="P53">
-        <v>329.0178544761903</v>
+        <v>332.2687990881903</v>
       </c>
       <c r="Q53">
-        <v>416.8178544761903</v>
+        <v>420.0687990881904</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.267825197588114</v>
+        <v>0.267879680362736</v>
       </c>
       <c r="T53">
         <v>1.091160124386098</v>
       </c>
       <c r="U53">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V53">
         <v>0.18</v>
       </c>
       <c r="W53">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.059376809520138</v>
+        <v>3.122922653208959</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.210190388333284</v>
+        <v>0.208596711981808</v>
       </c>
       <c r="C54">
-        <v>1097.541447836042</v>
+        <v>1105.959641564576</v>
       </c>
       <c r="D54">
-        <v>1293.605447836042</v>
+        <v>1302.023641564576</v>
       </c>
       <c r="E54">
         <v>-47.63599999999997</v>
@@ -5709,37 +5709,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M54">
-        <v>198.656583996851</v>
+        <v>194.614280796851</v>
       </c>
       <c r="N54">
-        <v>397.4209670235571</v>
+        <v>401.4632702235571</v>
       </c>
       <c r="O54">
-        <v>71.53577406424027</v>
+        <v>72.26338864024028</v>
       </c>
       <c r="P54">
-        <v>325.8851929593168</v>
+        <v>329.1998815833168</v>
       </c>
       <c r="Q54">
-        <v>413.6851929593169</v>
+        <v>416.9998815833169</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.2720015138827594</v>
+        <v>0.2720570214838511</v>
       </c>
       <c r="T54">
         <v>1.11168495605856</v>
       </c>
       <c r="U54">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V54">
         <v>0.18</v>
       </c>
       <c r="W54">
-        <v>0.1531339647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.000542640106289</v>
+        <v>3.062866448339556</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2150898878263242</v>
+        <v>0.2094232185638074</v>
       </c>
       <c r="C55">
-        <v>1052.268859364569</v>
+        <v>1081.19324701567</v>
       </c>
       <c r="D55">
-        <v>1268.78985936457</v>
+        <v>1297.71424701567</v>
       </c>
       <c r="E55">
         <v>-27.17900000000009</v>
@@ -5791,45 +5791,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M55">
-        <v>212.5601582198673</v>
+        <v>198.3568631198674</v>
       </c>
       <c r="N55">
-        <v>383.5173928005408</v>
+        <v>397.7206879005407</v>
       </c>
       <c r="O55">
-        <v>69.03313070409735</v>
+        <v>71.58972382209733</v>
       </c>
       <c r="P55">
-        <v>314.4842620964434</v>
+        <v>326.1309640784434</v>
       </c>
       <c r="Q55">
-        <v>402.2842620964435</v>
+        <v>413.9309640784435</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.276355545764411</v>
+        <v>0.2764121218016093</v>
       </c>
       <c r="T55">
         <v>1.133083184823466</v>
       </c>
       <c r="U55">
-        <v>0.1960487374989668</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V55">
         <v>0.18</v>
       </c>
       <c r="W55">
-        <v>0.1607599647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.804276944524285</v>
+        <v>3.005076515352017</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2160238673193643</v>
+        <v>0.2137035651458068</v>
       </c>
       <c r="C56">
-        <v>1027.188977369197</v>
+        <v>1038.867292441527</v>
       </c>
       <c r="D56">
-        <v>1264.166977369197</v>
+        <v>1275.845292441527</v>
       </c>
       <c r="E56">
         <v>-6.72199999999998</v>
@@ -5873,37 +5873,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M56">
-        <v>216.5707272428837</v>
+        <v>210.7159338428837</v>
       </c>
       <c r="N56">
-        <v>379.5068237775244</v>
+        <v>385.3616171775244</v>
       </c>
       <c r="O56">
-        <v>68.31122827995439</v>
+        <v>69.3650910919544</v>
       </c>
       <c r="P56">
-        <v>311.19559549757</v>
+        <v>315.99652608557</v>
       </c>
       <c r="Q56">
-        <v>398.9955954975701</v>
+        <v>403.7965260855701</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.2808988833800474</v>
+        <v>0.2809565743070963</v>
       </c>
       <c r="T56">
         <v>1.155411771360759</v>
       </c>
       <c r="U56">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V56">
         <v>0.18</v>
       </c>
       <c r="W56">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.752345889996057</v>
+        <v>2.828820489032699</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2169578468124045</v>
+        <v>0.2145940317278063</v>
       </c>
       <c r="C57">
-        <v>1002.142660355938</v>
+        <v>1013.953055032513</v>
       </c>
       <c r="D57">
-        <v>1259.577660355937</v>
+        <v>1271.388055032513</v>
       </c>
       <c r="E57">
         <v>13.73500000000013</v>
@@ -5955,37 +5955,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M57">
-        <v>220.5812962659001</v>
+        <v>214.6180807659001</v>
       </c>
       <c r="N57">
-        <v>375.496254754508</v>
+        <v>381.459470254508</v>
       </c>
       <c r="O57">
-        <v>67.58932585581144</v>
+        <v>68.66270464581144</v>
       </c>
       <c r="P57">
-        <v>307.9069288986966</v>
+        <v>312.7967656086965</v>
       </c>
       <c r="Q57">
-        <v>395.7069288986967</v>
+        <v>400.5967656086966</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2856441471119343</v>
+        <v>0.2857030024794938</v>
       </c>
       <c r="T57">
         <v>1.178732739521932</v>
       </c>
       <c r="U57">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V57">
         <v>0.18</v>
       </c>
       <c r="W57">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.702303237450674</v>
+        <v>2.777387389232103</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2178918263054447</v>
+        <v>0.2154844983098056</v>
       </c>
       <c r="C58">
-        <v>977.1295440932731</v>
+        <v>989.0698524216928</v>
       </c>
       <c r="D58">
-        <v>1255.021544093273</v>
+        <v>1266.961852421693</v>
       </c>
       <c r="E58">
         <v>34.19200000000001</v>
@@ -6037,37 +6037,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M58">
-        <v>224.5918652889164</v>
+        <v>218.5202276889165</v>
       </c>
       <c r="N58">
-        <v>371.4856857314917</v>
+        <v>377.5573233314917</v>
       </c>
       <c r="O58">
-        <v>66.8674234316685</v>
+        <v>67.96031819966849</v>
       </c>
       <c r="P58">
-        <v>304.6182622998232</v>
+        <v>309.5970051318232</v>
       </c>
       <c r="Q58">
-        <v>392.4182622998233</v>
+        <v>397.3970051318232</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.2906051046498161</v>
+        <v>0.2906651773870002</v>
       </c>
       <c r="T58">
         <v>1.203113751690432</v>
       </c>
       <c r="U58">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V58">
         <v>0.18</v>
       </c>
       <c r="W58">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.654047822496198</v>
+        <v>2.72779118585296</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2188258057984849</v>
+        <v>0.2163749648918051</v>
       </c>
       <c r="C59">
-        <v>952.1492696006542</v>
+        <v>964.2173616005146</v>
       </c>
       <c r="D59">
-        <v>1250.498269600654</v>
+        <v>1262.566361600515</v>
       </c>
       <c r="E59">
         <v>54.64900000000011</v>
@@ -6119,37 +6119,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M59">
-        <v>228.6024343119328</v>
+        <v>222.4223746119329</v>
       </c>
       <c r="N59">
-        <v>367.4751167084753</v>
+        <v>373.6551764084753</v>
       </c>
       <c r="O59">
-        <v>66.14552100752555</v>
+        <v>67.25793175352554</v>
       </c>
       <c r="P59">
-        <v>301.3295957009498</v>
+        <v>306.3972446549497</v>
       </c>
       <c r="Q59">
-        <v>389.1295957009498</v>
+        <v>394.1972446549498</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.2957968043987623</v>
+        <v>0.2958581511274139</v>
       </c>
       <c r="T59">
         <v>1.228628764424908</v>
       </c>
       <c r="U59">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V59">
         <v>0.18</v>
       </c>
       <c r="W59">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.607485579996265</v>
+        <v>2.67993520013624</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.219759785291525</v>
+        <v>0.2172654314738045</v>
       </c>
       <c r="C60">
-        <v>927.2014830542107</v>
+        <v>939.3952640274069</v>
       </c>
       <c r="D60">
-        <v>1246.00748305421</v>
+        <v>1258.201264027407</v>
       </c>
       <c r="E60">
         <v>75.10599999999977</v>
@@ -6201,37 +6201,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M60">
-        <v>232.6130033349491</v>
+        <v>226.3245215349492</v>
       </c>
       <c r="N60">
-        <v>363.464547685459</v>
+        <v>369.753029485459</v>
       </c>
       <c r="O60">
-        <v>65.42361858338262</v>
+        <v>66.55554530738262</v>
       </c>
       <c r="P60">
-        <v>298.0409291020764</v>
+        <v>303.1974841780764</v>
       </c>
       <c r="Q60">
-        <v>385.8409291020765</v>
+        <v>390.9974841780764</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.3012357279452771</v>
+        <v>0.3012984093316568</v>
       </c>
       <c r="T60">
         <v>1.255358777765787</v>
       </c>
       <c r="U60">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V60">
         <v>0.18</v>
       </c>
       <c r="W60">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.562528932065296</v>
+        <v>2.633729420823547</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2206937647845652</v>
+        <v>0.2181558980558039</v>
       </c>
       <c r="C61">
-        <v>902.2858356944896</v>
+        <v>914.60324555082</v>
       </c>
       <c r="D61">
-        <v>1241.54883569449</v>
+        <v>1253.86624555082</v>
       </c>
       <c r="E61">
         <v>95.56299999999987</v>
@@ -6283,37 +6283,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M61">
-        <v>236.6235723579655</v>
+        <v>230.2266684579655</v>
       </c>
       <c r="N61">
-        <v>359.4539786624426</v>
+        <v>365.8508825624426</v>
       </c>
       <c r="O61">
-        <v>64.70171615923967</v>
+        <v>65.85315886123966</v>
       </c>
       <c r="P61">
-        <v>294.752262503203</v>
+        <v>299.997723701203</v>
       </c>
       <c r="Q61">
-        <v>382.5522625032031</v>
+        <v>387.797723701203</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.3069399648355244</v>
+        <v>0.3070040459848871</v>
       </c>
       <c r="T61">
         <v>1.283392694196466</v>
       </c>
       <c r="U61">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V61">
         <v>0.18</v>
       </c>
       <c r="W61">
-        <v>0.1607599647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.519096238301477</v>
+        <v>2.589089939114674</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2239401442776054</v>
+        <v>0.2190463646378034</v>
       </c>
       <c r="C62">
-        <v>866.5763767411477</v>
+        <v>889.8409963338609</v>
       </c>
       <c r="D62">
-        <v>1226.296376741148</v>
+        <v>1249.560996333861</v>
       </c>
       <c r="E62">
         <v>116.02</v>
@@ -6365,45 +6365,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M62">
-        <v>246.4030153809819</v>
+        <v>234.1288153809819</v>
       </c>
       <c r="N62">
-        <v>349.6745356394262</v>
+        <v>361.9487356394262</v>
       </c>
       <c r="O62">
-        <v>62.94141641509672</v>
+        <v>65.15077241509671</v>
       </c>
       <c r="P62">
-        <v>286.7331192243295</v>
+        <v>296.7979632243295</v>
       </c>
       <c r="Q62">
-        <v>374.5331192243295</v>
+        <v>384.5979632243296</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.3129294135702843</v>
+        <v>0.3129949644707791</v>
       </c>
       <c r="T62">
         <v>1.312828306448678</v>
       </c>
       <c r="U62">
-        <v>0.2007487374989669</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V62">
         <v>0.18</v>
       </c>
       <c r="W62">
-        <v>0.1646139647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.419116300580853</v>
+        <v>2.545938440129428</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2249126637706456</v>
+        <v>0.2199368312198028</v>
       </c>
       <c r="C63">
-        <v>841.6228709038196</v>
+        <v>865.1082107804764</v>
       </c>
       <c r="D63">
-        <v>1221.79987090382</v>
+        <v>1245.285210780476</v>
       </c>
       <c r="E63">
         <v>136.4769999999999</v>
@@ -6447,45 +6447,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M63">
-        <v>250.5097323039982</v>
+        <v>238.0309623039983</v>
       </c>
       <c r="N63">
-        <v>345.5678187164099</v>
+        <v>358.0465887164098</v>
       </c>
       <c r="O63">
-        <v>62.20220736895377</v>
+        <v>64.44838596895376</v>
       </c>
       <c r="P63">
-        <v>283.3656113474561</v>
+        <v>293.5982027474561</v>
       </c>
       <c r="Q63">
-        <v>371.1656113474561</v>
+        <v>381.3982027474561</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.3192260135222112</v>
+        <v>0.3192931095456911</v>
       </c>
       <c r="T63">
         <v>1.343773437277928</v>
       </c>
       <c r="U63">
-        <v>0.2007487374989669</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V63">
         <v>0.18</v>
       </c>
       <c r="W63">
-        <v>0.1646139647491528</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.379458656309037</v>
+        <v>2.504201744389602</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2258851832636857</v>
+        <v>0.2228100578018022</v>
       </c>
       <c r="C64">
-        <v>816.7022196028336</v>
+        <v>831.0520927645077</v>
       </c>
       <c r="D64">
-        <v>1217.336219602834</v>
+        <v>1231.686092764508</v>
       </c>
       <c r="E64">
         <v>156.934</v>
@@ -6529,37 +6529,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M64">
-        <v>254.6164492270146</v>
+        <v>246.8796118270146</v>
       </c>
       <c r="N64">
-        <v>341.4611017933935</v>
+        <v>349.1979391933935</v>
       </c>
       <c r="O64">
-        <v>61.46299832281083</v>
+        <v>62.85562905481083</v>
       </c>
       <c r="P64">
-        <v>279.9981034705826</v>
+        <v>286.3423101385827</v>
       </c>
       <c r="Q64">
-        <v>367.7981034705827</v>
+        <v>374.1423101385827</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.3258540134716079</v>
+        <v>0.3259227359403353</v>
       </c>
       <c r="T64">
         <v>1.376347259203452</v>
       </c>
       <c r="U64">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V64">
         <v>0.18</v>
       </c>
       <c r="W64">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.341080290884697</v>
+        <v>2.414446242073939</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2268577027567259</v>
+        <v>0.2237325043838016</v>
       </c>
       <c r="C65">
-        <v>791.8140640624672</v>
+        <v>806.2918750199312</v>
       </c>
       <c r="D65">
-        <v>1212.905064062467</v>
+        <v>1227.382875019931</v>
       </c>
       <c r="E65">
         <v>177.3909999999998</v>
@@ -6611,37 +6611,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M65">
-        <v>258.723166150031</v>
+        <v>250.861541050031</v>
       </c>
       <c r="N65">
-        <v>337.3543848703771</v>
+        <v>345.2160099703772</v>
       </c>
       <c r="O65">
-        <v>60.72378927666789</v>
+        <v>62.13888179466789</v>
       </c>
       <c r="P65">
-        <v>276.6305955937092</v>
+        <v>283.0771281757093</v>
       </c>
       <c r="Q65">
-        <v>364.4305955937093</v>
+        <v>370.8771281757093</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.3328402836885396</v>
+        <v>0.3329107205184738</v>
       </c>
       <c r="T65">
         <v>1.410681828260087</v>
       </c>
       <c r="U65">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V65">
         <v>0.18</v>
       </c>
       <c r="W65">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.30392028626748</v>
+        <v>2.376121698548955</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2278302222497661</v>
+        <v>0.224654950965801</v>
       </c>
       <c r="C66">
-        <v>766.9580507118858</v>
+        <v>781.5616214227784</v>
       </c>
       <c r="D66">
-        <v>1208.506050711886</v>
+        <v>1223.109621422778</v>
       </c>
       <c r="E66">
         <v>197.848</v>
@@ -6693,37 +6693,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M66">
-        <v>262.8298830730474</v>
+        <v>254.8434702730474</v>
       </c>
       <c r="N66">
-        <v>333.2476679473608</v>
+        <v>341.2340807473607</v>
       </c>
       <c r="O66">
-        <v>59.98458023052493</v>
+        <v>61.42213453452493</v>
       </c>
       <c r="P66">
-        <v>273.2630877168358</v>
+        <v>279.8119462128358</v>
       </c>
       <c r="Q66">
-        <v>361.0630877168359</v>
+        <v>367.6119462128358</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.3402146800286342</v>
+        <v>0.3402869264620645</v>
       </c>
       <c r="T66">
         <v>1.446923873375424</v>
       </c>
       <c r="U66">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V66">
         <v>0.18</v>
       </c>
       <c r="W66">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.26792153179455</v>
+        <v>2.338994797009128</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2288027417428063</v>
+        <v>0.2255773975478005</v>
       </c>
       <c r="C67">
-        <v>742.1338310911008</v>
+        <v>756.8610200895671</v>
       </c>
       <c r="D67">
-        <v>1204.138831091101</v>
+        <v>1218.866020089567</v>
       </c>
       <c r="E67">
         <v>218.3050000000001</v>
@@ -6775,37 +6775,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M67">
-        <v>266.9365999960638</v>
+        <v>258.8253994960638</v>
       </c>
       <c r="N67">
-        <v>329.1409510243444</v>
+        <v>337.2521515243444</v>
       </c>
       <c r="O67">
-        <v>59.24537118438198</v>
+        <v>60.70538727438198</v>
       </c>
       <c r="P67">
-        <v>269.8955798399624</v>
+        <v>276.5467642499624</v>
       </c>
       <c r="Q67">
-        <v>357.6955798399624</v>
+        <v>364.3467642499625</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.3480104704453056</v>
+        <v>0.348084629888146</v>
       </c>
       <c r="T67">
         <v>1.485236892497352</v>
       </c>
       <c r="U67">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V67">
         <v>0.18</v>
       </c>
       <c r="W67">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.233030431305403</v>
+        <v>2.303010261670526</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2297752612358465</v>
+        <v>0.2264998441297999</v>
       </c>
       <c r="C68">
-        <v>717.3410617589532</v>
+        <v>732.1897634501927</v>
       </c>
       <c r="D68">
-        <v>1199.803061758953</v>
+        <v>1214.651763450193</v>
       </c>
       <c r="E68">
         <v>238.7619999999999</v>
@@ -6857,37 +6857,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M68">
-        <v>271.0433169190801</v>
+        <v>262.8073287190801</v>
       </c>
       <c r="N68">
-        <v>325.034234101328</v>
+        <v>333.270222301328</v>
       </c>
       <c r="O68">
-        <v>58.50616213823904</v>
+        <v>59.98864001423905</v>
       </c>
       <c r="P68">
-        <v>266.528071963089</v>
+        <v>273.281582287089</v>
       </c>
       <c r="Q68">
-        <v>354.328071963089</v>
+        <v>361.0815822870891</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.35626483676884</v>
+        <v>0.3563410217510559</v>
       </c>
       <c r="T68">
         <v>1.525803618626451</v>
       </c>
       <c r="U68">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V68">
         <v>0.18</v>
       </c>
       <c r="W68">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.199196636891685</v>
+        <v>2.26811616679673</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2307477807288866</v>
+        <v>0.2274222907117993</v>
       </c>
       <c r="C69">
-        <v>692.5794042030816</v>
+        <v>707.5475481736134</v>
       </c>
       <c r="D69">
-        <v>1195.498404203081</v>
+        <v>1210.466548173614</v>
       </c>
       <c r="E69">
         <v>259.2190000000001</v>
@@ -6939,37 +6939,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M69">
-        <v>275.1500338420965</v>
+        <v>266.7892579420965</v>
       </c>
       <c r="N69">
-        <v>320.9275171783116</v>
+        <v>329.2882930783117</v>
       </c>
       <c r="O69">
-        <v>57.76695309209609</v>
+        <v>59.27189275409609</v>
       </c>
       <c r="P69">
-        <v>263.1605640862156</v>
+        <v>270.0164003242156</v>
       </c>
       <c r="Q69">
-        <v>350.9605640862156</v>
+        <v>357.8164003242156</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.3650194677180432</v>
+        <v>0.3650978009995966</v>
       </c>
       <c r="T69">
         <v>1.56882893421792</v>
       </c>
       <c r="U69">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V69">
         <v>0.18</v>
       </c>
       <c r="W69">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.166372806490316</v>
+        <v>2.234263686695286</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2317203002219268</v>
+        <v>0.2283447372937987</v>
       </c>
       <c r="C70">
-        <v>667.8485247518192</v>
+        <v>682.934075095076</v>
       </c>
       <c r="D70">
-        <v>1191.224524751819</v>
+        <v>1206.310075095076</v>
       </c>
       <c r="E70">
         <v>279.6759999999999</v>
@@ -7021,37 +7021,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M70">
-        <v>279.2567507651128</v>
+        <v>270.7711871651128</v>
       </c>
       <c r="N70">
-        <v>316.8208002552953</v>
+        <v>325.3063638552953</v>
       </c>
       <c r="O70">
-        <v>57.02774404595315</v>
+        <v>58.55514549395315</v>
       </c>
       <c r="P70">
-        <v>259.7930562093421</v>
+        <v>266.7512183613421</v>
       </c>
       <c r="Q70">
-        <v>347.5930562093422</v>
+        <v>354.5512183613422</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.3743212631015716</v>
+        <v>0.3744018789511712</v>
       </c>
       <c r="T70">
         <v>1.614543332033857</v>
       </c>
       <c r="U70">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V70">
         <v>0.18</v>
       </c>
       <c r="W70">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.134514382865459</v>
+        <v>2.201406867773296</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.232692819714967</v>
+        <v>0.2292671838757981</v>
       </c>
       <c r="C71">
-        <v>643.1480944879784</v>
+        <v>658.3490491448249</v>
       </c>
       <c r="D71">
-        <v>1186.981094487978</v>
+        <v>1202.182049144825</v>
       </c>
       <c r="E71">
         <v>300.133</v>
@@ -7103,37 +7103,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M71">
-        <v>283.3634676881292</v>
+        <v>274.7531163881292</v>
       </c>
       <c r="N71">
-        <v>312.7140833322789</v>
+        <v>321.3244346322789</v>
       </c>
       <c r="O71">
-        <v>56.2885349998102</v>
+        <v>57.8383982338102</v>
       </c>
       <c r="P71">
-        <v>256.4255483324687</v>
+        <v>263.4860363984687</v>
       </c>
       <c r="Q71">
-        <v>344.2255483324687</v>
+        <v>351.2860363984688</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.3842231743162954</v>
+        <v>0.3843062199963958</v>
       </c>
       <c r="T71">
         <v>1.663207045837918</v>
       </c>
       <c r="U71">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V71">
         <v>0.18</v>
       </c>
       <c r="W71">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.103579391809438</v>
+        <v>2.169502420414263</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2336653392080072</v>
+        <v>0.2301896304577976</v>
       </c>
       <c r="C72">
-        <v>618.4777891644649</v>
+        <v>633.7921792782777</v>
       </c>
       <c r="D72">
-        <v>1182.767789164465</v>
+        <v>1198.082179278278</v>
       </c>
       <c r="E72">
         <v>320.5900000000001</v>
@@ -7185,37 +7185,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M72">
-        <v>287.4701846111456</v>
+        <v>278.7350456111456</v>
       </c>
       <c r="N72">
-        <v>308.6073664092625</v>
+        <v>317.3425054092625</v>
       </c>
       <c r="O72">
-        <v>55.54932595366725</v>
+        <v>57.12165097366725</v>
       </c>
       <c r="P72">
-        <v>253.0580404555953</v>
+        <v>260.2208544355952</v>
       </c>
       <c r="Q72">
-        <v>340.8580404555953</v>
+        <v>348.0208544355953</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.394785212945334</v>
+        <v>0.3948708504446352</v>
       </c>
       <c r="T72">
         <v>1.715115007228916</v>
       </c>
       <c r="U72">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V72">
         <v>0.18</v>
       </c>
       <c r="W72">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.073528257640731</v>
+        <v>2.138509528694059</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2346378587010474</v>
+        <v>0.231112077039797</v>
       </c>
       <c r="C73">
-        <v>593.8372891216886</v>
+        <v>609.2631784076232</v>
       </c>
       <c r="D73">
-        <v>1178.584289121688</v>
+        <v>1194.010178407623</v>
       </c>
       <c r="E73">
         <v>341.0469999999998</v>
@@ -7267,37 +7267,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M73">
-        <v>291.5769015341619</v>
+        <v>282.7169748341619</v>
       </c>
       <c r="N73">
-        <v>304.5006494862462</v>
+        <v>313.3605761862462</v>
       </c>
       <c r="O73">
-        <v>54.81011690752432</v>
+        <v>56.40490371352432</v>
       </c>
       <c r="P73">
-        <v>249.6905325787219</v>
+        <v>256.9556724727219</v>
       </c>
       <c r="Q73">
-        <v>337.490532578722</v>
+        <v>344.755672472722</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.4060756680315478</v>
+        <v>0.4061640760962015</v>
       </c>
       <c r="T73">
         <v>1.77060282802619</v>
       </c>
       <c r="U73">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V73">
         <v>0.18</v>
       </c>
       <c r="W73">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.044323634293679</v>
+        <v>2.108389676177242</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2356103781940875</v>
+        <v>0.2320345236217964</v>
       </c>
       <c r="C74">
-        <v>569.2262792067158</v>
+        <v>584.7617633348041</v>
       </c>
       <c r="D74">
-        <v>1174.430279206716</v>
+        <v>1189.965763334804</v>
       </c>
       <c r="E74">
         <v>361.5039999999999</v>
@@ -7349,37 +7349,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M74">
-        <v>295.6836184571783</v>
+        <v>286.6989040571783</v>
       </c>
       <c r="N74">
-        <v>300.3939325632298</v>
+        <v>309.3786469632299</v>
       </c>
       <c r="O74">
-        <v>54.07090786138137</v>
+        <v>55.68815645338137</v>
       </c>
       <c r="P74">
-        <v>246.3230247018485</v>
+        <v>253.6904905098485</v>
       </c>
       <c r="Q74">
-        <v>334.1230247018485</v>
+        <v>341.4904905098485</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.4181725841953481</v>
+        <v>0.4182639607228797</v>
       </c>
       <c r="T74">
         <v>1.830054064594698</v>
       </c>
       <c r="U74">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V74">
         <v>0.18</v>
       </c>
       <c r="W74">
-        <v>0.1646139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.015930250484045</v>
+        <v>2.079106486230336</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2463400776871277</v>
+        <v>0.2329569702037958</v>
       </c>
       <c r="C75">
-        <v>504.8095139912596</v>
+        <v>560.2876546858658</v>
       </c>
       <c r="D75">
-        <v>1130.47051399126</v>
+        <v>1185.948654685866</v>
       </c>
       <c r="E75">
         <v>381.961</v>
@@ -7431,45 +7431,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M75">
-        <v>324.1321196801946</v>
+        <v>290.6808332801947</v>
       </c>
       <c r="N75">
-        <v>271.9454313402135</v>
+        <v>305.3967177402134</v>
       </c>
       <c r="O75">
-        <v>48.95017764123843</v>
+        <v>54.97140919323842</v>
       </c>
       <c r="P75">
-        <v>222.995253698975</v>
+        <v>250.425308546975</v>
       </c>
       <c r="Q75">
-        <v>310.7952536989751</v>
+        <v>338.2253085469751</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.4311655682231338</v>
+        <v>0.4312601330996823</v>
       </c>
       <c r="T75">
         <v>1.893909096464577</v>
       </c>
       <c r="U75">
-        <v>0.2170487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V75">
         <v>0.18</v>
       </c>
       <c r="W75">
-        <v>0.1779799647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.838995628105381</v>
+        <v>2.050625575460057</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2474462571801679</v>
+        <v>0.2338794167857952</v>
       </c>
       <c r="C76">
-        <v>480.0068842158487</v>
+        <v>535.8405768466257</v>
       </c>
       <c r="D76">
-        <v>1126.124884215849</v>
+        <v>1181.958576846626</v>
       </c>
       <c r="E76">
         <v>402.4179999999999</v>
@@ -7513,45 +7513,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M76">
-        <v>328.572285703211</v>
+        <v>294.662762503211</v>
       </c>
       <c r="N76">
-        <v>267.5052653171971</v>
+        <v>301.4147885171971</v>
       </c>
       <c r="O76">
-        <v>48.15094775709547</v>
+        <v>54.25466193309548</v>
       </c>
       <c r="P76">
-        <v>219.3543175601016</v>
+        <v>247.1601265841016</v>
       </c>
       <c r="Q76">
-        <v>307.1543175601017</v>
+        <v>334.9601265841017</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.4451580125607492</v>
+        <v>0.4452560110439312</v>
       </c>
       <c r="T76">
         <v>1.962676053862908</v>
       </c>
       <c r="U76">
-        <v>0.2170487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V76">
         <v>0.18</v>
       </c>
       <c r="W76">
-        <v>0.1779799647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.814144335833687</v>
+        <v>2.022914419034922</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2485524366732081</v>
+        <v>0.2435348633677947</v>
       </c>
       <c r="C77">
-        <v>455.2375364804379</v>
+        <v>475.17509486727</v>
       </c>
       <c r="D77">
-        <v>1121.812536480438</v>
+        <v>1141.75009486727</v>
       </c>
       <c r="E77">
         <v>422.875</v>
@@ -7595,37 +7595,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M77">
-        <v>333.0124517262274</v>
+        <v>320.4313967262274</v>
       </c>
       <c r="N77">
-        <v>263.0650992941807</v>
+        <v>275.6461542941807</v>
       </c>
       <c r="O77">
-        <v>47.35171787295253</v>
+        <v>49.61630777295252</v>
       </c>
       <c r="P77">
-        <v>215.7133814212282</v>
+        <v>226.0298465212282</v>
       </c>
       <c r="Q77">
-        <v>303.5133814212282</v>
+        <v>313.8298465212282</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.4602698524453738</v>
+        <v>0.46037155922372</v>
       </c>
       <c r="T77">
         <v>2.036944367853106</v>
       </c>
       <c r="U77">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V77">
         <v>0.18</v>
       </c>
       <c r="W77">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.789955744689237</v>
+        <v>1.860234537284401</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2496586161662482</v>
+        <v>0.2445737499497941</v>
       </c>
       <c r="C78">
-        <v>430.5010898959547</v>
+        <v>450.5542405828726</v>
       </c>
       <c r="D78">
-        <v>1117.533089895955</v>
+        <v>1137.586240582873</v>
       </c>
       <c r="E78">
         <v>443.3319999999999</v>
@@ -7677,37 +7677,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M78">
-        <v>337.4526177492438</v>
+        <v>324.7038153492438</v>
       </c>
       <c r="N78">
-        <v>258.6249332711644</v>
+        <v>271.3737356711644</v>
       </c>
       <c r="O78">
-        <v>46.55248798880958</v>
+        <v>48.84727242080958</v>
       </c>
       <c r="P78">
-        <v>212.0724452823548</v>
+        <v>222.5264632503548</v>
       </c>
       <c r="Q78">
-        <v>299.8724452823549</v>
+        <v>310.3264632503548</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.4766410123203838</v>
+        <v>0.4767467364184913</v>
       </c>
       <c r="T78">
         <v>2.117401708009154</v>
       </c>
       <c r="U78">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V78">
         <v>0.18</v>
       </c>
       <c r="W78">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.766403695417011</v>
+        <v>1.835757767056975</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2507647956592884</v>
+        <v>0.2456126365317935</v>
       </c>
       <c r="C79">
-        <v>405.797169363241</v>
+        <v>425.9636463062434</v>
       </c>
       <c r="D79">
-        <v>1113.286169363241</v>
+        <v>1133.452646306243</v>
       </c>
       <c r="E79">
         <v>463.789</v>
@@ -7759,37 +7759,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M79">
-        <v>341.8927837722601</v>
+        <v>328.9762339722602</v>
       </c>
       <c r="N79">
-        <v>254.184767248148</v>
+        <v>267.101317048148</v>
       </c>
       <c r="O79">
-        <v>45.75325810466664</v>
+        <v>48.07823706866663</v>
       </c>
       <c r="P79">
-        <v>208.4315091434813</v>
+        <v>219.0230799794813</v>
       </c>
       <c r="Q79">
-        <v>296.2315091434814</v>
+        <v>306.8230799794814</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.4944357513149598</v>
+        <v>0.4945458420649818</v>
       </c>
       <c r="T79">
         <v>2.204855338613553</v>
       </c>
       <c r="U79">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V79">
         <v>0.18</v>
       </c>
       <c r="W79">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.743463387684322</v>
+        <v>1.811916757095196</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2518709751523286</v>
+        <v>0.2466515231137929</v>
       </c>
       <c r="C80">
-        <v>381.1254054634564</v>
+        <v>401.4029833684981</v>
       </c>
       <c r="D80">
-        <v>1109.071405463457</v>
+        <v>1129.348983368498</v>
       </c>
       <c r="E80">
         <v>484.2460000000001</v>
@@ -7841,37 +7841,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M80">
-        <v>346.3329497952765</v>
+        <v>333.2486525952766</v>
       </c>
       <c r="N80">
-        <v>249.7446012251316</v>
+        <v>262.8288984251316</v>
       </c>
       <c r="O80">
-        <v>44.95402822052368</v>
+        <v>47.30920171652368</v>
       </c>
       <c r="P80">
-        <v>204.7905730046079</v>
+        <v>215.5196967086079</v>
       </c>
       <c r="Q80">
-        <v>292.590573004608</v>
+        <v>303.3196967086079</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.5138481938544972</v>
+        <v>0.5139630482247896</v>
       </c>
       <c r="T80">
         <v>2.300259299272899</v>
       </c>
       <c r="U80">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V80">
         <v>0.18</v>
       </c>
       <c r="W80">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.72111129297042</v>
+        <v>1.788687055081155</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2529771546453688</v>
+        <v>0.2476904096957923</v>
       </c>
       <c r="C81">
-        <v>356.4854343509567</v>
+        <v>376.8719278433614</v>
       </c>
       <c r="D81">
-        <v>1104.888434350957</v>
+        <v>1125.274927843361</v>
       </c>
       <c r="E81">
         <v>504.703</v>
@@ -7923,37 +7923,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M81">
-        <v>350.7731158182929</v>
+        <v>337.5210712182929</v>
       </c>
       <c r="N81">
-        <v>245.3044352021153</v>
+        <v>258.5564798021152</v>
       </c>
       <c r="O81">
-        <v>44.15479833638074</v>
+        <v>46.54016636438074</v>
       </c>
       <c r="P81">
-        <v>201.1496368657345</v>
+        <v>212.0163134377345</v>
       </c>
       <c r="Q81">
-        <v>288.9496368657346</v>
+        <v>299.8163134377346</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.5351094404454193</v>
+        <v>0.5352295121141029</v>
       </c>
       <c r="T81">
         <v>2.40474935142361</v>
       </c>
       <c r="U81">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V81">
         <v>0.18</v>
       </c>
       <c r="W81">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.699325074072061</v>
+        <v>1.766045446788989</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2540833341384089</v>
+        <v>0.2487292962777918</v>
       </c>
       <c r="C82">
-        <v>331.8768976485903</v>
+        <v>352.3701604619314</v>
       </c>
       <c r="D82">
-        <v>1100.73689764859</v>
+        <v>1121.230160461932</v>
       </c>
       <c r="E82">
         <v>525.1600000000001</v>
@@ -8005,37 +8005,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M82">
-        <v>355.2132818413093</v>
+        <v>341.7934898413093</v>
       </c>
       <c r="N82">
-        <v>240.8642691790989</v>
+        <v>254.2840611790988</v>
       </c>
       <c r="O82">
-        <v>43.3555684522378</v>
+        <v>45.77113101223779</v>
       </c>
       <c r="P82">
-        <v>197.5087007268611</v>
+        <v>208.5129301668611</v>
       </c>
       <c r="Q82">
-        <v>285.3087007268612</v>
+        <v>296.3129301668611</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.5584968116954335</v>
+        <v>0.5586226223923474</v>
       </c>
       <c r="T82">
         <v>2.519688408789392</v>
       </c>
       <c r="U82">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V82">
         <v>0.18</v>
       </c>
       <c r="W82">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.67808351064616</v>
+        <v>1.743969878704126</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2551895136314491</v>
+        <v>0.2497681828597912</v>
       </c>
       <c r="C83">
-        <v>307.2994423453454</v>
+        <v>327.8973665292765</v>
       </c>
       <c r="D83">
-        <v>1096.616442345345</v>
+        <v>1117.214366529277</v>
       </c>
       <c r="E83">
         <v>545.617</v>
@@ -8087,37 +8087,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M83">
-        <v>359.6534478643256</v>
+        <v>346.0659084643256</v>
       </c>
       <c r="N83">
-        <v>236.4241031560825</v>
+        <v>250.0116425560825</v>
       </c>
       <c r="O83">
-        <v>42.55633856809486</v>
+        <v>45.00209566009485</v>
       </c>
       <c r="P83">
-        <v>193.8677645879877</v>
+        <v>205.0095468959877</v>
       </c>
       <c r="Q83">
-        <v>281.6677645879877</v>
+        <v>292.8095468959878</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.5843460114980809</v>
+        <v>0.5844781653314599</v>
       </c>
       <c r="T83">
         <v>2.646726314298941</v>
       </c>
       <c r="U83">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V83">
         <v>0.18</v>
       </c>
       <c r="W83">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.657366430267813</v>
+        <v>1.722439386374446</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2562956931244893</v>
+        <v>0.2508070694417906</v>
       </c>
       <c r="C84">
-        <v>282.7527206962884</v>
+        <v>303.4532358428146</v>
       </c>
       <c r="D84">
-        <v>1092.526720696289</v>
+        <v>1113.227235842815</v>
       </c>
       <c r="E84">
         <v>566.0740000000001</v>
@@ -8169,37 +8169,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M84">
-        <v>364.093613887342</v>
+        <v>350.338327087342</v>
       </c>
       <c r="N84">
-        <v>231.9839371330661</v>
+        <v>245.7392239330661</v>
       </c>
       <c r="O84">
-        <v>41.75710868395191</v>
+        <v>44.2330603079519</v>
       </c>
       <c r="P84">
-        <v>190.2268284491142</v>
+        <v>201.5061636251142</v>
       </c>
       <c r="Q84">
-        <v>278.0268284491143</v>
+        <v>289.3061636251143</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.6130673446121333</v>
+        <v>0.6132065463749181</v>
       </c>
       <c r="T84">
         <v>2.787879542642884</v>
       </c>
       <c r="U84">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V84">
         <v>0.18</v>
       </c>
       <c r="W84">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.637154644532839</v>
+        <v>1.701434028004026</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2574018726175295</v>
+        <v>0.25184595602379</v>
       </c>
       <c r="C85">
-        <v>258.2363901247297</v>
+        <v>279.0374626124399</v>
       </c>
       <c r="D85">
-        <v>1088.46739012473</v>
+        <v>1109.26846261244</v>
       </c>
       <c r="E85">
         <v>586.5310000000002</v>
@@ -8251,37 +8251,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M85">
-        <v>368.5337799103584</v>
+        <v>354.6107457103584</v>
       </c>
       <c r="N85">
-        <v>227.5437711100498</v>
+        <v>241.4668053100497</v>
       </c>
       <c r="O85">
-        <v>40.95787879980895</v>
+        <v>43.46402495580895</v>
       </c>
       <c r="P85">
-        <v>186.5858923102408</v>
+        <v>198.0027803542408</v>
       </c>
       <c r="Q85">
-        <v>274.3858923102409</v>
+        <v>285.8027803542408</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.6451676580925452</v>
+        <v>0.645314736952901</v>
       </c>
       <c r="T85">
         <v>2.945639033144939</v>
       </c>
       <c r="U85">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V85">
         <v>0.18</v>
       </c>
       <c r="W85">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.617429889779431</v>
+        <v>1.68093482284735</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2585080521105697</v>
+        <v>0.2528848426057894</v>
       </c>
       <c r="C86">
-        <v>233.7501131265694</v>
+        <v>254.6497453823415</v>
       </c>
       <c r="D86">
-        <v>1084.438113126569</v>
+        <v>1105.337745382341</v>
       </c>
       <c r="E86">
         <v>606.9879999999998</v>
@@ -8333,37 +8333,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M86">
-        <v>372.9739459333746</v>
+        <v>358.8831643333747</v>
       </c>
       <c r="N86">
-        <v>223.1036050870335</v>
+        <v>237.1943866870334</v>
       </c>
       <c r="O86">
-        <v>40.15864891566603</v>
+        <v>42.69498960366602</v>
       </c>
       <c r="P86">
-        <v>182.9449561713675</v>
+        <v>194.4993970833674</v>
       </c>
       <c r="Q86">
-        <v>270.7449561713676</v>
+        <v>282.2993970833675</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.6812805107580079</v>
+        <v>0.6814364513531314</v>
       </c>
       <c r="T86">
         <v>3.123118459959748</v>
       </c>
       <c r="U86">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V86">
         <v>0.18</v>
       </c>
       <c r="W86">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.598174772043962</v>
+        <v>1.66092369400393</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2596142316036099</v>
+        <v>0.2539237291877888</v>
       </c>
       <c r="C87">
-        <v>209.2935571767491</v>
+        <v>230.289786954482</v>
       </c>
       <c r="D87">
-        <v>1080.438557176749</v>
+        <v>1101.434786954482</v>
       </c>
       <c r="E87">
         <v>627.4449999999999</v>
@@ -8415,37 +8415,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M87">
-        <v>377.414111956391</v>
+        <v>363.1555829563911</v>
       </c>
       <c r="N87">
-        <v>218.6634390640171</v>
+        <v>232.9219680640171</v>
       </c>
       <c r="O87">
-        <v>39.35941903152307</v>
+        <v>41.92595425152307</v>
       </c>
       <c r="P87">
-        <v>179.304020032494</v>
+        <v>190.996013812494</v>
       </c>
       <c r="Q87">
-        <v>267.1040200324941</v>
+        <v>278.796013812494</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.7222084104455327</v>
+        <v>0.7223743943400593</v>
       </c>
       <c r="T87">
         <v>3.324261810349867</v>
       </c>
       <c r="U87">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V87">
         <v>0.18</v>
       </c>
       <c r="W87">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.579372715902268</v>
+        <v>1.641383415250942</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.26072041109665</v>
+        <v>0.2549626157697883</v>
       </c>
       <c r="C88">
-        <v>184.866394637779</v>
+        <v>205.9572943136914</v>
       </c>
       <c r="D88">
-        <v>1076.468394637779</v>
+        <v>1097.559294313691</v>
       </c>
       <c r="E88">
         <v>647.9019999999998</v>
@@ -8497,37 +8497,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M88">
-        <v>381.8542779794074</v>
+        <v>367.4280015794074</v>
       </c>
       <c r="N88">
-        <v>214.2232730410008</v>
+        <v>228.6495494410007</v>
       </c>
       <c r="O88">
-        <v>38.56018914738014</v>
+        <v>41.15691889938013</v>
       </c>
       <c r="P88">
-        <v>175.6630838936206</v>
+        <v>187.4926305416206</v>
       </c>
       <c r="Q88">
-        <v>263.4630838936207</v>
+        <v>275.2926305416207</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.7689831529455613</v>
+        <v>0.7691606148965486</v>
       </c>
       <c r="T88">
         <v>3.554139925081432</v>
       </c>
       <c r="U88">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V88">
         <v>0.18</v>
       </c>
       <c r="W88">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.561007916880149</v>
+        <v>1.622297561585234</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2618265905896902</v>
+        <v>0.2560015023517876</v>
       </c>
       <c r="C89">
-        <v>160.4683026702626</v>
+        <v>181.6519785543362</v>
       </c>
       <c r="D89">
-        <v>1072.527302670263</v>
+        <v>1093.710978554336</v>
       </c>
       <c r="E89">
         <v>668.3589999999999</v>
@@ -8579,37 +8579,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M89">
-        <v>386.2944440024237</v>
+        <v>371.7004202024238</v>
       </c>
       <c r="N89">
-        <v>209.7831070179844</v>
+        <v>224.3771308179843</v>
       </c>
       <c r="O89">
-        <v>37.76095926323719</v>
+        <v>40.38788354723717</v>
       </c>
       <c r="P89">
-        <v>172.0221477547472</v>
+        <v>183.9892472707471</v>
       </c>
       <c r="Q89">
-        <v>259.8221477547472</v>
+        <v>271.7892472707472</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.8229540096763631</v>
+        <v>0.8231447155386514</v>
       </c>
       <c r="T89">
         <v>3.819383903617851</v>
       </c>
       <c r="U89">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V89">
         <v>0.18</v>
       </c>
       <c r="W89">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.543065297145894</v>
+        <v>1.603650463176208</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2629327700827304</v>
+        <v>0.2570403889337871</v>
       </c>
       <c r="C90">
-        <v>136.0989631453874</v>
+        <v>157.3735548085244</v>
       </c>
       <c r="D90">
-        <v>1068.614963145387</v>
+        <v>1089.889554808525</v>
       </c>
       <c r="E90">
         <v>688.816</v>
@@ -8661,37 +8661,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M90">
-        <v>390.7346100254401</v>
+        <v>375.9728388254402</v>
       </c>
       <c r="N90">
-        <v>205.342940994968</v>
+        <v>220.1047121949679</v>
       </c>
       <c r="O90">
-        <v>36.96172937909424</v>
+        <v>39.61884819509422</v>
       </c>
       <c r="P90">
-        <v>168.3812116158738</v>
+        <v>180.4858639998737</v>
       </c>
       <c r="Q90">
-        <v>256.1812116158738</v>
+        <v>268.2858639998738</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.8859200091956324</v>
+        <v>0.8861261662877716</v>
       </c>
       <c r="T90">
         <v>4.128835211910343</v>
       </c>
       <c r="U90">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V90">
         <v>0.18</v>
       </c>
       <c r="W90">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.525530464223782</v>
+        <v>1.585427162458297</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2640389495757706</v>
+        <v>0.2580792755157865</v>
       </c>
       <c r="C91">
-        <v>111.7580625593212</v>
+        <v>133.1217421758147</v>
       </c>
       <c r="D91">
-        <v>1064.731062559321</v>
+        <v>1086.094742175815</v>
       </c>
       <c r="E91">
         <v>709.2729999999999</v>
@@ -8743,37 +8743,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M91">
-        <v>395.1747760484565</v>
+        <v>380.2452574484565</v>
       </c>
       <c r="N91">
-        <v>200.9027749719517</v>
+        <v>215.8322935719516</v>
       </c>
       <c r="O91">
-        <v>36.1624994949513</v>
+        <v>38.84981284295129</v>
       </c>
       <c r="P91">
-        <v>164.7402754770004</v>
+        <v>176.9824807290003</v>
       </c>
       <c r="Q91">
-        <v>252.5402754770004</v>
+        <v>264.7824807290004</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.9603343722638594</v>
+        <v>0.9605587899003681</v>
       </c>
       <c r="T91">
         <v>4.494550394437832</v>
       </c>
       <c r="U91">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V91">
         <v>0.18</v>
       </c>
       <c r="W91">
-        <v>0.1779799647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.508389672490931</v>
+        <v>1.567613374116068</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2892777290688107</v>
+        <v>0.2591181620977859</v>
       </c>
       <c r="C92">
-        <v>9.768549378442458</v>
+        <v>108.8962636543822</v>
       </c>
       <c r="D92">
-        <v>983.1985493784426</v>
+        <v>1082.326263654382</v>
       </c>
       <c r="E92">
         <v>729.73</v>
@@ -8825,45 +8825,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M92">
-        <v>459.8198930714729</v>
+        <v>384.5176760714729</v>
       </c>
       <c r="N92">
-        <v>136.2576579489352</v>
+        <v>211.5598749489352</v>
       </c>
       <c r="O92">
-        <v>24.52637843080834</v>
+        <v>38.08077749080834</v>
       </c>
       <c r="P92">
-        <v>111.7312795181269</v>
+        <v>173.4790974581269</v>
       </c>
       <c r="Q92">
-        <v>199.531279518127</v>
+        <v>261.2790974581269</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>1.049631607945732</v>
+        <v>1.049877938235484</v>
       </c>
       <c r="T92">
         <v>4.933408613470819</v>
       </c>
       <c r="U92">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V92">
         <v>0.18</v>
       </c>
       <c r="W92">
-        <v>0.2047939647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.296328323332796</v>
+        <v>1.550195447737001</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2906520485618509</v>
+        <v>0.2601570486797854</v>
       </c>
       <c r="C93">
-        <v>-14.77112135756624</v>
+        <v>84.69684607361955</v>
       </c>
       <c r="D93">
-        <v>979.1158786424339</v>
+        <v>1078.58384607362</v>
       </c>
       <c r="E93">
         <v>750.1870000000001</v>
@@ -8907,45 +8907,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M93">
-        <v>464.9290029944893</v>
+        <v>388.7900946944893</v>
       </c>
       <c r="N93">
-        <v>131.1485480259188</v>
+        <v>207.2874563259188</v>
       </c>
       <c r="O93">
-        <v>23.60673864466539</v>
+        <v>37.31174213866539</v>
       </c>
       <c r="P93">
-        <v>107.5418093812534</v>
+        <v>169.9757141872534</v>
       </c>
       <c r="Q93">
-        <v>195.3418093812535</v>
+        <v>257.7757141872535</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>1.158772673779132</v>
+        <v>1.159045786200626</v>
       </c>
       <c r="T93">
         <v>5.469790881177803</v>
       </c>
       <c r="U93">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V93">
         <v>0.18</v>
       </c>
       <c r="W93">
-        <v>0.2047939647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.282082957142326</v>
+        <v>1.533160332926704</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2920263680548911</v>
+        <v>0.2611959352617848</v>
       </c>
       <c r="C94">
-        <v>-39.27702623234109</v>
+        <v>60.5232200281273</v>
       </c>
       <c r="D94">
-        <v>975.066973767659</v>
+        <v>1074.867220028127</v>
       </c>
       <c r="E94">
         <v>770.644</v>
@@ -8989,45 +8989,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M94">
-        <v>470.0381129175056</v>
+        <v>393.0625133175056</v>
       </c>
       <c r="N94">
-        <v>126.0394381029025</v>
+        <v>203.0150377029025</v>
       </c>
       <c r="O94">
-        <v>22.68709885852245</v>
+        <v>36.54270678652244</v>
       </c>
       <c r="P94">
-        <v>103.3523392443801</v>
+        <v>166.47233091638</v>
       </c>
       <c r="Q94">
-        <v>191.1523392443801</v>
+        <v>254.2723309163801</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.295199006070882</v>
+        <v>1.295505596157053</v>
       </c>
       <c r="T94">
         <v>6.140268715811535</v>
       </c>
       <c r="U94">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V94">
         <v>0.18</v>
       </c>
       <c r="W94">
-        <v>0.2047939647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.268147272825562</v>
+        <v>1.51649554669924</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2934006875479313</v>
+        <v>0.2622348218437842</v>
       </c>
       <c r="C95">
-        <v>-63.74958241326567</v>
+        <v>36.37511981306329</v>
       </c>
       <c r="D95">
-        <v>971.0514175867346</v>
+        <v>1071.176119813063</v>
       </c>
       <c r="E95">
         <v>791.1010000000001</v>
@@ -9071,45 +9071,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M95">
-        <v>475.147222840522</v>
+        <v>397.334931940522</v>
       </c>
       <c r="N95">
-        <v>120.9303281798861</v>
+        <v>198.7426190798861</v>
       </c>
       <c r="O95">
-        <v>21.76745907237949</v>
+        <v>35.77367143437949</v>
       </c>
       <c r="P95">
-        <v>99.16286910750659</v>
+        <v>162.9689476455066</v>
       </c>
       <c r="Q95">
-        <v>186.9628691075067</v>
+        <v>250.7689476455067</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.470604290445989</v>
+        <v>1.470953923243888</v>
       </c>
       <c r="T95">
         <v>7.002311646054904</v>
       </c>
       <c r="U95">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V95">
         <v>0.18</v>
       </c>
       <c r="W95">
-        <v>0.2047939647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.254511280644641</v>
+        <v>1.500189142971291</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3199801670409715</v>
+        <v>0.2853185884257836</v>
       </c>
       <c r="C96">
-        <v>-155.8424334700248</v>
+        <v>-60.0210827940432</v>
       </c>
       <c r="D96">
-        <v>899.4155665299753</v>
+        <v>995.2369172059567</v>
       </c>
       <c r="E96">
         <v>811.558</v>
@@ -9153,45 +9153,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M96">
-        <v>543.1370593635384</v>
+        <v>456.6039493635383</v>
       </c>
       <c r="N96">
-        <v>52.94049165686977</v>
+        <v>139.4736016568698</v>
       </c>
       <c r="O96">
-        <v>9.529288498236557</v>
+        <v>25.10524829823656</v>
       </c>
       <c r="P96">
-        <v>43.41120315863321</v>
+        <v>114.3683533586332</v>
       </c>
       <c r="Q96">
-        <v>131.2112031586333</v>
+        <v>202.1683533586333</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.704478002946131</v>
+        <v>1.704885026026334</v>
       </c>
       <c r="T96">
         <v>8.151702219712728</v>
       </c>
       <c r="U96">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V96">
         <v>0.18</v>
       </c>
       <c r="W96">
-        <v>0.2316079647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.097471698430792</v>
+        <v>1.305458596780169</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3216226265340117</v>
+        <v>0.2865919950077831</v>
       </c>
       <c r="C97">
-        <v>-180.380949396492</v>
+        <v>-84.35509276215566</v>
       </c>
       <c r="D97">
-        <v>895.3340506035082</v>
+        <v>991.3599072378444</v>
       </c>
       <c r="E97">
         <v>832.0150000000001</v>
@@ -9235,45 +9235,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M97">
-        <v>548.9151131865548</v>
+        <v>461.4614381865547</v>
       </c>
       <c r="N97">
-        <v>47.16243783385335</v>
+        <v>134.6161128338534</v>
       </c>
       <c r="O97">
-        <v>8.489238810093601</v>
+        <v>24.23090031009361</v>
       </c>
       <c r="P97">
-        <v>38.67319902375974</v>
+        <v>110.3852125237598</v>
       </c>
       <c r="Q97">
-        <v>126.4731990237598</v>
+        <v>198.1852125237598</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>2.031901200446332</v>
+        <v>2.03238856992176</v>
       </c>
       <c r="T97">
         <v>9.760849022833687</v>
       </c>
       <c r="U97">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V97">
         <v>0.18</v>
       </c>
       <c r="W97">
-        <v>0.2316079647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.085919364763099</v>
+        <v>1.291716927340378</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.3232650860270518</v>
+        <v>0.2878654015897825</v>
       </c>
       <c r="C98">
-        <v>-204.8825891169774</v>
+        <v>-108.6590136565717</v>
       </c>
       <c r="D98">
-        <v>891.2894108830225</v>
+        <v>987.5129863434283</v>
       </c>
       <c r="E98">
         <v>852.472</v>
@@ -9317,45 +9317,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M98">
-        <v>554.6931670095711</v>
+        <v>466.318927009571</v>
       </c>
       <c r="N98">
-        <v>41.38438401083704</v>
+        <v>129.7586240108371</v>
       </c>
       <c r="O98">
-        <v>7.449189121950667</v>
+        <v>23.35655232195067</v>
       </c>
       <c r="P98">
-        <v>33.93519488888637</v>
+        <v>106.4020716888864</v>
       </c>
       <c r="Q98">
-        <v>121.7351948888864</v>
+        <v>194.2020716888865</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.523035996696625</v>
+        <v>2.523643885764892</v>
       </c>
       <c r="T98">
         <v>12.17456922751509</v>
       </c>
       <c r="U98">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V98">
         <v>0.18</v>
       </c>
       <c r="W98">
-        <v>0.2316079647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.074607704713483</v>
+        <v>1.278261542680582</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.324907545520092</v>
+        <v>0.2891388081717819</v>
       </c>
       <c r="C99">
-        <v>-229.3478501448287</v>
+        <v>-132.9331944005996</v>
       </c>
       <c r="D99">
-        <v>887.2811498551711</v>
+        <v>983.6958055994004</v>
       </c>
       <c r="E99">
         <v>872.9289999999999</v>
@@ -9399,45 +9399,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M99">
-        <v>560.4712208325874</v>
+        <v>471.1764158325874</v>
       </c>
       <c r="N99">
-        <v>35.60633018782073</v>
+        <v>124.9011351878207</v>
       </c>
       <c r="O99">
-        <v>6.409139433807732</v>
+        <v>22.48220433380773</v>
       </c>
       <c r="P99">
-        <v>29.197190754013</v>
+        <v>102.418930854013</v>
       </c>
       <c r="Q99">
-        <v>116.9971907540131</v>
+        <v>190.2189308540131</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>3.341593990447122</v>
+        <v>3.342402745503452</v>
       </c>
       <c r="T99">
         <v>16.19743623531746</v>
       </c>
       <c r="U99">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V99">
         <v>0.18</v>
       </c>
       <c r="W99">
-        <v>0.2316079647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.063529274767984</v>
+        <v>1.265083588632329</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3265500050131321</v>
+        <v>0.2904122147537813</v>
       </c>
       <c r="C100">
-        <v>-253.7772210838946</v>
+        <v>-157.1779785433409</v>
       </c>
       <c r="D100">
-        <v>883.3087789161054</v>
+        <v>979.908021456659</v>
       </c>
       <c r="E100">
         <v>893.386</v>
@@ -9481,45 +9481,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M100">
-        <v>566.2492746556038</v>
+        <v>476.0339046556038</v>
       </c>
       <c r="N100">
-        <v>29.82827636480431</v>
+        <v>120.0436463648043</v>
       </c>
       <c r="O100">
-        <v>5.369089745664776</v>
+        <v>21.60785634566477</v>
       </c>
       <c r="P100">
-        <v>24.45918661913953</v>
+        <v>98.43579001913955</v>
       </c>
       <c r="Q100">
-        <v>112.2591866191396</v>
+        <v>186.2357900191396</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>4.978709977948115</v>
+        <v>4.979920464980571</v>
       </c>
       <c r="T100">
         <v>24.24317025092221</v>
       </c>
       <c r="U100">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V100">
         <v>0.18</v>
       </c>
       <c r="W100">
-        <v>0.2316079647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.052676935229535</v>
+        <v>1.252174572421795</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3281924645061723</v>
+        <v>0.3145783813357807</v>
       </c>
       <c r="C101">
-        <v>-278.1711818270744</v>
+        <v>-244.3648929030851</v>
       </c>
       <c r="D101">
-        <v>879.3718181729255</v>
+        <v>913.1781070969149</v>
       </c>
       <c r="E101">
         <v>913.8429999999998</v>
@@ -9563,37 +9563,37 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M101">
-        <v>572.0273284786201</v>
+        <v>538.0032460786201</v>
       </c>
       <c r="N101">
-        <v>24.050222541788</v>
+        <v>58.074304941788</v>
       </c>
       <c r="O101">
-        <v>4.329040057521841</v>
+        <v>10.45337488952184</v>
       </c>
       <c r="P101">
-        <v>19.72118248426616</v>
+        <v>47.62093005226616</v>
       </c>
       <c r="Q101">
-        <v>107.5211824842662</v>
+        <v>135.4209300522662</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>9.890057940451095</v>
+        <v>9.892473623411933</v>
       </c>
       <c r="T101">
         <v>48.38037229773646</v>
       </c>
       <c r="U101">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V101">
         <v>0.18</v>
       </c>
       <c r="W101">
-        <v>0.2316079647491529</v>
+        <v>0.2178319647491528</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>1.042043834873681</v>
+        <v>1.107944153432304</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ukraine/ukraine_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/ukraine/ukraine_farming_agriculture.xlsx
@@ -1127,43 +1127,43 @@
         <v>5.93075356415479</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>172.263021427899</v>
       </c>
       <c r="G2">
         <v>1.65831095195464</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0305237242614145</v>
       </c>
       <c r="I2">
         <v>0.5432859168010949</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>934.3</v>
       </c>
       <c r="L2">
-        <v>2441.48365817095</v>
+        <v>2415.59339536041</v>
       </c>
       <c r="M2">
         <v>1178</v>
       </c>
       <c r="N2">
-        <v>1573.78365817095</v>
+        <v>1568.35039536041</v>
       </c>
       <c r="O2">
         <v>1111.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>20.457</v>
       </c>
       <c r="Q2">
         <v>0.234800755954049</v>
       </c>
       <c r="R2">
-        <v>0.165618369717838</v>
+        <v>0.166331716299838</v>
       </c>
       <c r="S2">
         <v>0.194707964749153</v>
@@ -1185,13 +1185,13 @@
         <v>0.282493283134955</v>
       </c>
       <c r="X2">
-        <v>0.165618369717838</v>
+        <v>0.166610804699339</v>
       </c>
       <c r="Y2">
         <v>1.16296219377227</v>
       </c>
       <c r="Z2">
-        <v>0.58871224504425</v>
+        <v>0.59358844747795</v>
       </c>
       <c r="AA2">
         <v>1111.4</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1656183697178382</v>
+        <v>0.1663317162998375</v>
       </c>
       <c r="C2">
-        <v>2441.483658170947</v>
+        <v>2415.593395360408</v>
       </c>
       <c r="D2">
-        <v>1573.783658170947</v>
+        <v>1568.350395360407</v>
       </c>
       <c r="E2">
-        <v>-1111.4</v>
+        <v>-1090.943</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.457</v>
       </c>
       <c r="G2">
         <v>867.7</v>
@@ -1445,28 +1445,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.460275723016365</v>
       </c>
       <c r="N2">
-        <v>596.0775510204081</v>
+        <v>592.6172752973918</v>
       </c>
       <c r="O2">
-        <v>107.2939591836735</v>
+        <v>106.6711095535305</v>
       </c>
       <c r="P2">
-        <v>488.7835918367347</v>
+        <v>485.9461657438612</v>
       </c>
       <c r="Q2">
-        <v>576.5835918367347</v>
+        <v>573.7461657438613</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1656183697178382</v>
+        <v>0.1666108046993394</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5935884474779501</v>
       </c>
       <c r="U2">
         <v>0.1691487374989669</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.2630214278994</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1663317162998375</v>
+        <v>0.167045062881837</v>
       </c>
       <c r="C3">
-        <v>2415.593395360408</v>
+        <v>2389.740518604152</v>
       </c>
       <c r="D3">
-        <v>1568.350395360407</v>
+        <v>1562.954518604152</v>
       </c>
       <c r="E3">
-        <v>-1090.943</v>
+        <v>-1070.486</v>
       </c>
       <c r="F3">
-        <v>20.457</v>
+        <v>40.914</v>
       </c>
       <c r="G3">
         <v>867.7</v>
@@ -1527,28 +1527,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M3">
-        <v>3.460275723016365</v>
+        <v>6.92055144603273</v>
       </c>
       <c r="N3">
-        <v>592.6172752973918</v>
+        <v>589.1569995743754</v>
       </c>
       <c r="O3">
-        <v>106.6711095535305</v>
+        <v>106.0482599233876</v>
       </c>
       <c r="P3">
-        <v>485.9461657438612</v>
+        <v>483.1087396509878</v>
       </c>
       <c r="Q3">
-        <v>573.7461657438613</v>
+        <v>570.9087396509879</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1666108046993394</v>
+        <v>0.1676234934559734</v>
       </c>
       <c r="T3">
-        <v>0.5935884474779501</v>
+        <v>0.5985641642470316</v>
       </c>
       <c r="U3">
         <v>0.1691487374989669</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.2630214278994</v>
+        <v>86.13151071394968</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.167045062881837</v>
+        <v>0.1677584094638364</v>
       </c>
       <c r="C4">
-        <v>2389.740518604152</v>
+        <v>2363.924643347421</v>
       </c>
       <c r="D4">
-        <v>1562.954518604152</v>
+        <v>1557.595643347421</v>
       </c>
       <c r="E4">
-        <v>-1070.486</v>
+        <v>-1050.029</v>
       </c>
       <c r="F4">
-        <v>40.914</v>
+        <v>61.371</v>
       </c>
       <c r="G4">
         <v>867.7</v>
@@ -1609,28 +1609,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M4">
-        <v>6.92055144603273</v>
+        <v>10.38082716904909</v>
       </c>
       <c r="N4">
-        <v>589.1569995743754</v>
+        <v>585.696723851359</v>
       </c>
       <c r="O4">
-        <v>106.0482599233876</v>
+        <v>105.4254102932446</v>
       </c>
       <c r="P4">
-        <v>483.1087396509878</v>
+        <v>480.2713135581144</v>
       </c>
       <c r="Q4">
-        <v>570.9087396509879</v>
+        <v>568.0713135581145</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1676234934559734</v>
+        <v>0.1686570623931565</v>
       </c>
       <c r="T4">
-        <v>0.5985641642470316</v>
+        <v>0.6036424731144447</v>
       </c>
       <c r="U4">
         <v>0.1691487374989669</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.13151071394968</v>
+        <v>57.42100714263313</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1677584094638364</v>
+        <v>0.1684717560458358</v>
       </c>
       <c r="C5">
-        <v>2363.924643347421</v>
+        <v>2338.145390291494</v>
       </c>
       <c r="D5">
-        <v>1557.595643347421</v>
+        <v>1552.273390291494</v>
       </c>
       <c r="E5">
-        <v>-1050.029</v>
+        <v>-1029.572</v>
       </c>
       <c r="F5">
-        <v>61.371</v>
+        <v>81.828</v>
       </c>
       <c r="G5">
         <v>867.7</v>
@@ -1691,28 +1691,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M5">
-        <v>10.38082716904909</v>
+        <v>13.84110289206546</v>
       </c>
       <c r="N5">
-        <v>585.696723851359</v>
+        <v>582.2364481283427</v>
       </c>
       <c r="O5">
-        <v>105.4254102932446</v>
+        <v>104.8025606631017</v>
       </c>
       <c r="P5">
-        <v>480.2713135581144</v>
+        <v>477.433887465241</v>
       </c>
       <c r="Q5">
-        <v>568.0713135581145</v>
+        <v>565.2338874652411</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1686570623931565</v>
+        <v>0.169712164016531</v>
       </c>
       <c r="T5">
-        <v>0.6036424731144447</v>
+        <v>0.6088265800832623</v>
       </c>
       <c r="U5">
         <v>0.1691487374989669</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.42100714263313</v>
+        <v>43.06575535697484</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1684717560458358</v>
+        <v>0.1691851026278353</v>
       </c>
       <c r="C6">
-        <v>2338.145390291494</v>
+        <v>2312.402385304204</v>
       </c>
       <c r="D6">
-        <v>1552.273390291494</v>
+        <v>1546.987385304204</v>
       </c>
       <c r="E6">
-        <v>-1029.572</v>
+        <v>-1009.115</v>
       </c>
       <c r="F6">
-        <v>81.828</v>
+        <v>102.285</v>
       </c>
       <c r="G6">
         <v>867.7</v>
@@ -1773,28 +1773,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M6">
-        <v>13.84110289206546</v>
+        <v>17.30137861508183</v>
       </c>
       <c r="N6">
-        <v>582.2364481283427</v>
+        <v>578.7761724053263</v>
       </c>
       <c r="O6">
-        <v>104.8025606631017</v>
+        <v>104.1797110329587</v>
       </c>
       <c r="P6">
-        <v>477.433887465241</v>
+        <v>474.5964613723676</v>
       </c>
       <c r="Q6">
-        <v>565.2338874652411</v>
+        <v>562.3964613723676</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.169712164016531</v>
+        <v>0.1707894783056607</v>
       </c>
       <c r="T6">
-        <v>0.6088265800832623</v>
+        <v>0.6141198261461601</v>
       </c>
       <c r="U6">
         <v>0.1691487374989669</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.06575535697484</v>
+        <v>34.45260428557987</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1691851026278353</v>
+        <v>0.1698984492098347</v>
       </c>
       <c r="C7">
-        <v>2312.402385304204</v>
+        <v>2286.695259332263</v>
       </c>
       <c r="D7">
-        <v>1546.987385304204</v>
+        <v>1541.737259332263</v>
       </c>
       <c r="E7">
-        <v>-1009.115</v>
+        <v>-988.6580000000001</v>
       </c>
       <c r="F7">
-        <v>102.285</v>
+        <v>122.742</v>
       </c>
       <c r="G7">
         <v>867.7</v>
@@ -1855,28 +1855,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M7">
-        <v>17.30137861508183</v>
+        <v>20.76165433809819</v>
       </c>
       <c r="N7">
-        <v>578.7761724053263</v>
+        <v>575.3158966823099</v>
       </c>
       <c r="O7">
-        <v>104.1797110329587</v>
+        <v>103.5568614028158</v>
       </c>
       <c r="P7">
-        <v>474.5964613723676</v>
+        <v>471.7590352794941</v>
       </c>
       <c r="Q7">
-        <v>562.3964613723676</v>
+        <v>559.5590352794942</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1707894783056607</v>
+        <v>0.1718897141754101</v>
       </c>
       <c r="T7">
-        <v>0.6141198261461601</v>
+        <v>0.6195256944657154</v>
       </c>
       <c r="U7">
         <v>0.1691487374989669</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.45260428557987</v>
+        <v>28.71050357131656</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1698984492098347</v>
+        <v>0.1706117957918341</v>
       </c>
       <c r="C8">
-        <v>2286.695259332263</v>
+        <v>2261.023648315374</v>
       </c>
       <c r="D8">
-        <v>1541.737259332263</v>
+        <v>1536.522648315374</v>
       </c>
       <c r="E8">
-        <v>-988.6580000000001</v>
+        <v>-968.2010000000001</v>
       </c>
       <c r="F8">
-        <v>122.742</v>
+        <v>143.199</v>
       </c>
       <c r="G8">
         <v>867.7</v>
@@ -1937,28 +1937,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M8">
-        <v>20.76165433809819</v>
+        <v>24.22193006111455</v>
       </c>
       <c r="N8">
-        <v>575.3158966823099</v>
+        <v>571.8556209592936</v>
       </c>
       <c r="O8">
-        <v>103.5568614028158</v>
+        <v>102.9340117726728</v>
       </c>
       <c r="P8">
-        <v>471.7590352794941</v>
+        <v>468.9216091866207</v>
       </c>
       <c r="Q8">
-        <v>559.5590352794942</v>
+        <v>556.7216091866208</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1718897141754101</v>
+        <v>0.1730136110316058</v>
       </c>
       <c r="T8">
-        <v>0.6195256944657154</v>
+        <v>0.6250478180179493</v>
       </c>
       <c r="U8">
         <v>0.1691487374989669</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.71050357131656</v>
+        <v>24.60900306112849</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1706117957918341</v>
+        <v>0.1713251423738335</v>
       </c>
       <c r="C9">
-        <v>2261.023648315374</v>
+        <v>2235.387193102074</v>
       </c>
       <c r="D9">
-        <v>1536.522648315374</v>
+        <v>1531.343193102074</v>
       </c>
       <c r="E9">
-        <v>-968.201</v>
+        <v>-947.7440000000001</v>
       </c>
       <c r="F9">
-        <v>143.199</v>
+        <v>163.656</v>
       </c>
       <c r="G9">
         <v>867.7</v>
@@ -2019,28 +2019,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M9">
-        <v>24.22193006111456</v>
+        <v>27.68220578413092</v>
       </c>
       <c r="N9">
-        <v>571.8556209592936</v>
+        <v>568.3953452362772</v>
       </c>
       <c r="O9">
-        <v>102.9340117726728</v>
+        <v>102.3111621425299</v>
       </c>
       <c r="P9">
-        <v>468.9216091866207</v>
+        <v>466.0841830937473</v>
       </c>
       <c r="Q9">
-        <v>556.7216091866208</v>
+        <v>553.8841830937474</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1730136110316058</v>
+        <v>0.1741619404281536</v>
       </c>
       <c r="T9">
-        <v>0.6250478180179493</v>
+        <v>0.6306899877343621</v>
       </c>
       <c r="U9">
         <v>0.1691487374989669</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.60900306112848</v>
+        <v>21.53287767848742</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1713251423738335</v>
+        <v>0.172038488955833</v>
       </c>
       <c r="C10">
-        <v>2235.387193102074</v>
+        <v>2209.785539367277</v>
       </c>
       <c r="D10">
-        <v>1531.343193102074</v>
+        <v>1526.198539367277</v>
       </c>
       <c r="E10">
-        <v>-947.7440000000001</v>
+        <v>-927.287</v>
       </c>
       <c r="F10">
-        <v>163.656</v>
+        <v>184.113</v>
       </c>
       <c r="G10">
         <v>867.7</v>
@@ -2101,28 +2101,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M10">
-        <v>27.68220578413092</v>
+        <v>31.14248150714728</v>
       </c>
       <c r="N10">
-        <v>568.3953452362772</v>
+        <v>564.9350695132608</v>
       </c>
       <c r="O10">
-        <v>102.3111621425299</v>
+        <v>101.6883125123869</v>
       </c>
       <c r="P10">
-        <v>466.0841830937473</v>
+        <v>463.2467570008739</v>
       </c>
       <c r="Q10">
-        <v>553.8841830937474</v>
+        <v>551.046757000874</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1741619404281536</v>
+        <v>0.1753355078334167</v>
       </c>
       <c r="T10">
-        <v>0.6306899877343621</v>
+        <v>0.6364561611808061</v>
       </c>
       <c r="U10">
         <v>0.1691487374989669</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.53287767848742</v>
+        <v>19.14033571421104</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.172038488955833</v>
+        <v>0.1727518355378324</v>
       </c>
       <c r="C11">
-        <v>2209.785539367277</v>
+        <v>2184.218337531471</v>
       </c>
       <c r="D11">
-        <v>1526.198539367277</v>
+        <v>1521.088337531471</v>
       </c>
       <c r="E11">
-        <v>-927.287</v>
+        <v>-906.8300000000002</v>
       </c>
       <c r="F11">
-        <v>184.113</v>
+        <v>204.57</v>
       </c>
       <c r="G11">
         <v>867.7</v>
@@ -2183,28 +2183,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M11">
-        <v>31.14248150714728</v>
+        <v>34.60275723016365</v>
       </c>
       <c r="N11">
-        <v>564.9350695132608</v>
+        <v>561.4747937902445</v>
       </c>
       <c r="O11">
-        <v>101.6883125123869</v>
+        <v>101.065462882244</v>
       </c>
       <c r="P11">
-        <v>463.2467570008739</v>
+        <v>460.4093309080005</v>
       </c>
       <c r="Q11">
-        <v>551.046757000874</v>
+        <v>548.2093309080005</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1753355078334167</v>
+        <v>0.1765351545143523</v>
       </c>
       <c r="T11">
-        <v>0.6364561611808061</v>
+        <v>0.6423504718149488</v>
       </c>
       <c r="U11">
         <v>0.1691487374989669</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.14033571421104</v>
+        <v>17.22630214278994</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1727518355378324</v>
+        <v>0.1734651821198318</v>
       </c>
       <c r="C12">
-        <v>2184.218337531471</v>
+        <v>2158.68524268154</v>
       </c>
       <c r="D12">
-        <v>1521.088337531471</v>
+        <v>1516.01224268154</v>
       </c>
       <c r="E12">
-        <v>-906.83</v>
+        <v>-886.373</v>
       </c>
       <c r="F12">
-        <v>204.57</v>
+        <v>225.027</v>
       </c>
       <c r="G12">
         <v>867.7</v>
@@ -2265,28 +2265,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M12">
-        <v>34.60275723016365</v>
+        <v>38.06303295318002</v>
       </c>
       <c r="N12">
-        <v>561.4747937902445</v>
+        <v>558.0145180672281</v>
       </c>
       <c r="O12">
-        <v>101.065462882244</v>
+        <v>100.4426132521011</v>
       </c>
       <c r="P12">
-        <v>460.4093309080005</v>
+        <v>457.571904815127</v>
       </c>
       <c r="Q12">
-        <v>548.2093309080005</v>
+        <v>545.3719048151271</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1765351545143523</v>
+        <v>0.1777617595476685</v>
       </c>
       <c r="T12">
-        <v>0.6423504718149488</v>
+        <v>0.6483772388678362</v>
       </c>
       <c r="U12">
         <v>0.1691487374989669</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.22630214278994</v>
+        <v>15.66027467526358</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1734651821198318</v>
+        <v>0.1741785287018312</v>
       </c>
       <c r="C13">
-        <v>2158.68524268154</v>
+        <v>2133.185914493155</v>
       </c>
       <c r="D13">
-        <v>1516.01224268154</v>
+        <v>1510.969914493154</v>
       </c>
       <c r="E13">
-        <v>-886.373</v>
+        <v>-865.9160000000001</v>
       </c>
       <c r="F13">
-        <v>225.027</v>
+        <v>245.484</v>
       </c>
       <c r="G13">
         <v>867.7</v>
@@ -2347,28 +2347,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M13">
-        <v>38.06303295318002</v>
+        <v>41.52330867619638</v>
       </c>
       <c r="N13">
-        <v>558.0145180672281</v>
+        <v>554.5542423442117</v>
       </c>
       <c r="O13">
-        <v>100.4426132521011</v>
+        <v>99.8197636219581</v>
       </c>
       <c r="P13">
-        <v>457.571904815127</v>
+        <v>454.7344787222536</v>
       </c>
       <c r="Q13">
-        <v>545.3719048151271</v>
+        <v>542.5344787222537</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1777617595476685</v>
+        <v>0.1790162419681055</v>
       </c>
       <c r="T13">
-        <v>0.6483772388678362</v>
+        <v>0.6545409778991983</v>
       </c>
       <c r="U13">
         <v>0.1691487374989669</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.66027467526358</v>
+        <v>14.35525178565828</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1741785287018312</v>
+        <v>0.1748918752838306</v>
       </c>
       <c r="C14">
-        <v>2133.185914493155</v>
+        <v>2107.720017154715</v>
       </c>
       <c r="D14">
-        <v>1510.969914493154</v>
+        <v>1505.961017154715</v>
       </c>
       <c r="E14">
-        <v>-865.9160000000001</v>
+        <v>-845.4590000000001</v>
       </c>
       <c r="F14">
-        <v>245.484</v>
+        <v>265.941</v>
       </c>
       <c r="G14">
         <v>867.7</v>
@@ -2429,28 +2429,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M14">
-        <v>41.52330867619638</v>
+        <v>44.98358439921275</v>
       </c>
       <c r="N14">
-        <v>554.5542423442117</v>
+        <v>551.0939666211954</v>
       </c>
       <c r="O14">
-        <v>99.8197636219581</v>
+        <v>99.19691399181517</v>
       </c>
       <c r="P14">
-        <v>454.7344787222536</v>
+        <v>451.8970526293802</v>
       </c>
       <c r="Q14">
-        <v>542.5344787222537</v>
+        <v>539.6970526293803</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1790162419681055</v>
+        <v>0.1802995630648744</v>
       </c>
       <c r="T14">
-        <v>0.6545409778991983</v>
+        <v>0.6608464120807068</v>
       </c>
       <c r="U14">
         <v>0.1691487374989669</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.35525178565828</v>
+        <v>13.25100164829995</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1748918752838306</v>
+        <v>0.17577742186583</v>
       </c>
       <c r="C15">
-        <v>2107.720017154715</v>
+        <v>2081.090997459398</v>
       </c>
       <c r="D15">
-        <v>1505.961017154715</v>
+        <v>1499.788997459398</v>
       </c>
       <c r="E15">
-        <v>-845.4590000000001</v>
+        <v>-825.0020000000001</v>
       </c>
       <c r="F15">
-        <v>265.941</v>
+        <v>286.398</v>
       </c>
       <c r="G15">
         <v>867.7</v>
@@ -2511,45 +2511,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M15">
-        <v>44.98358439921275</v>
+        <v>48.87345712222911</v>
       </c>
       <c r="N15">
-        <v>551.0939666211954</v>
+        <v>547.2040938981791</v>
       </c>
       <c r="O15">
-        <v>99.19691399181517</v>
+        <v>98.49673690167222</v>
       </c>
       <c r="P15">
-        <v>451.8970526293802</v>
+        <v>448.7073569965069</v>
       </c>
       <c r="Q15">
-        <v>539.6970526293803</v>
+        <v>536.5073569965069</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1802995630648744</v>
+        <v>0.1816127288383124</v>
       </c>
       <c r="T15">
-        <v>0.6608464120807068</v>
+        <v>0.6672984842664363</v>
       </c>
       <c r="U15">
-        <v>0.1691487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V15">
         <v>0.18</v>
       </c>
       <c r="W15">
-        <v>0.1387019647491528</v>
+        <v>0.1399319647491528</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.25100164829995</v>
+        <v>12.19634513534943</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.17577742186583</v>
+        <v>0.1765030684478295</v>
       </c>
       <c r="C16">
-        <v>2081.090997459398</v>
+        <v>2055.614024178899</v>
       </c>
       <c r="D16">
-        <v>1499.788997459398</v>
+        <v>1494.7690241789</v>
       </c>
       <c r="E16">
-        <v>-825.0020000000001</v>
+        <v>-804.5450000000001</v>
       </c>
       <c r="F16">
-        <v>286.398</v>
+        <v>306.8550000000001</v>
       </c>
       <c r="G16">
         <v>867.7</v>
@@ -2593,28 +2593,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M16">
-        <v>48.87345712222911</v>
+        <v>52.36441834524549</v>
       </c>
       <c r="N16">
-        <v>547.2040938981791</v>
+        <v>543.7131326751627</v>
       </c>
       <c r="O16">
-        <v>98.49673690167222</v>
+        <v>97.86836388152928</v>
       </c>
       <c r="P16">
-        <v>448.7073569965069</v>
+        <v>445.8447687936334</v>
       </c>
       <c r="Q16">
-        <v>536.5073569965069</v>
+        <v>533.6447687936335</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1816127288383124</v>
+        <v>0.1829567926299489</v>
       </c>
       <c r="T16">
-        <v>0.6672984842664363</v>
+        <v>0.6739023699153596</v>
       </c>
       <c r="U16">
         <v>0.1706487374989669</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.19634513534943</v>
+        <v>11.38325545965947</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1765030684478295</v>
+        <v>0.1772287150298289</v>
       </c>
       <c r="C17">
-        <v>2055.614024178899</v>
+        <v>2030.170543696792</v>
       </c>
       <c r="D17">
-        <v>1494.7690241789</v>
+        <v>1489.782543696792</v>
       </c>
       <c r="E17">
-        <v>-804.5450000000001</v>
+        <v>-784.0880000000001</v>
       </c>
       <c r="F17">
-        <v>306.855</v>
+        <v>327.312</v>
       </c>
       <c r="G17">
         <v>867.7</v>
@@ -2675,28 +2675,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M17">
-        <v>52.36441834524548</v>
+        <v>55.85537956826185</v>
       </c>
       <c r="N17">
-        <v>543.7131326751627</v>
+        <v>540.2221714521463</v>
       </c>
       <c r="O17">
-        <v>97.86836388152928</v>
+        <v>97.23999086138633</v>
       </c>
       <c r="P17">
-        <v>445.8447687936334</v>
+        <v>442.98218059076</v>
       </c>
       <c r="Q17">
-        <v>533.6447687936335</v>
+        <v>530.78218059076</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1829567926299489</v>
+        <v>0.1843328579404339</v>
       </c>
       <c r="T17">
-        <v>0.6739023699153596</v>
+        <v>0.6806634909368762</v>
       </c>
       <c r="U17">
         <v>0.1706487374989669</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.38325545965947</v>
+        <v>10.67180199343075</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1772287150298289</v>
+        <v>0.1779543616118283</v>
       </c>
       <c r="C18">
-        <v>2030.170543696792</v>
+        <v>2004.760221936251</v>
       </c>
       <c r="D18">
-        <v>1489.782543696792</v>
+        <v>1484.829221936251</v>
       </c>
       <c r="E18">
-        <v>-784.0880000000001</v>
+        <v>-763.6310000000001</v>
       </c>
       <c r="F18">
-        <v>327.312</v>
+        <v>347.769</v>
       </c>
       <c r="G18">
         <v>867.7</v>
@@ -2757,28 +2757,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M18">
-        <v>55.85537956826185</v>
+        <v>59.34634079127821</v>
       </c>
       <c r="N18">
-        <v>540.2221714521463</v>
+        <v>536.7312102291299</v>
       </c>
       <c r="O18">
-        <v>97.23999086138633</v>
+        <v>96.61161784124339</v>
       </c>
       <c r="P18">
-        <v>442.98218059076</v>
+        <v>440.1195923878865</v>
       </c>
       <c r="Q18">
-        <v>530.78218059076</v>
+        <v>527.9195923878866</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1843328579404339</v>
+        <v>0.1857420814511715</v>
       </c>
       <c r="T18">
-        <v>0.6806634909368762</v>
+        <v>0.6875875305372244</v>
       </c>
       <c r="U18">
         <v>0.1706487374989669</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.67180199343075</v>
+        <v>10.04404893499365</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1779543616118283</v>
+        <v>0.1789309281938277</v>
       </c>
       <c r="C19">
-        <v>2004.760221936251</v>
+        <v>1977.6888604298</v>
       </c>
       <c r="D19">
-        <v>1484.829221936251</v>
+        <v>1478.2148604298</v>
       </c>
       <c r="E19">
-        <v>-763.6310000000001</v>
+        <v>-743.174</v>
       </c>
       <c r="F19">
-        <v>347.769</v>
+        <v>368.2260000000001</v>
       </c>
       <c r="G19">
         <v>867.7</v>
@@ -2839,45 +2839,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M19">
-        <v>59.34634079127821</v>
+        <v>63.46328621429458</v>
       </c>
       <c r="N19">
-        <v>536.7312102291299</v>
+        <v>532.6142648061135</v>
       </c>
       <c r="O19">
-        <v>96.61161784124339</v>
+        <v>95.87056766510042</v>
       </c>
       <c r="P19">
-        <v>440.1195923878865</v>
+        <v>436.7436971410131</v>
       </c>
       <c r="Q19">
-        <v>527.9195923878866</v>
+        <v>524.5436971410131</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1857420814511715</v>
+        <v>0.187185676267049</v>
       </c>
       <c r="T19">
-        <v>0.6875875305372244</v>
+        <v>0.6946804491522155</v>
       </c>
       <c r="U19">
-        <v>0.1706487374989669</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V19">
         <v>0.18</v>
       </c>
       <c r="W19">
-        <v>0.1399319647491528</v>
+        <v>0.1413259647491528</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.04404893499365</v>
+        <v>9.392478495482425</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1789309281938277</v>
+        <v>0.1796705147758272</v>
       </c>
       <c r="C20">
-        <v>1977.6888604298</v>
+        <v>1952.261665028265</v>
       </c>
       <c r="D20">
-        <v>1478.2148604298</v>
+        <v>1473.244665028265</v>
       </c>
       <c r="E20">
-        <v>-743.1740000000001</v>
+        <v>-722.7170000000001</v>
       </c>
       <c r="F20">
-        <v>368.226</v>
+        <v>388.683</v>
       </c>
       <c r="G20">
         <v>867.7</v>
@@ -2921,28 +2921,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M20">
-        <v>63.46328621429458</v>
+        <v>66.98902433731094</v>
       </c>
       <c r="N20">
-        <v>532.6142648061135</v>
+        <v>529.0885266830971</v>
       </c>
       <c r="O20">
-        <v>95.87056766510042</v>
+        <v>95.23593480295749</v>
       </c>
       <c r="P20">
-        <v>436.7436971410131</v>
+        <v>433.8525918801396</v>
       </c>
       <c r="Q20">
-        <v>524.5436971410131</v>
+        <v>521.6525918801397</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.187185676267049</v>
+        <v>0.188664915399368</v>
       </c>
       <c r="T20">
-        <v>0.6946804491522154</v>
+        <v>0.7019485015601691</v>
       </c>
       <c r="U20">
         <v>0.1723487374989669</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.392478495482425</v>
+        <v>8.898137522035983</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1796705147758272</v>
+        <v>0.1804101013578266</v>
       </c>
       <c r="C21">
-        <v>1952.261665028265</v>
+        <v>1926.867780159672</v>
       </c>
       <c r="D21">
-        <v>1473.244665028265</v>
+        <v>1468.307780159672</v>
       </c>
       <c r="E21">
-        <v>-722.7170000000001</v>
+        <v>-702.26</v>
       </c>
       <c r="F21">
-        <v>388.683</v>
+        <v>409.14</v>
       </c>
       <c r="G21">
         <v>867.7</v>
@@ -3003,28 +3003,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M21">
-        <v>66.98902433731094</v>
+        <v>70.51476246032732</v>
       </c>
       <c r="N21">
-        <v>529.0885266830971</v>
+        <v>525.5627885600808</v>
       </c>
       <c r="O21">
-        <v>95.23593480295749</v>
+        <v>94.60130194081454</v>
       </c>
       <c r="P21">
-        <v>433.8525918801396</v>
+        <v>430.9614866192662</v>
       </c>
       <c r="Q21">
-        <v>521.6525918801397</v>
+        <v>518.7614866192663</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.188664915399368</v>
+        <v>0.190181135509995</v>
       </c>
       <c r="T21">
-        <v>0.7019485015601691</v>
+        <v>0.7093982552783217</v>
       </c>
       <c r="U21">
         <v>0.1723487374989669</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.898137522035983</v>
+        <v>8.453230645934182</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1804101013578266</v>
+        <v>0.181149687939826</v>
       </c>
       <c r="C22">
-        <v>1926.867780159672</v>
+        <v>1901.506872068805</v>
       </c>
       <c r="D22">
-        <v>1468.307780159672</v>
+        <v>1463.403872068805</v>
       </c>
       <c r="E22">
-        <v>-702.26</v>
+        <v>-681.8030000000001</v>
       </c>
       <c r="F22">
-        <v>409.14</v>
+        <v>429.597</v>
       </c>
       <c r="G22">
         <v>867.7</v>
@@ -3085,28 +3085,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M22">
-        <v>70.51476246032732</v>
+        <v>74.04050058334367</v>
       </c>
       <c r="N22">
-        <v>525.5627885600808</v>
+        <v>522.0370504370644</v>
       </c>
       <c r="O22">
-        <v>94.60130194081454</v>
+        <v>93.96666907867159</v>
       </c>
       <c r="P22">
-        <v>430.9614866192662</v>
+        <v>428.0703813583928</v>
       </c>
       <c r="Q22">
-        <v>518.7614866192663</v>
+        <v>515.8703813583929</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.190181135509995</v>
+        <v>0.1917357409398783</v>
       </c>
       <c r="T22">
-        <v>0.7093982552783217</v>
+        <v>0.7170366103564274</v>
       </c>
       <c r="U22">
         <v>0.1723487374989669</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.453230645934182</v>
+        <v>8.05069585327065</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.181149687939826</v>
+        <v>0.1818892745218254</v>
       </c>
       <c r="C23">
-        <v>1901.506872068805</v>
+        <v>1876.178611444363</v>
       </c>
       <c r="D23">
-        <v>1463.403872068805</v>
+        <v>1458.532611444363</v>
       </c>
       <c r="E23">
-        <v>-681.8030000000001</v>
+        <v>-661.346</v>
       </c>
       <c r="F23">
-        <v>429.597</v>
+        <v>450.054</v>
       </c>
       <c r="G23">
         <v>867.7</v>
@@ -3167,28 +3167,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M23">
-        <v>74.04050058334367</v>
+        <v>77.56623870636004</v>
       </c>
       <c r="N23">
-        <v>522.0370504370644</v>
+        <v>518.511312314048</v>
       </c>
       <c r="O23">
-        <v>93.96666907867159</v>
+        <v>93.33203621652865</v>
       </c>
       <c r="P23">
-        <v>428.0703813583928</v>
+        <v>425.1792760975194</v>
       </c>
       <c r="Q23">
-        <v>515.8703813583929</v>
+        <v>512.9792760975195</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1917357409398783</v>
+        <v>0.193330208047451</v>
       </c>
       <c r="T23">
-        <v>0.7170366103564274</v>
+        <v>0.7248708206929462</v>
       </c>
       <c r="U23">
         <v>0.1723487374989669</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.05069585327065</v>
+        <v>7.684755132667439</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1818892745218254</v>
+        <v>0.1827797411038248</v>
       </c>
       <c r="C24">
-        <v>1876.178611444363</v>
+        <v>1849.899442186641</v>
       </c>
       <c r="D24">
-        <v>1458.532611444363</v>
+        <v>1452.710442186641</v>
       </c>
       <c r="E24">
-        <v>-661.346</v>
+        <v>-640.8890000000001</v>
       </c>
       <c r="F24">
-        <v>450.054</v>
+        <v>470.511</v>
       </c>
       <c r="G24">
         <v>867.7</v>
@@ -3249,45 +3249,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M24">
-        <v>77.56623870636004</v>
+        <v>81.4683856293764</v>
       </c>
       <c r="N24">
-        <v>518.511312314048</v>
+        <v>514.6091653910318</v>
       </c>
       <c r="O24">
-        <v>93.33203621652865</v>
+        <v>92.62964977038571</v>
       </c>
       <c r="P24">
-        <v>425.1792760975194</v>
+        <v>421.9795156206461</v>
       </c>
       <c r="Q24">
-        <v>512.9792760975195</v>
+        <v>509.7795156206461</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.193330208047451</v>
+        <v>0.1949660898850905</v>
       </c>
       <c r="T24">
-        <v>0.7248708206929462</v>
+        <v>0.7329085170122317</v>
       </c>
       <c r="U24">
-        <v>0.1723487374989669</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V24">
         <v>0.18</v>
       </c>
       <c r="W24">
-        <v>0.1413259647491528</v>
+        <v>0.1419819647491528</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.684755132667439</v>
+        <v>7.316673166105683</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1827797411038248</v>
+        <v>0.1835258876858243</v>
       </c>
       <c r="C25">
-        <v>1849.899442186641</v>
+        <v>1824.599558391944</v>
       </c>
       <c r="D25">
-        <v>1452.710442186641</v>
+        <v>1447.867558391944</v>
       </c>
       <c r="E25">
-        <v>-640.8890000000001</v>
+        <v>-620.432</v>
       </c>
       <c r="F25">
-        <v>470.511</v>
+        <v>490.9680000000001</v>
       </c>
       <c r="G25">
         <v>867.7</v>
@@ -3331,28 +3331,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M25">
-        <v>81.4683856293764</v>
+        <v>85.01048935239278</v>
       </c>
       <c r="N25">
-        <v>514.6091653910318</v>
+        <v>511.0670616680154</v>
       </c>
       <c r="O25">
-        <v>92.62964977038571</v>
+        <v>91.99207110024275</v>
       </c>
       <c r="P25">
-        <v>421.9795156206461</v>
+        <v>419.0749905677726</v>
       </c>
       <c r="Q25">
-        <v>509.7795156206461</v>
+        <v>506.8749905677727</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1949660898850905</v>
+        <v>0.1966450212447731</v>
       </c>
       <c r="T25">
-        <v>0.7329085170122317</v>
+        <v>0.741157731655709</v>
       </c>
       <c r="U25">
         <v>0.1731487374989669</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.316673166105683</v>
+        <v>7.011811784184611</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1835258876858242</v>
+        <v>0.1842720342678237</v>
       </c>
       <c r="C26">
-        <v>1824.599558391944</v>
+        <v>1799.331856642364</v>
       </c>
       <c r="D26">
-        <v>1447.867558391944</v>
+        <v>1443.056856642364</v>
       </c>
       <c r="E26">
-        <v>-620.432</v>
+        <v>-599.9750000000001</v>
       </c>
       <c r="F26">
-        <v>490.968</v>
+        <v>511.425</v>
       </c>
       <c r="G26">
         <v>867.7</v>
@@ -3413,28 +3413,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M26">
-        <v>85.01048935239277</v>
+        <v>88.55259307540913</v>
       </c>
       <c r="N26">
-        <v>511.0670616680154</v>
+        <v>507.524957944999</v>
       </c>
       <c r="O26">
-        <v>91.99207110024275</v>
+        <v>91.35449243009981</v>
       </c>
       <c r="P26">
-        <v>419.0749905677726</v>
+        <v>416.1704655148991</v>
       </c>
       <c r="Q26">
-        <v>506.8749905677727</v>
+        <v>503.9704655148992</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1966450212447731</v>
+        <v>0.1983687241073806</v>
       </c>
       <c r="T26">
-        <v>0.7411577316557089</v>
+        <v>0.7496269253563455</v>
       </c>
       <c r="U26">
         <v>0.1731487374989669</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.011811784184612</v>
+        <v>6.731339312817227</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1842720342678237</v>
+        <v>0.1850181808498231</v>
       </c>
       <c r="C27">
-        <v>1799.331856642364</v>
+        <v>1774.096017214895</v>
       </c>
       <c r="D27">
-        <v>1443.056856642364</v>
+        <v>1438.278017214895</v>
       </c>
       <c r="E27">
-        <v>-599.9750000000001</v>
+        <v>-579.518</v>
       </c>
       <c r="F27">
-        <v>511.425</v>
+        <v>531.8820000000001</v>
       </c>
       <c r="G27">
         <v>867.7</v>
@@ -3495,28 +3495,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M27">
-        <v>88.55259307540913</v>
+        <v>92.0946967984255</v>
       </c>
       <c r="N27">
-        <v>507.524957944999</v>
+        <v>503.9828542219826</v>
       </c>
       <c r="O27">
-        <v>91.35449243009981</v>
+        <v>90.71691375995687</v>
       </c>
       <c r="P27">
-        <v>416.1704655148991</v>
+        <v>413.2659404620258</v>
       </c>
       <c r="Q27">
-        <v>503.9704655148992</v>
+        <v>501.0659404620258</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1983687241073806</v>
+        <v>0.2001390135338423</v>
       </c>
       <c r="T27">
-        <v>0.7496269253563455</v>
+        <v>0.7583250161840263</v>
       </c>
       <c r="U27">
         <v>0.1731487374989669</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.731339312817227</v>
+        <v>6.472441646939642</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1850181808498231</v>
+        <v>0.1857643274318225</v>
       </c>
       <c r="C28">
-        <v>1774.096017214895</v>
+        <v>1748.891724607738</v>
       </c>
       <c r="D28">
-        <v>1438.278017214895</v>
+        <v>1433.530724607738</v>
       </c>
       <c r="E28">
-        <v>-579.518</v>
+        <v>-559.061</v>
       </c>
       <c r="F28">
-        <v>531.8820000000001</v>
+        <v>552.3390000000001</v>
       </c>
       <c r="G28">
         <v>867.7</v>
@@ -3577,28 +3577,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M28">
-        <v>92.0946967984255</v>
+        <v>95.63680052144187</v>
       </c>
       <c r="N28">
-        <v>503.9828542219826</v>
+        <v>500.4407504989663</v>
       </c>
       <c r="O28">
-        <v>90.71691375995687</v>
+        <v>90.07933508981392</v>
       </c>
       <c r="P28">
-        <v>413.2659404620258</v>
+        <v>410.3614154091524</v>
       </c>
       <c r="Q28">
-        <v>501.0659404620258</v>
+        <v>498.1614154091524</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2001390135338423</v>
+        <v>0.2019578040404811</v>
       </c>
       <c r="T28">
-        <v>0.7583250161840263</v>
+        <v>0.7672614108699997</v>
       </c>
       <c r="U28">
         <v>0.1731487374989669</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.472441646939642</v>
+        <v>6.232721585941878</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1857643274318225</v>
+        <v>0.1867400740138219</v>
       </c>
       <c r="C29">
-        <v>1748.891724607738</v>
+        <v>1722.273706031259</v>
       </c>
       <c r="D29">
-        <v>1433.530724607738</v>
+        <v>1427.369706031259</v>
       </c>
       <c r="E29">
-        <v>-559.061</v>
+        <v>-538.604</v>
       </c>
       <c r="F29">
-        <v>552.3390000000001</v>
+        <v>572.796</v>
       </c>
       <c r="G29">
         <v>867.7</v>
@@ -3659,45 +3659,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M29">
-        <v>95.63680052144187</v>
+        <v>99.75170024445823</v>
       </c>
       <c r="N29">
-        <v>500.4407504989663</v>
+        <v>496.3258507759499</v>
       </c>
       <c r="O29">
-        <v>90.07933508981392</v>
+        <v>89.33865313967098</v>
       </c>
       <c r="P29">
-        <v>410.3614154091524</v>
+        <v>406.9871976362789</v>
       </c>
       <c r="Q29">
-        <v>498.1614154091524</v>
+        <v>494.787197636279</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2019578040404811</v>
+        <v>0.2038271165056377</v>
       </c>
       <c r="T29">
-        <v>0.7672614108699997</v>
+        <v>0.7764460387416947</v>
       </c>
       <c r="U29">
-        <v>0.1731487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V29">
         <v>0.18</v>
       </c>
       <c r="W29">
-        <v>0.1419819647491528</v>
+        <v>0.1428019647491529</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.232721585941878</v>
+        <v>5.975612942532512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1867400740138219</v>
+        <v>0.1874944205958213</v>
       </c>
       <c r="C30">
-        <v>1722.273706031259</v>
+        <v>1697.089818415862</v>
       </c>
       <c r="D30">
-        <v>1427.369706031259</v>
+        <v>1422.642818415862</v>
       </c>
       <c r="E30">
-        <v>-538.604</v>
+        <v>-518.147</v>
       </c>
       <c r="F30">
-        <v>572.796</v>
+        <v>593.253</v>
       </c>
       <c r="G30">
         <v>867.7</v>
@@ -3741,28 +3741,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M30">
-        <v>99.75170024445823</v>
+        <v>103.3142609674746</v>
       </c>
       <c r="N30">
-        <v>496.3258507759499</v>
+        <v>492.7632900529335</v>
       </c>
       <c r="O30">
-        <v>89.33865313967098</v>
+        <v>88.69739220952803</v>
       </c>
       <c r="P30">
-        <v>406.9871976362789</v>
+        <v>404.0658978434055</v>
       </c>
       <c r="Q30">
-        <v>494.787197636279</v>
+        <v>491.8658978434056</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2038271165056377</v>
+        <v>0.2057490856599535</v>
       </c>
       <c r="T30">
-        <v>0.7764460387416947</v>
+        <v>0.7858893885252682</v>
       </c>
       <c r="U30">
         <v>0.1741487374989669</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.975612942532512</v>
+        <v>5.769557323824494</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1874944205958213</v>
+        <v>0.1882487671778207</v>
       </c>
       <c r="C31">
-        <v>1697.089818415862</v>
+        <v>1671.93713465449</v>
       </c>
       <c r="D31">
-        <v>1422.642818415862</v>
+        <v>1417.94713465449</v>
       </c>
       <c r="E31">
-        <v>-518.1470000000002</v>
+        <v>-497.6900000000001</v>
       </c>
       <c r="F31">
-        <v>593.2529999999999</v>
+        <v>613.71</v>
       </c>
       <c r="G31">
         <v>867.7</v>
@@ -3823,28 +3823,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M31">
-        <v>103.3142609674746</v>
+        <v>106.876821690491</v>
       </c>
       <c r="N31">
-        <v>492.7632900529335</v>
+        <v>489.2007293299172</v>
       </c>
       <c r="O31">
-        <v>88.69739220952803</v>
+        <v>88.05613127938508</v>
       </c>
       <c r="P31">
-        <v>404.0658978434055</v>
+        <v>401.1445980505321</v>
       </c>
       <c r="Q31">
-        <v>491.8658978434056</v>
+        <v>488.9445980505321</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2057490856599535</v>
+        <v>0.2077259682186784</v>
       </c>
       <c r="T31">
-        <v>0.7858893885252682</v>
+        <v>0.7956025483026583</v>
       </c>
       <c r="U31">
         <v>0.1741487374989669</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.769557323824495</v>
+        <v>5.577238746363678</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1882487671778207</v>
+        <v>0.1890031137598202</v>
       </c>
       <c r="C32">
-        <v>1671.93713465449</v>
+        <v>1646.815346782149</v>
       </c>
       <c r="D32">
-        <v>1417.94713465449</v>
+        <v>1413.282346782149</v>
       </c>
       <c r="E32">
-        <v>-497.6900000000001</v>
+        <v>-477.2330000000001</v>
       </c>
       <c r="F32">
-        <v>613.71</v>
+        <v>634.167</v>
       </c>
       <c r="G32">
         <v>867.7</v>
@@ -3905,28 +3905,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M32">
-        <v>106.876821690491</v>
+        <v>110.4393824135073</v>
       </c>
       <c r="N32">
-        <v>489.2007293299172</v>
+        <v>485.6381686069008</v>
       </c>
       <c r="O32">
-        <v>88.05613127938508</v>
+        <v>87.41487034924214</v>
       </c>
       <c r="P32">
-        <v>401.1445980505321</v>
+        <v>398.2232982576586</v>
       </c>
       <c r="Q32">
-        <v>488.9445980505321</v>
+        <v>486.0232982576587</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2077259682186784</v>
+        <v>0.2097601517211345</v>
       </c>
       <c r="T32">
-        <v>0.7956025483026583</v>
+        <v>0.8055972489431612</v>
       </c>
       <c r="U32">
         <v>0.1741487374989669</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.577238746363678</v>
+        <v>5.397327819061623</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1890031137598202</v>
+        <v>0.1897574603418196</v>
       </c>
       <c r="C33">
-        <v>1646.815346782149</v>
+        <v>1621.724150873154</v>
       </c>
       <c r="D33">
-        <v>1413.282346782149</v>
+        <v>1408.648150873154</v>
       </c>
       <c r="E33">
-        <v>-477.2330000000001</v>
+        <v>-456.7760000000001</v>
       </c>
       <c r="F33">
-        <v>634.167</v>
+        <v>654.624</v>
       </c>
       <c r="G33">
         <v>867.7</v>
@@ -3987,28 +3987,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M33">
-        <v>110.4393824135073</v>
+        <v>114.0019431365237</v>
       </c>
       <c r="N33">
-        <v>485.6381686069008</v>
+        <v>482.0756078838845</v>
       </c>
       <c r="O33">
-        <v>87.41487034924214</v>
+        <v>86.7736094190992</v>
       </c>
       <c r="P33">
-        <v>398.2232982576586</v>
+        <v>395.3019984647852</v>
       </c>
       <c r="Q33">
-        <v>486.0232982576587</v>
+        <v>483.1019984647853</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2097601517211345</v>
+        <v>0.2118541641501334</v>
       </c>
       <c r="T33">
-        <v>0.8055972489431612</v>
+        <v>0.8158859113672082</v>
       </c>
       <c r="U33">
         <v>0.1741487374989669</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.397327819061623</v>
+        <v>5.228661324715948</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1897574603418196</v>
+        <v>0.190511806923819</v>
       </c>
       <c r="C34">
-        <v>1621.724150873154</v>
+        <v>1596.663246975114</v>
       </c>
       <c r="D34">
-        <v>1408.648150873154</v>
+        <v>1404.044246975114</v>
       </c>
       <c r="E34">
-        <v>-456.7760000000001</v>
+        <v>-436.3190000000001</v>
       </c>
       <c r="F34">
-        <v>654.624</v>
+        <v>675.081</v>
       </c>
       <c r="G34">
         <v>867.7</v>
@@ -4069,28 +4069,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M34">
-        <v>114.0019431365237</v>
+        <v>117.5645038595401</v>
       </c>
       <c r="N34">
-        <v>482.0756078838845</v>
+        <v>478.513047160868</v>
       </c>
       <c r="O34">
-        <v>86.7736094190992</v>
+        <v>86.13234848895624</v>
       </c>
       <c r="P34">
-        <v>395.3019984647852</v>
+        <v>392.3806986719118</v>
       </c>
       <c r="Q34">
-        <v>483.1019984647853</v>
+        <v>480.1806986719118</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2118541641501334</v>
+        <v>0.2140106844128337</v>
       </c>
       <c r="T34">
-        <v>0.8158859113672082</v>
+        <v>0.8264816980427193</v>
       </c>
       <c r="U34">
         <v>0.1741487374989669</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.228661324715948</v>
+        <v>5.070217042148798</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.190511806923819</v>
+        <v>0.1912661535058184</v>
       </c>
       <c r="C35">
-        <v>1596.663246975114</v>
+        <v>1571.632339044221</v>
       </c>
       <c r="D35">
-        <v>1404.044246975114</v>
+        <v>1399.470339044221</v>
       </c>
       <c r="E35">
-        <v>-436.3190000000001</v>
+        <v>-415.8620000000001</v>
       </c>
       <c r="F35">
-        <v>675.081</v>
+        <v>695.538</v>
       </c>
       <c r="G35">
         <v>867.7</v>
@@ -4151,28 +4151,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M35">
-        <v>117.5645038595401</v>
+        <v>121.1270645825564</v>
       </c>
       <c r="N35">
-        <v>478.513047160868</v>
+        <v>474.9504864378517</v>
       </c>
       <c r="O35">
-        <v>86.13234848895624</v>
+        <v>85.49108755881331</v>
       </c>
       <c r="P35">
-        <v>392.3806986719118</v>
+        <v>389.4593988790384</v>
       </c>
       <c r="Q35">
-        <v>480.1806986719118</v>
+        <v>477.2593988790385</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2140106844128337</v>
+        <v>0.2162325537744038</v>
       </c>
       <c r="T35">
-        <v>0.8264816980427193</v>
+        <v>0.8373985691629429</v>
       </c>
       <c r="U35">
         <v>0.1741487374989669</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.070217042148798</v>
+        <v>4.921093011497364</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1912661535058184</v>
+        <v>0.1920205000878178</v>
       </c>
       <c r="C36">
-        <v>1571.632339044221</v>
+        <v>1546.631134881786</v>
       </c>
       <c r="D36">
-        <v>1399.470339044221</v>
+        <v>1394.926134881787</v>
       </c>
       <c r="E36">
-        <v>-415.8620000000001</v>
+        <v>-395.405</v>
       </c>
       <c r="F36">
-        <v>695.538</v>
+        <v>715.9950000000001</v>
       </c>
       <c r="G36">
         <v>867.7</v>
@@ -4233,28 +4233,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M36">
-        <v>121.1270645825564</v>
+        <v>124.6896253055728</v>
       </c>
       <c r="N36">
-        <v>474.9504864378517</v>
+        <v>471.3879257148353</v>
       </c>
       <c r="O36">
-        <v>85.49108755881331</v>
+        <v>84.84982662867036</v>
       </c>
       <c r="P36">
-        <v>389.4593988790384</v>
+        <v>386.5380990861649</v>
       </c>
       <c r="Q36">
-        <v>477.2593988790385</v>
+        <v>474.338099086165</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2162325537744038</v>
+        <v>0.218522788347099</v>
       </c>
       <c r="T36">
-        <v>0.8373985691629429</v>
+        <v>0.8486513440099425</v>
       </c>
       <c r="U36">
         <v>0.1741487374989669</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.921093011497364</v>
+        <v>4.780490354026009</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1920205000878178</v>
+        <v>0.1927748466698173</v>
       </c>
       <c r="C37">
-        <v>1546.631134881786</v>
+        <v>1521.659346072021</v>
       </c>
       <c r="D37">
-        <v>1394.926134881787</v>
+        <v>1390.411346072021</v>
       </c>
       <c r="E37">
-        <v>-395.405</v>
+        <v>-374.948</v>
       </c>
       <c r="F37">
-        <v>715.9950000000001</v>
+        <v>736.4520000000001</v>
       </c>
       <c r="G37">
         <v>867.7</v>
@@ -4315,28 +4315,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M37">
-        <v>124.6896253055728</v>
+        <v>128.2521860285892</v>
       </c>
       <c r="N37">
-        <v>471.3879257148353</v>
+        <v>467.825364991819</v>
       </c>
       <c r="O37">
-        <v>84.84982662867036</v>
+        <v>84.20856569852741</v>
       </c>
       <c r="P37">
-        <v>386.5380990861649</v>
+        <v>383.6167992932915</v>
       </c>
       <c r="Q37">
-        <v>474.338099086165</v>
+        <v>471.4167992932916</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.218522788347099</v>
+        <v>0.220884592750191</v>
       </c>
       <c r="T37">
-        <v>0.8486513440099425</v>
+        <v>0.8602557680709109</v>
       </c>
       <c r="U37">
         <v>0.1741487374989669</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.780490354026009</v>
+        <v>4.647698955303064</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1927748466698173</v>
+        <v>0.1935291932518167</v>
       </c>
       <c r="C38">
-        <v>1521.659346072021</v>
+        <v>1496.716687921008</v>
       </c>
       <c r="D38">
-        <v>1390.411346072021</v>
+        <v>1385.925687921008</v>
       </c>
       <c r="E38">
-        <v>-374.9480000000001</v>
+        <v>-354.4910000000001</v>
       </c>
       <c r="F38">
-        <v>736.452</v>
+        <v>756.909</v>
       </c>
       <c r="G38">
         <v>867.7</v>
@@ -4397,28 +4397,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M38">
-        <v>128.2521860285891</v>
+        <v>131.8147467516055</v>
       </c>
       <c r="N38">
-        <v>467.825364991819</v>
+        <v>464.2628042688026</v>
       </c>
       <c r="O38">
-        <v>84.20856569852742</v>
+        <v>83.56730476838446</v>
       </c>
       <c r="P38">
-        <v>383.6167992932916</v>
+        <v>380.6954995004181</v>
       </c>
       <c r="Q38">
-        <v>471.4167992932917</v>
+        <v>468.4954995004182</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.220884592750191</v>
+        <v>0.2233213750708415</v>
       </c>
       <c r="T38">
-        <v>0.8602557680709109</v>
+        <v>0.8722285865465131</v>
       </c>
       <c r="U38">
         <v>0.1741487374989669</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.647698955303065</v>
+        <v>4.522085470024605</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1935291932518167</v>
+        <v>0.1950625398338161</v>
       </c>
       <c r="C39">
-        <v>1496.716687921008</v>
+        <v>1467.230399269107</v>
       </c>
       <c r="D39">
-        <v>1385.925687921008</v>
+        <v>1376.896399269106</v>
       </c>
       <c r="E39">
-        <v>-354.4910000000001</v>
+        <v>-334.0340000000001</v>
       </c>
       <c r="F39">
-        <v>756.909</v>
+        <v>777.366</v>
       </c>
       <c r="G39">
         <v>867.7</v>
@@ -4479,45 +4479,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M39">
-        <v>131.8147467516055</v>
+        <v>137.3207224746219</v>
       </c>
       <c r="N39">
-        <v>464.2628042688026</v>
+        <v>458.7568285457862</v>
       </c>
       <c r="O39">
-        <v>83.56730476838446</v>
+        <v>82.57622913824152</v>
       </c>
       <c r="P39">
-        <v>380.6954995004181</v>
+        <v>376.1805994075447</v>
       </c>
       <c r="Q39">
-        <v>468.4954995004182</v>
+        <v>463.9805994075448</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2233213750708415</v>
+        <v>0.2258367632728033</v>
       </c>
       <c r="T39">
-        <v>0.8722285865465131</v>
+        <v>0.8845876249729414</v>
       </c>
       <c r="U39">
-        <v>0.1741487374989669</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V39">
         <v>0.18</v>
       </c>
       <c r="W39">
-        <v>0.1428019647491529</v>
+        <v>0.1448519647491529</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.522085470024605</v>
+        <v>4.340769115386562</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1950625398338161</v>
+        <v>0.1958373864158155</v>
       </c>
       <c r="C40">
-        <v>1467.230399269107</v>
+        <v>1442.255226810376</v>
       </c>
       <c r="D40">
-        <v>1376.896399269106</v>
+        <v>1372.378226810376</v>
       </c>
       <c r="E40">
-        <v>-334.0340000000001</v>
+        <v>-313.577</v>
       </c>
       <c r="F40">
-        <v>777.366</v>
+        <v>797.8230000000001</v>
       </c>
       <c r="G40">
         <v>867.7</v>
@@ -4561,28 +4561,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M40">
-        <v>137.3207224746219</v>
+        <v>140.9344256976383</v>
       </c>
       <c r="N40">
-        <v>458.7568285457862</v>
+        <v>455.1431253227698</v>
       </c>
       <c r="O40">
-        <v>82.57622913824152</v>
+        <v>81.92576255809857</v>
       </c>
       <c r="P40">
-        <v>376.1805994075447</v>
+        <v>373.2173627646713</v>
       </c>
       <c r="Q40">
-        <v>463.9805994075448</v>
+        <v>461.0173627646714</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2258367632728033</v>
+        <v>0.2284346232190917</v>
       </c>
       <c r="T40">
-        <v>0.8845876249729414</v>
+        <v>0.8973518777740066</v>
       </c>
       <c r="U40">
         <v>0.1766487374989669</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.340769115386562</v>
+        <v>4.229467343197163</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1958373864158155</v>
+        <v>0.196612232997815</v>
       </c>
       <c r="C41">
-        <v>1442.255226810376</v>
+        <v>1417.309609392954</v>
       </c>
       <c r="D41">
-        <v>1372.378226810376</v>
+        <v>1367.889609392954</v>
       </c>
       <c r="E41">
-        <v>-313.577</v>
+        <v>-293.12</v>
       </c>
       <c r="F41">
-        <v>797.8230000000001</v>
+        <v>818.2800000000001</v>
       </c>
       <c r="G41">
         <v>867.7</v>
@@ -4643,28 +4643,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M41">
-        <v>140.9344256976383</v>
+        <v>144.5481289206546</v>
       </c>
       <c r="N41">
-        <v>455.1431253227698</v>
+        <v>451.5294220997535</v>
       </c>
       <c r="O41">
-        <v>81.92576255809857</v>
+        <v>81.27529597795562</v>
       </c>
       <c r="P41">
-        <v>373.2173627646713</v>
+        <v>370.2541261217979</v>
       </c>
       <c r="Q41">
-        <v>461.0173627646714</v>
+        <v>458.0541261217979</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2284346232190917</v>
+        <v>0.231119078496923</v>
       </c>
       <c r="T41">
-        <v>0.8973518777740066</v>
+        <v>0.9105416056684407</v>
       </c>
       <c r="U41">
         <v>0.1766487374989669</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.229467343197163</v>
+        <v>4.123730659617234</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.196612232997815</v>
+        <v>0.1973870795798144</v>
       </c>
       <c r="C42">
-        <v>1417.309609392954</v>
+        <v>1392.393257966511</v>
       </c>
       <c r="D42">
-        <v>1367.889609392954</v>
+        <v>1363.43025796651</v>
       </c>
       <c r="E42">
-        <v>-293.12</v>
+        <v>-272.663</v>
       </c>
       <c r="F42">
-        <v>818.2800000000001</v>
+        <v>838.7370000000001</v>
       </c>
       <c r="G42">
         <v>867.7</v>
@@ -4725,28 +4725,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M42">
-        <v>144.5481289206546</v>
+        <v>148.161832143671</v>
       </c>
       <c r="N42">
-        <v>451.5294220997535</v>
+        <v>447.9157188767372</v>
       </c>
       <c r="O42">
-        <v>81.27529597795562</v>
+        <v>80.62482939781269</v>
       </c>
       <c r="P42">
-        <v>370.2541261217979</v>
+        <v>367.2908894789245</v>
       </c>
       <c r="Q42">
-        <v>458.0541261217979</v>
+        <v>455.0908894789246</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.231119078496923</v>
+        <v>0.2338945322587486</v>
       </c>
       <c r="T42">
-        <v>0.9105416056684407</v>
+        <v>0.9241784429830249</v>
       </c>
       <c r="U42">
         <v>0.1766487374989669</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.123730659617234</v>
+        <v>4.023151863041205</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1973870795798144</v>
+        <v>0.1993673261618138</v>
       </c>
       <c r="C43">
-        <v>1392.393257966511</v>
+        <v>1360.670672050217</v>
       </c>
       <c r="D43">
-        <v>1363.43025796651</v>
+        <v>1352.164672050217</v>
       </c>
       <c r="E43">
-        <v>-272.663</v>
+        <v>-252.206</v>
       </c>
       <c r="F43">
-        <v>838.7370000000001</v>
+        <v>859.1940000000001</v>
       </c>
       <c r="G43">
         <v>867.7</v>
@@ -4807,45 +4807,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M43">
-        <v>148.161832143671</v>
+        <v>154.7827143666873</v>
       </c>
       <c r="N43">
-        <v>447.9157188767372</v>
+        <v>441.2948366537208</v>
       </c>
       <c r="O43">
-        <v>80.62482939781269</v>
+        <v>79.43307059766974</v>
       </c>
       <c r="P43">
-        <v>367.2908894789245</v>
+        <v>361.861766056051</v>
       </c>
       <c r="Q43">
-        <v>455.0908894789246</v>
+        <v>449.6617660560511</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2338945322587486</v>
+        <v>0.2367656913227062</v>
       </c>
       <c r="T43">
-        <v>0.9241784429830249</v>
+        <v>0.9382855160670777</v>
       </c>
       <c r="U43">
-        <v>0.1766487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V43">
         <v>0.18</v>
       </c>
       <c r="W43">
-        <v>0.1448519647491529</v>
+        <v>0.1477219647491528</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.023151863041205</v>
+        <v>3.851060200483841</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1993673261618138</v>
+        <v>0.2001708727438132</v>
       </c>
       <c r="C44">
-        <v>1360.670672050217</v>
+        <v>1335.695231805429</v>
       </c>
       <c r="D44">
-        <v>1352.164672050217</v>
+        <v>1347.646231805429</v>
       </c>
       <c r="E44">
-        <v>-252.2060000000001</v>
+        <v>-231.7490000000001</v>
       </c>
       <c r="F44">
-        <v>859.194</v>
+        <v>879.651</v>
       </c>
       <c r="G44">
         <v>867.7</v>
@@ -4889,28 +4889,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M44">
-        <v>154.7827143666873</v>
+        <v>158.4680170897037</v>
       </c>
       <c r="N44">
-        <v>441.2948366537208</v>
+        <v>437.6095339307044</v>
       </c>
       <c r="O44">
-        <v>79.43307059766974</v>
+        <v>78.76971610752679</v>
       </c>
       <c r="P44">
-        <v>361.861766056051</v>
+        <v>358.8398178231776</v>
       </c>
       <c r="Q44">
-        <v>449.6617660560511</v>
+        <v>446.6398178231777</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2367656913227062</v>
+        <v>0.2397375928099605</v>
       </c>
       <c r="T44">
-        <v>0.9382855160670777</v>
+        <v>0.9528875741716234</v>
       </c>
       <c r="U44">
         <v>0.1801487374989669</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.851060200483841</v>
+        <v>3.761500660937706</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2001708727438132</v>
+        <v>0.2009744193258127</v>
       </c>
       <c r="C45">
-        <v>1335.695231805429</v>
+        <v>1310.749888938665</v>
       </c>
       <c r="D45">
-        <v>1347.646231805429</v>
+        <v>1343.157888938665</v>
       </c>
       <c r="E45">
-        <v>-231.7490000000001</v>
+        <v>-211.292</v>
       </c>
       <c r="F45">
-        <v>879.651</v>
+        <v>900.1080000000001</v>
       </c>
       <c r="G45">
         <v>867.7</v>
@@ -4971,28 +4971,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M45">
-        <v>158.4680170897037</v>
+        <v>162.1533198127201</v>
       </c>
       <c r="N45">
-        <v>437.6095339307044</v>
+        <v>433.9242312076881</v>
       </c>
       <c r="O45">
-        <v>78.76971610752679</v>
+        <v>78.10636161738385</v>
       </c>
       <c r="P45">
-        <v>358.8398178231776</v>
+        <v>355.8178695903042</v>
       </c>
       <c r="Q45">
-        <v>446.6398178231777</v>
+        <v>443.6178695903043</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2397375928099605</v>
+        <v>0.2428156336360453</v>
       </c>
       <c r="T45">
-        <v>0.9528875741716234</v>
+        <v>0.9680111343513317</v>
       </c>
       <c r="U45">
         <v>0.1801487374989669</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.761500660937706</v>
+        <v>3.676012009552758</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2009744193258127</v>
+        <v>0.2017779659078121</v>
       </c>
       <c r="C46">
-        <v>1310.749888938665</v>
+        <v>1285.83434372972</v>
       </c>
       <c r="D46">
-        <v>1343.157888938665</v>
+        <v>1338.69934372972</v>
       </c>
       <c r="E46">
-        <v>-211.292</v>
+        <v>-190.835</v>
       </c>
       <c r="F46">
-        <v>900.1080000000001</v>
+        <v>920.5650000000001</v>
       </c>
       <c r="G46">
         <v>867.7</v>
@@ -5053,28 +5053,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M46">
-        <v>162.1533198127201</v>
+        <v>165.8386225357364</v>
       </c>
       <c r="N46">
-        <v>433.9242312076881</v>
+        <v>430.2389284846716</v>
       </c>
       <c r="O46">
-        <v>78.10636161738385</v>
+        <v>77.44300712724089</v>
       </c>
       <c r="P46">
-        <v>355.8178695903042</v>
+        <v>352.7959213574308</v>
       </c>
       <c r="Q46">
-        <v>443.6178695903043</v>
+        <v>440.5959213574308</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2428156336360453</v>
+        <v>0.2460056032194423</v>
       </c>
       <c r="T46">
-        <v>0.9680111343513317</v>
+        <v>0.9836846421739383</v>
       </c>
       <c r="U46">
         <v>0.1801487374989669</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.676012009552758</v>
+        <v>3.594322853784918</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2017779659078121</v>
+        <v>0.2025815124898115</v>
       </c>
       <c r="C47">
-        <v>1285.83434372972</v>
+        <v>1260.948300424842</v>
       </c>
       <c r="D47">
-        <v>1338.69934372972</v>
+        <v>1334.270300424842</v>
       </c>
       <c r="E47">
-        <v>-190.835</v>
+        <v>-170.378</v>
       </c>
       <c r="F47">
-        <v>920.5650000000001</v>
+        <v>941.022</v>
       </c>
       <c r="G47">
         <v>867.7</v>
@@ -5135,28 +5135,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M47">
-        <v>165.8386225357364</v>
+        <v>169.5239252587528</v>
       </c>
       <c r="N47">
-        <v>430.2389284846716</v>
+        <v>426.5536257616553</v>
       </c>
       <c r="O47">
-        <v>77.44300712724089</v>
+        <v>76.77965263709795</v>
       </c>
       <c r="P47">
-        <v>352.7959213574308</v>
+        <v>349.7739731245574</v>
       </c>
       <c r="Q47">
-        <v>440.5959213574308</v>
+        <v>437.5739731245574</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2460056032194423</v>
+        <v>0.2493137198244466</v>
       </c>
       <c r="T47">
-        <v>0.9836846421739383</v>
+        <v>0.9999386502862712</v>
       </c>
       <c r="U47">
         <v>0.1801487374989669</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.594322853784918</v>
+        <v>3.516185400441768</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2025815124898115</v>
+        <v>0.2044641790718109</v>
       </c>
       <c r="C48">
-        <v>1260.948300424842</v>
+        <v>1230.228176547125</v>
       </c>
       <c r="D48">
-        <v>1334.270300424842</v>
+        <v>1324.007176547125</v>
       </c>
       <c r="E48">
-        <v>-170.378</v>
+        <v>-149.921</v>
       </c>
       <c r="F48">
-        <v>941.022</v>
+        <v>961.479</v>
       </c>
       <c r="G48">
         <v>867.7</v>
@@ -5217,45 +5217,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M48">
-        <v>169.5239252587528</v>
+        <v>175.9013691817692</v>
       </c>
       <c r="N48">
-        <v>426.5536257616553</v>
+        <v>420.176181838639</v>
       </c>
       <c r="O48">
-        <v>76.77965263709795</v>
+        <v>75.63171273095502</v>
       </c>
       <c r="P48">
-        <v>349.7739731245574</v>
+        <v>344.5444691076839</v>
       </c>
       <c r="Q48">
-        <v>437.5739731245574</v>
+        <v>432.344469107684</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2493137198244466</v>
+        <v>0.2527466710183189</v>
       </c>
       <c r="T48">
-        <v>0.9999386502862712</v>
+        <v>1.016806017195296</v>
       </c>
       <c r="U48">
-        <v>0.1801487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V48">
         <v>0.18</v>
       </c>
       <c r="W48">
-        <v>0.1477219647491528</v>
+        <v>0.1500179647491529</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.516185400441768</v>
+        <v>3.388703304545892</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2044641790718109</v>
+        <v>0.2052906856538103</v>
       </c>
       <c r="C49">
-        <v>1230.228176547125</v>
+        <v>1205.315281763363</v>
       </c>
       <c r="D49">
-        <v>1324.007176547125</v>
+        <v>1319.551281763363</v>
       </c>
       <c r="E49">
-        <v>-149.921</v>
+        <v>-129.4639999999999</v>
       </c>
       <c r="F49">
-        <v>961.479</v>
+        <v>981.9360000000001</v>
       </c>
       <c r="G49">
         <v>867.7</v>
@@ -5299,28 +5299,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M49">
-        <v>175.9013691817692</v>
+        <v>179.6439515047855</v>
       </c>
       <c r="N49">
-        <v>420.176181838639</v>
+        <v>416.4335995156226</v>
       </c>
       <c r="O49">
-        <v>75.63171273095502</v>
+        <v>74.95804791281206</v>
       </c>
       <c r="P49">
-        <v>344.5444691076839</v>
+        <v>341.4755516028105</v>
       </c>
       <c r="Q49">
-        <v>432.344469107684</v>
+        <v>429.2755516028106</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2527466710183189</v>
+        <v>0.256311658796571</v>
       </c>
       <c r="T49">
-        <v>1.016806017195296</v>
+        <v>1.034322128985437</v>
       </c>
       <c r="U49">
         <v>0.1829487374989669</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.388703304545892</v>
+        <v>3.318105319034519</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2052906856538103</v>
+        <v>0.2061171922358097</v>
       </c>
       <c r="C50">
-        <v>1205.315281763363</v>
+        <v>1180.432278662332</v>
       </c>
       <c r="D50">
-        <v>1319.551281763363</v>
+        <v>1315.125278662332</v>
       </c>
       <c r="E50">
-        <v>-129.4640000000001</v>
+        <v>-109.0070000000001</v>
       </c>
       <c r="F50">
-        <v>981.936</v>
+        <v>1002.393</v>
       </c>
       <c r="G50">
         <v>867.7</v>
@@ -5381,28 +5381,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M50">
-        <v>179.6439515047855</v>
+        <v>183.3865338278019</v>
       </c>
       <c r="N50">
-        <v>416.4335995156226</v>
+        <v>412.6910171926062</v>
       </c>
       <c r="O50">
-        <v>74.95804791281206</v>
+        <v>74.28438309466911</v>
       </c>
       <c r="P50">
-        <v>341.4755516028105</v>
+        <v>338.4066340979371</v>
       </c>
       <c r="Q50">
-        <v>429.2755516028106</v>
+        <v>426.2066340979371</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.256311658796571</v>
+        <v>0.2600164500171075</v>
       </c>
       <c r="T50">
-        <v>1.034322128985437</v>
+        <v>1.052525147120289</v>
       </c>
       <c r="U50">
         <v>0.1829487374989669</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.318105319034519</v>
+        <v>3.250388883952182</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2061171922358097</v>
+        <v>0.2069436988178092</v>
       </c>
       <c r="C51">
-        <v>1180.432278662332</v>
+        <v>1155.578867463933</v>
       </c>
       <c r="D51">
-        <v>1315.125278662332</v>
+        <v>1310.728867463933</v>
       </c>
       <c r="E51">
-        <v>-109.0070000000001</v>
+        <v>-88.55000000000007</v>
       </c>
       <c r="F51">
-        <v>1002.393</v>
+        <v>1022.85</v>
       </c>
       <c r="G51">
         <v>867.7</v>
@@ -5463,28 +5463,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M51">
-        <v>183.3865338278019</v>
+        <v>187.1291161508183</v>
       </c>
       <c r="N51">
-        <v>412.6910171926062</v>
+        <v>408.9484348695898</v>
       </c>
       <c r="O51">
-        <v>74.28438309466911</v>
+        <v>73.61071827652617</v>
       </c>
       <c r="P51">
-        <v>338.4066340979371</v>
+        <v>335.3377165930636</v>
       </c>
       <c r="Q51">
-        <v>426.2066340979371</v>
+        <v>423.1377165930637</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2600164500171075</v>
+        <v>0.2638694328864655</v>
       </c>
       <c r="T51">
-        <v>1.052525147120289</v>
+        <v>1.071456285980536</v>
       </c>
       <c r="U51">
         <v>0.1829487374989669</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.250388883952182</v>
+        <v>3.185381106273138</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2069436988178092</v>
+        <v>0.2077702053998086</v>
       </c>
       <c r="C52">
-        <v>1155.578867463933</v>
+        <v>1130.754752383323</v>
       </c>
       <c r="D52">
-        <v>1310.728867463933</v>
+        <v>1306.361752383322</v>
       </c>
       <c r="E52">
-        <v>-88.55000000000007</v>
+        <v>-68.09300000000007</v>
       </c>
       <c r="F52">
-        <v>1022.85</v>
+        <v>1043.307</v>
       </c>
       <c r="G52">
         <v>867.7</v>
@@ -5545,28 +5545,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M52">
-        <v>187.1291161508183</v>
+        <v>190.8716984738346</v>
       </c>
       <c r="N52">
-        <v>408.9484348695898</v>
+        <v>405.2058525465735</v>
       </c>
       <c r="O52">
-        <v>73.61071827652617</v>
+        <v>72.93705345838323</v>
       </c>
       <c r="P52">
-        <v>335.3377165930636</v>
+        <v>332.2687990881903</v>
       </c>
       <c r="Q52">
-        <v>423.1377165930637</v>
+        <v>420.0687990881904</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2638694328864655</v>
+        <v>0.267879680362736</v>
       </c>
       <c r="T52">
-        <v>1.071456285980536</v>
+        <v>1.091160124386098</v>
       </c>
       <c r="U52">
         <v>0.1829487374989669</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.185381106273138</v>
+        <v>3.122922653208959</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2077702053998086</v>
+        <v>0.208596711981808</v>
       </c>
       <c r="C53">
-        <v>1130.754752383323</v>
+        <v>1105.959641564576</v>
       </c>
       <c r="D53">
-        <v>1306.361752383322</v>
+        <v>1302.023641564576</v>
       </c>
       <c r="E53">
-        <v>-68.09300000000007</v>
+        <v>-47.63599999999997</v>
       </c>
       <c r="F53">
-        <v>1043.307</v>
+        <v>1063.764</v>
       </c>
       <c r="G53">
         <v>867.7</v>
@@ -5627,28 +5627,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M53">
-        <v>190.8716984738346</v>
+        <v>194.614280796851</v>
       </c>
       <c r="N53">
-        <v>405.2058525465735</v>
+        <v>401.4632702235571</v>
       </c>
       <c r="O53">
-        <v>72.93705345838323</v>
+        <v>72.26338864024028</v>
       </c>
       <c r="P53">
-        <v>332.2687990881903</v>
+        <v>329.1998815833168</v>
       </c>
       <c r="Q53">
-        <v>420.0687990881904</v>
+        <v>416.9998815833169</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.267879680362736</v>
+        <v>0.2720570214838511</v>
       </c>
       <c r="T53">
-        <v>1.091160124386098</v>
+        <v>1.11168495605856</v>
       </c>
       <c r="U53">
         <v>0.1829487374989669</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.122922653208959</v>
+        <v>3.062866448339556</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.208596711981808</v>
+        <v>0.2094232185638074</v>
       </c>
       <c r="C54">
-        <v>1105.959641564576</v>
+        <v>1081.19324701567</v>
       </c>
       <c r="D54">
-        <v>1302.023641564576</v>
+        <v>1297.71424701567</v>
       </c>
       <c r="E54">
-        <v>-47.63599999999997</v>
+        <v>-27.17900000000009</v>
       </c>
       <c r="F54">
-        <v>1063.764</v>
+        <v>1084.221</v>
       </c>
       <c r="G54">
         <v>867.7</v>
@@ -5709,28 +5709,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M54">
-        <v>194.614280796851</v>
+        <v>198.3568631198674</v>
       </c>
       <c r="N54">
-        <v>401.4632702235571</v>
+        <v>397.7206879005407</v>
       </c>
       <c r="O54">
-        <v>72.26338864024028</v>
+        <v>71.58972382209733</v>
       </c>
       <c r="P54">
-        <v>329.1998815833168</v>
+        <v>326.1309640784434</v>
       </c>
       <c r="Q54">
-        <v>416.9998815833169</v>
+        <v>413.9309640784435</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2720570214838511</v>
+        <v>0.2764121218016093</v>
       </c>
       <c r="T54">
-        <v>1.11168495605856</v>
+        <v>1.133083184823466</v>
       </c>
       <c r="U54">
         <v>0.1829487374989669</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.062866448339556</v>
+        <v>3.005076515352017</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2094232185638074</v>
+        <v>0.2137035651458068</v>
       </c>
       <c r="C55">
-        <v>1081.19324701567</v>
+        <v>1038.867292441527</v>
       </c>
       <c r="D55">
-        <v>1297.71424701567</v>
+        <v>1275.845292441527</v>
       </c>
       <c r="E55">
-        <v>-27.17900000000009</v>
+        <v>-6.72199999999998</v>
       </c>
       <c r="F55">
-        <v>1084.221</v>
+        <v>1104.678</v>
       </c>
       <c r="G55">
         <v>867.7</v>
@@ -5791,45 +5791,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M55">
-        <v>198.3568631198674</v>
+        <v>210.7159338428837</v>
       </c>
       <c r="N55">
-        <v>397.7206879005407</v>
+        <v>385.3616171775244</v>
       </c>
       <c r="O55">
-        <v>71.58972382209733</v>
+        <v>69.3650910919544</v>
       </c>
       <c r="P55">
-        <v>326.1309640784434</v>
+        <v>315.99652608557</v>
       </c>
       <c r="Q55">
-        <v>413.9309640784435</v>
+        <v>403.7965260855701</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2764121218016093</v>
+        <v>0.2809565743070963</v>
       </c>
       <c r="T55">
-        <v>1.133083184823466</v>
+        <v>1.155411771360759</v>
       </c>
       <c r="U55">
-        <v>0.1829487374989669</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V55">
         <v>0.18</v>
       </c>
       <c r="W55">
-        <v>0.1500179647491529</v>
+        <v>0.1564139647491528</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.005076515352017</v>
+        <v>2.828820489032699</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2137035651458068</v>
+        <v>0.2145940317278063</v>
       </c>
       <c r="C56">
-        <v>1038.867292441527</v>
+        <v>1013.953055032513</v>
       </c>
       <c r="D56">
-        <v>1275.845292441527</v>
+        <v>1271.388055032513</v>
       </c>
       <c r="E56">
-        <v>-6.72199999999998</v>
+        <v>13.73500000000013</v>
       </c>
       <c r="F56">
-        <v>1104.678</v>
+        <v>1125.135</v>
       </c>
       <c r="G56">
         <v>867.7</v>
@@ -5873,28 +5873,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M56">
-        <v>210.7159338428837</v>
+        <v>214.6180807659001</v>
       </c>
       <c r="N56">
-        <v>385.3616171775244</v>
+        <v>381.459470254508</v>
       </c>
       <c r="O56">
-        <v>69.3650910919544</v>
+        <v>68.66270464581144</v>
       </c>
       <c r="P56">
-        <v>315.99652608557</v>
+        <v>312.7967656086965</v>
       </c>
       <c r="Q56">
-        <v>403.7965260855701</v>
+        <v>400.5967656086966</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2809565743070963</v>
+        <v>0.2857030024794938</v>
       </c>
       <c r="T56">
-        <v>1.155411771360759</v>
+        <v>1.178732739521932</v>
       </c>
       <c r="U56">
         <v>0.1907487374989669</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.828820489032699</v>
+        <v>2.777387389232103</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2145940317278063</v>
+        <v>0.2154844983098056</v>
       </c>
       <c r="C57">
-        <v>1013.953055032513</v>
+        <v>989.0698524216928</v>
       </c>
       <c r="D57">
-        <v>1271.388055032513</v>
+        <v>1266.961852421693</v>
       </c>
       <c r="E57">
-        <v>13.73500000000013</v>
+        <v>34.19200000000001</v>
       </c>
       <c r="F57">
-        <v>1125.135</v>
+        <v>1145.592</v>
       </c>
       <c r="G57">
         <v>867.7</v>
@@ -5955,28 +5955,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M57">
-        <v>214.6180807659001</v>
+        <v>218.5202276889165</v>
       </c>
       <c r="N57">
-        <v>381.459470254508</v>
+        <v>377.5573233314917</v>
       </c>
       <c r="O57">
-        <v>68.66270464581144</v>
+        <v>67.96031819966849</v>
       </c>
       <c r="P57">
-        <v>312.7967656086965</v>
+        <v>309.5970051318232</v>
       </c>
       <c r="Q57">
-        <v>400.5967656086966</v>
+        <v>397.3970051318232</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2857030024794938</v>
+        <v>0.2906651773870002</v>
       </c>
       <c r="T57">
-        <v>1.178732739521932</v>
+        <v>1.203113751690432</v>
       </c>
       <c r="U57">
         <v>0.1907487374989669</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.777387389232103</v>
+        <v>2.72779118585296</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2154844983098056</v>
+        <v>0.2163749648918051</v>
       </c>
       <c r="C58">
-        <v>989.0698524216928</v>
+        <v>964.2173616005146</v>
       </c>
       <c r="D58">
-        <v>1266.961852421693</v>
+        <v>1262.566361600515</v>
       </c>
       <c r="E58">
-        <v>34.19200000000001</v>
+        <v>54.64900000000011</v>
       </c>
       <c r="F58">
-        <v>1145.592</v>
+        <v>1166.049</v>
       </c>
       <c r="G58">
         <v>867.7</v>
@@ -6037,28 +6037,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M58">
-        <v>218.5202276889165</v>
+        <v>222.4223746119329</v>
       </c>
       <c r="N58">
-        <v>377.5573233314917</v>
+        <v>373.6551764084753</v>
       </c>
       <c r="O58">
-        <v>67.96031819966849</v>
+        <v>67.25793175352554</v>
       </c>
       <c r="P58">
-        <v>309.5970051318232</v>
+        <v>306.3972446549497</v>
       </c>
       <c r="Q58">
-        <v>397.3970051318232</v>
+        <v>394.1972446549498</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2906651773870002</v>
+        <v>0.2958581511274139</v>
       </c>
       <c r="T58">
-        <v>1.203113751690432</v>
+        <v>1.228628764424908</v>
       </c>
       <c r="U58">
         <v>0.1907487374989669</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.72779118585296</v>
+        <v>2.67993520013624</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2163749648918051</v>
+        <v>0.2172654314738045</v>
       </c>
       <c r="C59">
-        <v>964.2173616005146</v>
+        <v>939.3952640274067</v>
       </c>
       <c r="D59">
-        <v>1262.566361600515</v>
+        <v>1258.201264027407</v>
       </c>
       <c r="E59">
-        <v>54.64900000000011</v>
+        <v>75.10599999999999</v>
       </c>
       <c r="F59">
-        <v>1166.049</v>
+        <v>1186.506</v>
       </c>
       <c r="G59">
         <v>867.7</v>
@@ -6119,28 +6119,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M59">
-        <v>222.4223746119329</v>
+        <v>226.3245215349492</v>
       </c>
       <c r="N59">
-        <v>373.6551764084753</v>
+        <v>369.7530294854589</v>
       </c>
       <c r="O59">
-        <v>67.25793175352554</v>
+        <v>66.5555453073826</v>
       </c>
       <c r="P59">
-        <v>306.3972446549497</v>
+        <v>303.1974841780763</v>
       </c>
       <c r="Q59">
-        <v>394.1972446549498</v>
+        <v>390.9974841780764</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2958581511274139</v>
+        <v>0.3012984093316568</v>
       </c>
       <c r="T59">
-        <v>1.228628764424908</v>
+        <v>1.255358777765787</v>
       </c>
       <c r="U59">
         <v>0.1907487374989669</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.67993520013624</v>
+        <v>2.633729420823546</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2172654314738045</v>
+        <v>0.2181558980558039</v>
       </c>
       <c r="C60">
-        <v>939.3952640274069</v>
+        <v>914.60324555082</v>
       </c>
       <c r="D60">
-        <v>1258.201264027407</v>
+        <v>1253.86624555082</v>
       </c>
       <c r="E60">
-        <v>75.10599999999977</v>
+        <v>95.56299999999987</v>
       </c>
       <c r="F60">
-        <v>1186.506</v>
+        <v>1206.963</v>
       </c>
       <c r="G60">
         <v>867.7</v>
@@ -6201,28 +6201,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M60">
-        <v>226.3245215349492</v>
+        <v>230.2266684579655</v>
       </c>
       <c r="N60">
-        <v>369.753029485459</v>
+        <v>365.8508825624426</v>
       </c>
       <c r="O60">
-        <v>66.55554530738262</v>
+        <v>65.85315886123966</v>
       </c>
       <c r="P60">
-        <v>303.1974841780764</v>
+        <v>299.997723701203</v>
       </c>
       <c r="Q60">
-        <v>390.9974841780764</v>
+        <v>387.797723701203</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3012984093316568</v>
+        <v>0.3070040459848871</v>
       </c>
       <c r="T60">
-        <v>1.255358777765787</v>
+        <v>1.283392694196466</v>
       </c>
       <c r="U60">
         <v>0.1907487374989669</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.633729420823547</v>
+        <v>2.589089939114674</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2181558980558039</v>
+        <v>0.2190463646378034</v>
       </c>
       <c r="C61">
-        <v>914.60324555082</v>
+        <v>889.8409963338609</v>
       </c>
       <c r="D61">
-        <v>1253.86624555082</v>
+        <v>1249.560996333861</v>
       </c>
       <c r="E61">
-        <v>95.56299999999987</v>
+        <v>116.02</v>
       </c>
       <c r="F61">
-        <v>1206.963</v>
+        <v>1227.42</v>
       </c>
       <c r="G61">
         <v>867.7</v>
@@ -6283,28 +6283,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M61">
-        <v>230.2266684579655</v>
+        <v>234.1288153809819</v>
       </c>
       <c r="N61">
-        <v>365.8508825624426</v>
+        <v>361.9487356394262</v>
       </c>
       <c r="O61">
-        <v>65.85315886123966</v>
+        <v>65.15077241509671</v>
       </c>
       <c r="P61">
-        <v>299.997723701203</v>
+        <v>296.7979632243295</v>
       </c>
       <c r="Q61">
-        <v>387.797723701203</v>
+        <v>384.5979632243296</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3070040459848871</v>
+        <v>0.3129949644707791</v>
       </c>
       <c r="T61">
-        <v>1.283392694196466</v>
+        <v>1.312828306448678</v>
       </c>
       <c r="U61">
         <v>0.1907487374989669</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.589089939114674</v>
+        <v>2.545938440129428</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2190463646378034</v>
+        <v>0.2199368312198028</v>
       </c>
       <c r="C62">
-        <v>889.8409963338609</v>
+        <v>865.1082107804764</v>
       </c>
       <c r="D62">
-        <v>1249.560996333861</v>
+        <v>1245.285210780476</v>
       </c>
       <c r="E62">
-        <v>116.02</v>
+        <v>136.4769999999999</v>
       </c>
       <c r="F62">
-        <v>1227.42</v>
+        <v>1247.877</v>
       </c>
       <c r="G62">
         <v>867.7</v>
@@ -6365,28 +6365,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M62">
-        <v>234.1288153809819</v>
+        <v>238.0309623039983</v>
       </c>
       <c r="N62">
-        <v>361.9487356394262</v>
+        <v>358.0465887164098</v>
       </c>
       <c r="O62">
-        <v>65.15077241509671</v>
+        <v>64.44838596895376</v>
       </c>
       <c r="P62">
-        <v>296.7979632243295</v>
+        <v>293.5982027474561</v>
       </c>
       <c r="Q62">
-        <v>384.5979632243296</v>
+        <v>381.3982027474561</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3129949644707791</v>
+        <v>0.3192931095456911</v>
       </c>
       <c r="T62">
-        <v>1.312828306448678</v>
+        <v>1.343773437277928</v>
       </c>
       <c r="U62">
         <v>0.1907487374989669</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.545938440129428</v>
+        <v>2.504201744389602</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2199368312198028</v>
+        <v>0.2228100578018022</v>
       </c>
       <c r="C63">
-        <v>865.1082107804764</v>
+        <v>831.0520927645077</v>
       </c>
       <c r="D63">
-        <v>1245.285210780476</v>
+        <v>1231.686092764508</v>
       </c>
       <c r="E63">
-        <v>136.4769999999999</v>
+        <v>156.934</v>
       </c>
       <c r="F63">
-        <v>1247.877</v>
+        <v>1268.334</v>
       </c>
       <c r="G63">
         <v>867.7</v>
@@ -6447,45 +6447,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M63">
-        <v>238.0309623039983</v>
+        <v>246.8796118270146</v>
       </c>
       <c r="N63">
-        <v>358.0465887164098</v>
+        <v>349.1979391933935</v>
       </c>
       <c r="O63">
-        <v>64.44838596895376</v>
+        <v>62.85562905481083</v>
       </c>
       <c r="P63">
-        <v>293.5982027474561</v>
+        <v>286.3423101385827</v>
       </c>
       <c r="Q63">
-        <v>381.3982027474561</v>
+        <v>374.1423101385827</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3192931095456911</v>
+        <v>0.3259227359403353</v>
       </c>
       <c r="T63">
-        <v>1.343773437277928</v>
+        <v>1.376347259203452</v>
       </c>
       <c r="U63">
-        <v>0.1907487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V63">
         <v>0.18</v>
       </c>
       <c r="W63">
-        <v>0.1564139647491528</v>
+        <v>0.1596119647491528</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.504201744389602</v>
+        <v>2.414446242073939</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2228100578018022</v>
+        <v>0.2237325043838016</v>
       </c>
       <c r="C64">
-        <v>831.0520927645077</v>
+        <v>806.2918750199312</v>
       </c>
       <c r="D64">
-        <v>1231.686092764508</v>
+        <v>1227.382875019931</v>
       </c>
       <c r="E64">
-        <v>156.934</v>
+        <v>177.3909999999998</v>
       </c>
       <c r="F64">
-        <v>1268.334</v>
+        <v>1288.791</v>
       </c>
       <c r="G64">
         <v>867.7</v>
@@ -6529,28 +6529,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M64">
-        <v>246.8796118270146</v>
+        <v>250.861541050031</v>
       </c>
       <c r="N64">
-        <v>349.1979391933935</v>
+        <v>345.2160099703772</v>
       </c>
       <c r="O64">
-        <v>62.85562905481083</v>
+        <v>62.13888179466789</v>
       </c>
       <c r="P64">
-        <v>286.3423101385827</v>
+        <v>283.0771281757093</v>
       </c>
       <c r="Q64">
-        <v>374.1423101385827</v>
+        <v>370.8771281757093</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3259227359403353</v>
+        <v>0.3329107205184738</v>
       </c>
       <c r="T64">
-        <v>1.376347259203452</v>
+        <v>1.410681828260087</v>
       </c>
       <c r="U64">
         <v>0.1946487374989669</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.414446242073939</v>
+        <v>2.376121698548955</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2237325043838016</v>
+        <v>0.224654950965801</v>
       </c>
       <c r="C65">
-        <v>806.2918750199312</v>
+        <v>781.5616214227784</v>
       </c>
       <c r="D65">
-        <v>1227.382875019931</v>
+        <v>1223.109621422778</v>
       </c>
       <c r="E65">
-        <v>177.3909999999998</v>
+        <v>197.848</v>
       </c>
       <c r="F65">
-        <v>1288.791</v>
+        <v>1309.248</v>
       </c>
       <c r="G65">
         <v>867.7</v>
@@ -6611,28 +6611,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M65">
-        <v>250.861541050031</v>
+        <v>254.8434702730474</v>
       </c>
       <c r="N65">
-        <v>345.2160099703772</v>
+        <v>341.2340807473607</v>
       </c>
       <c r="O65">
-        <v>62.13888179466789</v>
+        <v>61.42213453452493</v>
       </c>
       <c r="P65">
-        <v>283.0771281757093</v>
+        <v>279.8119462128358</v>
       </c>
       <c r="Q65">
-        <v>370.8771281757093</v>
+        <v>367.6119462128358</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3329107205184738</v>
+        <v>0.3402869264620645</v>
       </c>
       <c r="T65">
-        <v>1.410681828260087</v>
+        <v>1.446923873375424</v>
       </c>
       <c r="U65">
         <v>0.1946487374989669</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.376121698548955</v>
+        <v>2.338994797009128</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.224654950965801</v>
+        <v>0.2255773975478005</v>
       </c>
       <c r="C66">
-        <v>781.5616214227784</v>
+        <v>756.8610200895671</v>
       </c>
       <c r="D66">
-        <v>1223.109621422778</v>
+        <v>1218.866020089567</v>
       </c>
       <c r="E66">
-        <v>197.848</v>
+        <v>218.3050000000001</v>
       </c>
       <c r="F66">
-        <v>1309.248</v>
+        <v>1329.705</v>
       </c>
       <c r="G66">
         <v>867.7</v>
@@ -6693,28 +6693,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M66">
-        <v>254.8434702730474</v>
+        <v>258.8253994960638</v>
       </c>
       <c r="N66">
-        <v>341.2340807473607</v>
+        <v>337.2521515243444</v>
       </c>
       <c r="O66">
-        <v>61.42213453452493</v>
+        <v>60.70538727438198</v>
       </c>
       <c r="P66">
-        <v>279.8119462128358</v>
+        <v>276.5467642499624</v>
       </c>
       <c r="Q66">
-        <v>367.6119462128358</v>
+        <v>364.3467642499625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3402869264620645</v>
+        <v>0.348084629888146</v>
       </c>
       <c r="T66">
-        <v>1.446923873375424</v>
+        <v>1.485236892497352</v>
       </c>
       <c r="U66">
         <v>0.1946487374989669</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.338994797009128</v>
+        <v>2.303010261670526</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2255773975478005</v>
+        <v>0.2264998441297999</v>
       </c>
       <c r="C67">
-        <v>756.8610200895671</v>
+        <v>732.1897634501927</v>
       </c>
       <c r="D67">
-        <v>1218.866020089567</v>
+        <v>1214.651763450193</v>
       </c>
       <c r="E67">
-        <v>218.3050000000001</v>
+        <v>238.7619999999999</v>
       </c>
       <c r="F67">
-        <v>1329.705</v>
+        <v>1350.162</v>
       </c>
       <c r="G67">
         <v>867.7</v>
@@ -6775,28 +6775,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M67">
-        <v>258.8253994960638</v>
+        <v>262.8073287190801</v>
       </c>
       <c r="N67">
-        <v>337.2521515243444</v>
+        <v>333.270222301328</v>
       </c>
       <c r="O67">
-        <v>60.70538727438198</v>
+        <v>59.98864001423905</v>
       </c>
       <c r="P67">
-        <v>276.5467642499624</v>
+        <v>273.281582287089</v>
       </c>
       <c r="Q67">
-        <v>364.3467642499625</v>
+        <v>361.0815822870891</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.348084629888146</v>
+        <v>0.3563410217510559</v>
       </c>
       <c r="T67">
-        <v>1.485236892497352</v>
+        <v>1.525803618626451</v>
       </c>
       <c r="U67">
         <v>0.1946487374989669</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.303010261670526</v>
+        <v>2.26811616679673</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2264998441297999</v>
+        <v>0.2274222907117993</v>
       </c>
       <c r="C68">
-        <v>732.1897634501927</v>
+        <v>707.5475481736134</v>
       </c>
       <c r="D68">
-        <v>1214.651763450193</v>
+        <v>1210.466548173614</v>
       </c>
       <c r="E68">
-        <v>238.7619999999999</v>
+        <v>259.2190000000001</v>
       </c>
       <c r="F68">
-        <v>1350.162</v>
+        <v>1370.619</v>
       </c>
       <c r="G68">
         <v>867.7</v>
@@ -6857,28 +6857,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M68">
-        <v>262.8073287190801</v>
+        <v>266.7892579420965</v>
       </c>
       <c r="N68">
-        <v>333.270222301328</v>
+        <v>329.2882930783117</v>
       </c>
       <c r="O68">
-        <v>59.98864001423905</v>
+        <v>59.27189275409609</v>
       </c>
       <c r="P68">
-        <v>273.281582287089</v>
+        <v>270.0164003242156</v>
       </c>
       <c r="Q68">
-        <v>361.0815822870891</v>
+        <v>357.8164003242156</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3563410217510559</v>
+        <v>0.3650978009995966</v>
       </c>
       <c r="T68">
-        <v>1.525803618626451</v>
+        <v>1.56882893421792</v>
       </c>
       <c r="U68">
         <v>0.1946487374989669</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.26811616679673</v>
+        <v>2.234263686695286</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2274222907117993</v>
+        <v>0.2283447372937987</v>
       </c>
       <c r="C69">
-        <v>707.5475481736134</v>
+        <v>682.934075095076</v>
       </c>
       <c r="D69">
-        <v>1210.466548173614</v>
+        <v>1206.310075095076</v>
       </c>
       <c r="E69">
-        <v>259.2190000000001</v>
+        <v>279.6759999999999</v>
       </c>
       <c r="F69">
-        <v>1370.619</v>
+        <v>1391.076</v>
       </c>
       <c r="G69">
         <v>867.7</v>
@@ -6939,28 +6939,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M69">
-        <v>266.7892579420965</v>
+        <v>270.7711871651128</v>
       </c>
       <c r="N69">
-        <v>329.2882930783117</v>
+        <v>325.3063638552953</v>
       </c>
       <c r="O69">
-        <v>59.27189275409609</v>
+        <v>58.55514549395315</v>
       </c>
       <c r="P69">
-        <v>270.0164003242156</v>
+        <v>266.7512183613421</v>
       </c>
       <c r="Q69">
-        <v>357.8164003242156</v>
+        <v>354.5512183613422</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3650978009995966</v>
+        <v>0.3744018789511712</v>
       </c>
       <c r="T69">
-        <v>1.56882893421792</v>
+        <v>1.614543332033857</v>
       </c>
       <c r="U69">
         <v>0.1946487374989669</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.234263686695286</v>
+        <v>2.201406867773296</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2283447372937987</v>
+        <v>0.2292671838757981</v>
       </c>
       <c r="C70">
-        <v>682.934075095076</v>
+        <v>658.3490491448249</v>
       </c>
       <c r="D70">
-        <v>1206.310075095076</v>
+        <v>1202.182049144825</v>
       </c>
       <c r="E70">
-        <v>279.6759999999999</v>
+        <v>300.133</v>
       </c>
       <c r="F70">
-        <v>1391.076</v>
+        <v>1411.533</v>
       </c>
       <c r="G70">
         <v>867.7</v>
@@ -7021,28 +7021,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M70">
-        <v>270.7711871651128</v>
+        <v>274.7531163881292</v>
       </c>
       <c r="N70">
-        <v>325.3063638552953</v>
+        <v>321.3244346322789</v>
       </c>
       <c r="O70">
-        <v>58.55514549395315</v>
+        <v>57.8383982338102</v>
       </c>
       <c r="P70">
-        <v>266.7512183613421</v>
+        <v>263.4860363984687</v>
       </c>
       <c r="Q70">
-        <v>354.5512183613422</v>
+        <v>351.2860363984688</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3744018789511712</v>
+        <v>0.3843062199963958</v>
       </c>
       <c r="T70">
-        <v>1.614543332033857</v>
+        <v>1.663207045837918</v>
       </c>
       <c r="U70">
         <v>0.1946487374989669</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.201406867773296</v>
+        <v>2.169502420414263</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2292671838757981</v>
+        <v>0.2301896304577976</v>
       </c>
       <c r="C71">
-        <v>658.3490491448249</v>
+        <v>633.7921792782777</v>
       </c>
       <c r="D71">
-        <v>1202.182049144825</v>
+        <v>1198.082179278278</v>
       </c>
       <c r="E71">
-        <v>300.133</v>
+        <v>320.5900000000001</v>
       </c>
       <c r="F71">
-        <v>1411.533</v>
+        <v>1431.99</v>
       </c>
       <c r="G71">
         <v>867.7</v>
@@ -7103,28 +7103,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M71">
-        <v>274.7531163881292</v>
+        <v>278.7350456111456</v>
       </c>
       <c r="N71">
-        <v>321.3244346322789</v>
+        <v>317.3425054092625</v>
       </c>
       <c r="O71">
-        <v>57.8383982338102</v>
+        <v>57.12165097366725</v>
       </c>
       <c r="P71">
-        <v>263.4860363984687</v>
+        <v>260.2208544355952</v>
       </c>
       <c r="Q71">
-        <v>351.2860363984688</v>
+        <v>348.0208544355953</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3843062199963958</v>
+        <v>0.3948708504446352</v>
       </c>
       <c r="T71">
-        <v>1.663207045837918</v>
+        <v>1.715115007228916</v>
       </c>
       <c r="U71">
         <v>0.1946487374989669</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.169502420414263</v>
+        <v>2.138509528694059</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2301896304577976</v>
+        <v>0.231112077039797</v>
       </c>
       <c r="C72">
-        <v>633.7921792782777</v>
+        <v>609.2631784076229</v>
       </c>
       <c r="D72">
-        <v>1198.082179278278</v>
+        <v>1194.010178407623</v>
       </c>
       <c r="E72">
-        <v>320.5900000000001</v>
+        <v>341.047</v>
       </c>
       <c r="F72">
-        <v>1431.99</v>
+        <v>1452.447</v>
       </c>
       <c r="G72">
         <v>867.7</v>
@@ -7185,28 +7185,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M72">
-        <v>278.7350456111456</v>
+        <v>282.7169748341619</v>
       </c>
       <c r="N72">
-        <v>317.3425054092625</v>
+        <v>313.3605761862462</v>
       </c>
       <c r="O72">
-        <v>57.12165097366725</v>
+        <v>56.40490371352431</v>
       </c>
       <c r="P72">
-        <v>260.2208544355952</v>
+        <v>256.9556724727219</v>
       </c>
       <c r="Q72">
-        <v>348.0208544355953</v>
+        <v>344.7556724727219</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3948708504446352</v>
+        <v>0.4061640760962016</v>
       </c>
       <c r="T72">
-        <v>1.715115007228916</v>
+        <v>1.770602828026191</v>
       </c>
       <c r="U72">
         <v>0.1946487374989669</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.138509528694059</v>
+        <v>2.108389676177242</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.231112077039797</v>
+        <v>0.2320345236217964</v>
       </c>
       <c r="C73">
-        <v>609.2631784076232</v>
+        <v>584.7617633348041</v>
       </c>
       <c r="D73">
-        <v>1194.010178407623</v>
+        <v>1189.965763334804</v>
       </c>
       <c r="E73">
-        <v>341.0469999999998</v>
+        <v>361.5039999999999</v>
       </c>
       <c r="F73">
-        <v>1452.447</v>
+        <v>1472.904</v>
       </c>
       <c r="G73">
         <v>867.7</v>
@@ -7267,28 +7267,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M73">
-        <v>282.7169748341619</v>
+        <v>286.6989040571783</v>
       </c>
       <c r="N73">
-        <v>313.3605761862462</v>
+        <v>309.3786469632299</v>
       </c>
       <c r="O73">
-        <v>56.40490371352432</v>
+        <v>55.68815645338137</v>
       </c>
       <c r="P73">
-        <v>256.9556724727219</v>
+        <v>253.6904905098485</v>
       </c>
       <c r="Q73">
-        <v>344.755672472722</v>
+        <v>341.4904905098485</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4061640760962015</v>
+        <v>0.4182639607228797</v>
       </c>
       <c r="T73">
-        <v>1.77060282802619</v>
+        <v>1.830054064594698</v>
       </c>
       <c r="U73">
         <v>0.1946487374989669</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.108389676177242</v>
+        <v>2.079106486230336</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2320345236217964</v>
+        <v>0.2329569702037958</v>
       </c>
       <c r="C74">
-        <v>584.7617633348041</v>
+        <v>560.2876546858658</v>
       </c>
       <c r="D74">
-        <v>1189.965763334804</v>
+        <v>1185.948654685866</v>
       </c>
       <c r="E74">
-        <v>361.5039999999999</v>
+        <v>381.961</v>
       </c>
       <c r="F74">
-        <v>1472.904</v>
+        <v>1493.361</v>
       </c>
       <c r="G74">
         <v>867.7</v>
@@ -7349,28 +7349,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M74">
-        <v>286.6989040571783</v>
+        <v>290.6808332801947</v>
       </c>
       <c r="N74">
-        <v>309.3786469632299</v>
+        <v>305.3967177402134</v>
       </c>
       <c r="O74">
-        <v>55.68815645338137</v>
+        <v>54.97140919323842</v>
       </c>
       <c r="P74">
-        <v>253.6904905098485</v>
+        <v>250.425308546975</v>
       </c>
       <c r="Q74">
-        <v>341.4904905098485</v>
+        <v>338.2253085469751</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4182639607228797</v>
+        <v>0.4312601330996823</v>
       </c>
       <c r="T74">
-        <v>1.830054064594698</v>
+        <v>1.893909096464577</v>
       </c>
       <c r="U74">
         <v>0.1946487374989669</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.079106486230336</v>
+        <v>2.050625575460057</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2329569702037958</v>
+        <v>0.2338794167857952</v>
       </c>
       <c r="C75">
-        <v>560.2876546858658</v>
+        <v>535.8405768466257</v>
       </c>
       <c r="D75">
-        <v>1185.948654685866</v>
+        <v>1181.958576846626</v>
       </c>
       <c r="E75">
-        <v>381.961</v>
+        <v>402.4179999999999</v>
       </c>
       <c r="F75">
-        <v>1493.361</v>
+        <v>1513.818</v>
       </c>
       <c r="G75">
         <v>867.7</v>
@@ -7431,28 +7431,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M75">
-        <v>290.6808332801947</v>
+        <v>294.662762503211</v>
       </c>
       <c r="N75">
-        <v>305.3967177402134</v>
+        <v>301.4147885171971</v>
       </c>
       <c r="O75">
-        <v>54.97140919323842</v>
+        <v>54.25466193309548</v>
       </c>
       <c r="P75">
-        <v>250.425308546975</v>
+        <v>247.1601265841016</v>
       </c>
       <c r="Q75">
-        <v>338.2253085469751</v>
+        <v>334.9601265841017</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4312601330996823</v>
+        <v>0.4452560110439312</v>
       </c>
       <c r="T75">
-        <v>1.893909096464577</v>
+        <v>1.962676053862908</v>
       </c>
       <c r="U75">
         <v>0.1946487374989669</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.050625575460057</v>
+        <v>2.022914419034922</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2338794167857952</v>
+        <v>0.2435348633677947</v>
       </c>
       <c r="C76">
-        <v>535.8405768466257</v>
+        <v>475.17509486727</v>
       </c>
       <c r="D76">
-        <v>1181.958576846626</v>
+        <v>1141.75009486727</v>
       </c>
       <c r="E76">
-        <v>402.4179999999999</v>
+        <v>422.875</v>
       </c>
       <c r="F76">
-        <v>1513.818</v>
+        <v>1534.275</v>
       </c>
       <c r="G76">
         <v>867.7</v>
@@ -7513,45 +7513,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M76">
-        <v>294.662762503211</v>
+        <v>320.4313967262274</v>
       </c>
       <c r="N76">
-        <v>301.4147885171971</v>
+        <v>275.6461542941807</v>
       </c>
       <c r="O76">
-        <v>54.25466193309548</v>
+        <v>49.61630777295252</v>
       </c>
       <c r="P76">
-        <v>247.1601265841016</v>
+        <v>226.0298465212282</v>
       </c>
       <c r="Q76">
-        <v>334.9601265841017</v>
+        <v>313.8298465212282</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4452560110439312</v>
+        <v>0.46037155922372</v>
       </c>
       <c r="T76">
-        <v>1.962676053862908</v>
+        <v>2.036944367853106</v>
       </c>
       <c r="U76">
-        <v>0.1946487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V76">
         <v>0.18</v>
       </c>
       <c r="W76">
-        <v>0.1596119647491528</v>
+        <v>0.1712559647491529</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.022914419034922</v>
+        <v>1.860234537284401</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2435348633677947</v>
+        <v>0.2445737499497941</v>
       </c>
       <c r="C77">
-        <v>475.17509486727</v>
+        <v>450.5542405828726</v>
       </c>
       <c r="D77">
-        <v>1141.75009486727</v>
+        <v>1137.586240582873</v>
       </c>
       <c r="E77">
-        <v>422.875</v>
+        <v>443.3319999999999</v>
       </c>
       <c r="F77">
-        <v>1534.275</v>
+        <v>1554.732</v>
       </c>
       <c r="G77">
         <v>867.7</v>
@@ -7595,28 +7595,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M77">
-        <v>320.4313967262274</v>
+        <v>324.7038153492438</v>
       </c>
       <c r="N77">
-        <v>275.6461542941807</v>
+        <v>271.3737356711644</v>
       </c>
       <c r="O77">
-        <v>49.61630777295252</v>
+        <v>48.84727242080958</v>
       </c>
       <c r="P77">
-        <v>226.0298465212282</v>
+        <v>222.5264632503548</v>
       </c>
       <c r="Q77">
-        <v>313.8298465212282</v>
+        <v>310.3264632503548</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.46037155922372</v>
+        <v>0.4767467364184913</v>
       </c>
       <c r="T77">
-        <v>2.036944367853106</v>
+        <v>2.117401708009154</v>
       </c>
       <c r="U77">
         <v>0.2088487374989669</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.860234537284401</v>
+        <v>1.835757767056975</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2445737499497941</v>
+        <v>0.2456126365317935</v>
       </c>
       <c r="C78">
-        <v>450.5542405828726</v>
+        <v>425.9636463062434</v>
       </c>
       <c r="D78">
-        <v>1137.586240582873</v>
+        <v>1133.452646306243</v>
       </c>
       <c r="E78">
-        <v>443.3319999999999</v>
+        <v>463.789</v>
       </c>
       <c r="F78">
-        <v>1554.732</v>
+        <v>1575.189</v>
       </c>
       <c r="G78">
         <v>867.7</v>
@@ -7677,28 +7677,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M78">
-        <v>324.7038153492438</v>
+        <v>328.9762339722602</v>
       </c>
       <c r="N78">
-        <v>271.3737356711644</v>
+        <v>267.101317048148</v>
       </c>
       <c r="O78">
-        <v>48.84727242080958</v>
+        <v>48.07823706866663</v>
       </c>
       <c r="P78">
-        <v>222.5264632503548</v>
+        <v>219.0230799794813</v>
       </c>
       <c r="Q78">
-        <v>310.3264632503548</v>
+        <v>306.8230799794814</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4767467364184913</v>
+        <v>0.4945458420649818</v>
       </c>
       <c r="T78">
-        <v>2.117401708009154</v>
+        <v>2.204855338613553</v>
       </c>
       <c r="U78">
         <v>0.2088487374989669</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.835757767056975</v>
+        <v>1.811916757095196</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2456126365317935</v>
+        <v>0.2466515231137929</v>
       </c>
       <c r="C79">
-        <v>425.9636463062434</v>
+        <v>401.4029833684981</v>
       </c>
       <c r="D79">
-        <v>1133.452646306243</v>
+        <v>1129.348983368498</v>
       </c>
       <c r="E79">
-        <v>463.789</v>
+        <v>484.2460000000001</v>
       </c>
       <c r="F79">
-        <v>1575.189</v>
+        <v>1595.646</v>
       </c>
       <c r="G79">
         <v>867.7</v>
@@ -7759,28 +7759,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M79">
-        <v>328.9762339722602</v>
+        <v>333.2486525952766</v>
       </c>
       <c r="N79">
-        <v>267.101317048148</v>
+        <v>262.8288984251316</v>
       </c>
       <c r="O79">
-        <v>48.07823706866663</v>
+        <v>47.30920171652368</v>
       </c>
       <c r="P79">
-        <v>219.0230799794813</v>
+        <v>215.5196967086079</v>
       </c>
       <c r="Q79">
-        <v>306.8230799794814</v>
+        <v>303.3196967086079</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4945458420649818</v>
+        <v>0.5139630482247896</v>
       </c>
       <c r="T79">
-        <v>2.204855338613553</v>
+        <v>2.300259299272899</v>
       </c>
       <c r="U79">
         <v>0.2088487374989669</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.811916757095196</v>
+        <v>1.788687055081155</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2466515231137929</v>
+        <v>0.2476904096957923</v>
       </c>
       <c r="C80">
-        <v>401.4029833684981</v>
+        <v>376.8719278433614</v>
       </c>
       <c r="D80">
-        <v>1129.348983368498</v>
+        <v>1125.274927843361</v>
       </c>
       <c r="E80">
-        <v>484.2460000000001</v>
+        <v>504.703</v>
       </c>
       <c r="F80">
-        <v>1595.646</v>
+        <v>1616.103</v>
       </c>
       <c r="G80">
         <v>867.7</v>
@@ -7841,28 +7841,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M80">
-        <v>333.2486525952766</v>
+        <v>337.5210712182929</v>
       </c>
       <c r="N80">
-        <v>262.8288984251316</v>
+        <v>258.5564798021152</v>
       </c>
       <c r="O80">
-        <v>47.30920171652368</v>
+        <v>46.54016636438074</v>
       </c>
       <c r="P80">
-        <v>215.5196967086079</v>
+        <v>212.0163134377345</v>
       </c>
       <c r="Q80">
-        <v>303.3196967086079</v>
+        <v>299.8163134377346</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5139630482247896</v>
+        <v>0.5352295121141029</v>
       </c>
       <c r="T80">
-        <v>2.300259299272899</v>
+        <v>2.40474935142361</v>
       </c>
       <c r="U80">
         <v>0.2088487374989669</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.788687055081155</v>
+        <v>1.766045446788989</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2476904096957923</v>
+        <v>0.2487292962777918</v>
       </c>
       <c r="C81">
-        <v>376.8719278433614</v>
+        <v>352.3701604619314</v>
       </c>
       <c r="D81">
-        <v>1125.274927843361</v>
+        <v>1121.230160461932</v>
       </c>
       <c r="E81">
-        <v>504.703</v>
+        <v>525.1600000000001</v>
       </c>
       <c r="F81">
-        <v>1616.103</v>
+        <v>1636.56</v>
       </c>
       <c r="G81">
         <v>867.7</v>
@@ -7923,28 +7923,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M81">
-        <v>337.5210712182929</v>
+        <v>341.7934898413093</v>
       </c>
       <c r="N81">
-        <v>258.5564798021152</v>
+        <v>254.2840611790988</v>
       </c>
       <c r="O81">
-        <v>46.54016636438074</v>
+        <v>45.77113101223779</v>
       </c>
       <c r="P81">
-        <v>212.0163134377345</v>
+        <v>208.5129301668611</v>
       </c>
       <c r="Q81">
-        <v>299.8163134377346</v>
+        <v>296.3129301668611</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5352295121141029</v>
+        <v>0.5586226223923474</v>
       </c>
       <c r="T81">
-        <v>2.40474935142361</v>
+        <v>2.519688408789392</v>
       </c>
       <c r="U81">
         <v>0.2088487374989669</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.766045446788989</v>
+        <v>1.743969878704126</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2487292962777918</v>
+        <v>0.2497681828597912</v>
       </c>
       <c r="C82">
-        <v>352.3701604619314</v>
+        <v>327.8973665292765</v>
       </c>
       <c r="D82">
-        <v>1121.230160461932</v>
+        <v>1117.214366529277</v>
       </c>
       <c r="E82">
-        <v>525.1600000000001</v>
+        <v>545.617</v>
       </c>
       <c r="F82">
-        <v>1636.56</v>
+        <v>1657.017</v>
       </c>
       <c r="G82">
         <v>867.7</v>
@@ -8005,28 +8005,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M82">
-        <v>341.7934898413093</v>
+        <v>346.0659084643256</v>
       </c>
       <c r="N82">
-        <v>254.2840611790988</v>
+        <v>250.0116425560825</v>
       </c>
       <c r="O82">
-        <v>45.77113101223779</v>
+        <v>45.00209566009485</v>
       </c>
       <c r="P82">
-        <v>208.5129301668611</v>
+        <v>205.0095468959877</v>
       </c>
       <c r="Q82">
-        <v>296.3129301668611</v>
+        <v>292.8095468959878</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5586226223923474</v>
+        <v>0.5844781653314599</v>
       </c>
       <c r="T82">
-        <v>2.519688408789392</v>
+        <v>2.646726314298941</v>
       </c>
       <c r="U82">
         <v>0.2088487374989669</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.743969878704126</v>
+        <v>1.722439386374446</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2497681828597912</v>
+        <v>0.2508070694417906</v>
       </c>
       <c r="C83">
-        <v>327.8973665292765</v>
+        <v>303.4532358428146</v>
       </c>
       <c r="D83">
-        <v>1117.214366529277</v>
+        <v>1113.227235842815</v>
       </c>
       <c r="E83">
-        <v>545.617</v>
+        <v>566.0740000000001</v>
       </c>
       <c r="F83">
-        <v>1657.017</v>
+        <v>1677.474</v>
       </c>
       <c r="G83">
         <v>867.7</v>
@@ -8087,28 +8087,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M83">
-        <v>346.0659084643256</v>
+        <v>350.338327087342</v>
       </c>
       <c r="N83">
-        <v>250.0116425560825</v>
+        <v>245.7392239330661</v>
       </c>
       <c r="O83">
-        <v>45.00209566009485</v>
+        <v>44.2330603079519</v>
       </c>
       <c r="P83">
-        <v>205.0095468959877</v>
+        <v>201.5061636251142</v>
       </c>
       <c r="Q83">
-        <v>292.8095468959878</v>
+        <v>289.3061636251143</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5844781653314599</v>
+        <v>0.6132065463749181</v>
       </c>
       <c r="T83">
-        <v>2.646726314298941</v>
+        <v>2.787879542642884</v>
       </c>
       <c r="U83">
         <v>0.2088487374989669</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.722439386374446</v>
+        <v>1.701434028004026</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2508070694417906</v>
+        <v>0.25184595602379</v>
       </c>
       <c r="C84">
-        <v>303.4532358428146</v>
+        <v>279.0374626124399</v>
       </c>
       <c r="D84">
-        <v>1113.227235842815</v>
+        <v>1109.26846261244</v>
       </c>
       <c r="E84">
-        <v>566.0740000000001</v>
+        <v>586.5310000000002</v>
       </c>
       <c r="F84">
-        <v>1677.474</v>
+        <v>1697.931</v>
       </c>
       <c r="G84">
         <v>867.7</v>
@@ -8169,28 +8169,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M84">
-        <v>350.338327087342</v>
+        <v>354.6107457103584</v>
       </c>
       <c r="N84">
-        <v>245.7392239330661</v>
+        <v>241.4668053100497</v>
       </c>
       <c r="O84">
-        <v>44.2330603079519</v>
+        <v>43.46402495580895</v>
       </c>
       <c r="P84">
-        <v>201.5061636251142</v>
+        <v>198.0027803542408</v>
       </c>
       <c r="Q84">
-        <v>289.3061636251143</v>
+        <v>285.8027803542408</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6132065463749181</v>
+        <v>0.645314736952901</v>
       </c>
       <c r="T84">
-        <v>2.787879542642884</v>
+        <v>2.945639033144939</v>
       </c>
       <c r="U84">
         <v>0.2088487374989669</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.701434028004026</v>
+        <v>1.68093482284735</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.25184595602379</v>
+        <v>0.2528848426057895</v>
       </c>
       <c r="C85">
-        <v>279.0374626124399</v>
+        <v>254.6497453823411</v>
       </c>
       <c r="D85">
-        <v>1109.26846261244</v>
+        <v>1105.337745382341</v>
       </c>
       <c r="E85">
-        <v>586.5310000000002</v>
+        <v>606.9880000000001</v>
       </c>
       <c r="F85">
-        <v>1697.931</v>
+        <v>1718.388</v>
       </c>
       <c r="G85">
         <v>867.7</v>
@@ -8251,28 +8251,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M85">
-        <v>354.6107457103584</v>
+        <v>358.8831643333747</v>
       </c>
       <c r="N85">
-        <v>241.4668053100497</v>
+        <v>237.1943866870334</v>
       </c>
       <c r="O85">
-        <v>43.46402495580895</v>
+        <v>42.69498960366601</v>
       </c>
       <c r="P85">
-        <v>198.0027803542408</v>
+        <v>194.4993970833674</v>
       </c>
       <c r="Q85">
-        <v>285.8027803542408</v>
+        <v>282.2993970833675</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.645314736952901</v>
+        <v>0.6814364513531318</v>
       </c>
       <c r="T85">
-        <v>2.945639033144939</v>
+        <v>3.12311845995975</v>
       </c>
       <c r="U85">
         <v>0.2088487374989669</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.68093482284735</v>
+        <v>1.66092369400393</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2528848426057894</v>
+        <v>0.2539237291877888</v>
       </c>
       <c r="C86">
-        <v>254.6497453823415</v>
+        <v>230.289786954482</v>
       </c>
       <c r="D86">
-        <v>1105.337745382341</v>
+        <v>1101.434786954482</v>
       </c>
       <c r="E86">
-        <v>606.9879999999998</v>
+        <v>627.4449999999999</v>
       </c>
       <c r="F86">
-        <v>1718.388</v>
+        <v>1738.845</v>
       </c>
       <c r="G86">
         <v>867.7</v>
@@ -8333,28 +8333,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M86">
-        <v>358.8831643333747</v>
+        <v>363.1555829563911</v>
       </c>
       <c r="N86">
-        <v>237.1943866870334</v>
+        <v>232.9219680640171</v>
       </c>
       <c r="O86">
-        <v>42.69498960366602</v>
+        <v>41.92595425152307</v>
       </c>
       <c r="P86">
-        <v>194.4993970833674</v>
+        <v>190.996013812494</v>
       </c>
       <c r="Q86">
-        <v>282.2993970833675</v>
+        <v>278.796013812494</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6814364513531314</v>
+        <v>0.7223743943400593</v>
       </c>
       <c r="T86">
-        <v>3.123118459959748</v>
+        <v>3.324261810349867</v>
       </c>
       <c r="U86">
         <v>0.2088487374989669</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.66092369400393</v>
+        <v>1.641383415250942</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2539237291877888</v>
+        <v>0.2549626157697883</v>
       </c>
       <c r="C87">
-        <v>230.289786954482</v>
+        <v>205.9572943136914</v>
       </c>
       <c r="D87">
-        <v>1101.434786954482</v>
+        <v>1097.559294313691</v>
       </c>
       <c r="E87">
-        <v>627.4449999999999</v>
+        <v>647.9019999999998</v>
       </c>
       <c r="F87">
-        <v>1738.845</v>
+        <v>1759.302</v>
       </c>
       <c r="G87">
         <v>867.7</v>
@@ -8415,28 +8415,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M87">
-        <v>363.1555829563911</v>
+        <v>367.4280015794074</v>
       </c>
       <c r="N87">
-        <v>232.9219680640171</v>
+        <v>228.6495494410007</v>
       </c>
       <c r="O87">
-        <v>41.92595425152307</v>
+        <v>41.15691889938013</v>
       </c>
       <c r="P87">
-        <v>190.996013812494</v>
+        <v>187.4926305416206</v>
       </c>
       <c r="Q87">
-        <v>278.796013812494</v>
+        <v>275.2926305416207</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7223743943400593</v>
+        <v>0.7691606148965486</v>
       </c>
       <c r="T87">
-        <v>3.324261810349867</v>
+        <v>3.554139925081432</v>
       </c>
       <c r="U87">
         <v>0.2088487374989669</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.641383415250942</v>
+        <v>1.622297561585234</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2549626157697883</v>
+        <v>0.2560015023517876</v>
       </c>
       <c r="C88">
-        <v>205.9572943136914</v>
+        <v>181.6519785543362</v>
       </c>
       <c r="D88">
-        <v>1097.559294313691</v>
+        <v>1093.710978554336</v>
       </c>
       <c r="E88">
-        <v>647.9019999999998</v>
+        <v>668.3589999999999</v>
       </c>
       <c r="F88">
-        <v>1759.302</v>
+        <v>1779.759</v>
       </c>
       <c r="G88">
         <v>867.7</v>
@@ -8497,28 +8497,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M88">
-        <v>367.4280015794074</v>
+        <v>371.7004202024238</v>
       </c>
       <c r="N88">
-        <v>228.6495494410007</v>
+        <v>224.3771308179843</v>
       </c>
       <c r="O88">
-        <v>41.15691889938013</v>
+        <v>40.38788354723717</v>
       </c>
       <c r="P88">
-        <v>187.4926305416206</v>
+        <v>183.9892472707471</v>
       </c>
       <c r="Q88">
-        <v>275.2926305416207</v>
+        <v>271.7892472707472</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7691606148965486</v>
+        <v>0.8231447155386514</v>
       </c>
       <c r="T88">
-        <v>3.554139925081432</v>
+        <v>3.819383903617851</v>
       </c>
       <c r="U88">
         <v>0.2088487374989669</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.622297561585234</v>
+        <v>1.603650463176208</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2560015023517876</v>
+        <v>0.2570403889337871</v>
       </c>
       <c r="C89">
-        <v>181.6519785543362</v>
+        <v>157.3735548085244</v>
       </c>
       <c r="D89">
-        <v>1093.710978554336</v>
+        <v>1089.889554808525</v>
       </c>
       <c r="E89">
-        <v>668.3589999999999</v>
+        <v>688.816</v>
       </c>
       <c r="F89">
-        <v>1779.759</v>
+        <v>1800.216</v>
       </c>
       <c r="G89">
         <v>867.7</v>
@@ -8579,28 +8579,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M89">
-        <v>371.7004202024238</v>
+        <v>375.9728388254402</v>
       </c>
       <c r="N89">
-        <v>224.3771308179843</v>
+        <v>220.1047121949679</v>
       </c>
       <c r="O89">
-        <v>40.38788354723717</v>
+        <v>39.61884819509422</v>
       </c>
       <c r="P89">
-        <v>183.9892472707471</v>
+        <v>180.4858639998737</v>
       </c>
       <c r="Q89">
-        <v>271.7892472707472</v>
+        <v>268.2858639998738</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8231447155386514</v>
+        <v>0.8861261662877716</v>
       </c>
       <c r="T89">
-        <v>3.819383903617851</v>
+        <v>4.128835211910343</v>
       </c>
       <c r="U89">
         <v>0.2088487374989669</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.603650463176208</v>
+        <v>1.585427162458297</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2570403889337871</v>
+        <v>0.2580792755157865</v>
       </c>
       <c r="C90">
-        <v>157.3735548085244</v>
+        <v>133.1217421758147</v>
       </c>
       <c r="D90">
-        <v>1089.889554808525</v>
+        <v>1086.094742175815</v>
       </c>
       <c r="E90">
-        <v>688.816</v>
+        <v>709.2729999999999</v>
       </c>
       <c r="F90">
-        <v>1800.216</v>
+        <v>1820.673</v>
       </c>
       <c r="G90">
         <v>867.7</v>
@@ -8661,28 +8661,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M90">
-        <v>375.9728388254402</v>
+        <v>380.2452574484565</v>
       </c>
       <c r="N90">
-        <v>220.1047121949679</v>
+        <v>215.8322935719516</v>
       </c>
       <c r="O90">
-        <v>39.61884819509422</v>
+        <v>38.84981284295129</v>
       </c>
       <c r="P90">
-        <v>180.4858639998737</v>
+        <v>176.9824807290003</v>
       </c>
       <c r="Q90">
-        <v>268.2858639998738</v>
+        <v>264.7824807290004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8861261662877716</v>
+        <v>0.9605587899003681</v>
       </c>
       <c r="T90">
-        <v>4.128835211910343</v>
+        <v>4.494550394437832</v>
       </c>
       <c r="U90">
         <v>0.2088487374989669</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.585427162458297</v>
+        <v>1.567613374116068</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2580792755157865</v>
+        <v>0.2591181620977859</v>
       </c>
       <c r="C91">
-        <v>133.1217421758147</v>
+        <v>108.8962636543822</v>
       </c>
       <c r="D91">
-        <v>1086.094742175815</v>
+        <v>1082.326263654382</v>
       </c>
       <c r="E91">
-        <v>709.2729999999999</v>
+        <v>729.73</v>
       </c>
       <c r="F91">
-        <v>1820.673</v>
+        <v>1841.13</v>
       </c>
       <c r="G91">
         <v>867.7</v>
@@ -8743,28 +8743,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M91">
-        <v>380.2452574484565</v>
+        <v>384.5176760714729</v>
       </c>
       <c r="N91">
-        <v>215.8322935719516</v>
+        <v>211.5598749489352</v>
       </c>
       <c r="O91">
-        <v>38.84981284295129</v>
+        <v>38.08077749080834</v>
       </c>
       <c r="P91">
-        <v>176.9824807290003</v>
+        <v>173.4790974581269</v>
       </c>
       <c r="Q91">
-        <v>264.7824807290004</v>
+        <v>261.2790974581269</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9605587899003681</v>
+        <v>1.049877938235484</v>
       </c>
       <c r="T91">
-        <v>4.494550394437832</v>
+        <v>4.933408613470819</v>
       </c>
       <c r="U91">
         <v>0.2088487374989669</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.567613374116068</v>
+        <v>1.550195447737001</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2591181620977859</v>
+        <v>0.2601570486797854</v>
       </c>
       <c r="C92">
-        <v>108.8962636543822</v>
+        <v>84.69684607361955</v>
       </c>
       <c r="D92">
-        <v>1082.326263654382</v>
+        <v>1078.58384607362</v>
       </c>
       <c r="E92">
-        <v>729.73</v>
+        <v>750.1870000000001</v>
       </c>
       <c r="F92">
-        <v>1841.13</v>
+        <v>1861.587</v>
       </c>
       <c r="G92">
         <v>867.7</v>
@@ -8825,28 +8825,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M92">
-        <v>384.5176760714729</v>
+        <v>388.7900946944893</v>
       </c>
       <c r="N92">
-        <v>211.5598749489352</v>
+        <v>207.2874563259188</v>
       </c>
       <c r="O92">
-        <v>38.08077749080834</v>
+        <v>37.31174213866539</v>
       </c>
       <c r="P92">
-        <v>173.4790974581269</v>
+        <v>169.9757141872534</v>
       </c>
       <c r="Q92">
-        <v>261.2790974581269</v>
+        <v>257.7757141872535</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.049877938235484</v>
+        <v>1.159045786200626</v>
       </c>
       <c r="T92">
-        <v>4.933408613470819</v>
+        <v>5.469790881177803</v>
       </c>
       <c r="U92">
         <v>0.2088487374989669</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.550195447737001</v>
+        <v>1.533160332926704</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2601570486797854</v>
+        <v>0.2611959352617848</v>
       </c>
       <c r="C93">
-        <v>84.69684607361955</v>
+        <v>60.5232200281273</v>
       </c>
       <c r="D93">
-        <v>1078.58384607362</v>
+        <v>1074.867220028127</v>
       </c>
       <c r="E93">
-        <v>750.1870000000001</v>
+        <v>770.644</v>
       </c>
       <c r="F93">
-        <v>1861.587</v>
+        <v>1882.044</v>
       </c>
       <c r="G93">
         <v>867.7</v>
@@ -8907,28 +8907,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M93">
-        <v>388.7900946944893</v>
+        <v>393.0625133175056</v>
       </c>
       <c r="N93">
-        <v>207.2874563259188</v>
+        <v>203.0150377029025</v>
       </c>
       <c r="O93">
-        <v>37.31174213866539</v>
+        <v>36.54270678652244</v>
       </c>
       <c r="P93">
-        <v>169.9757141872534</v>
+        <v>166.47233091638</v>
       </c>
       <c r="Q93">
-        <v>257.7757141872535</v>
+        <v>254.2723309163801</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.159045786200626</v>
+        <v>1.295505596157053</v>
       </c>
       <c r="T93">
-        <v>5.469790881177803</v>
+        <v>6.140268715811535</v>
       </c>
       <c r="U93">
         <v>0.2088487374989669</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.533160332926704</v>
+        <v>1.51649554669924</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2611959352617848</v>
+        <v>0.2622348218437842</v>
       </c>
       <c r="C94">
-        <v>60.5232200281273</v>
+        <v>36.37511981306329</v>
       </c>
       <c r="D94">
-        <v>1074.867220028127</v>
+        <v>1071.176119813063</v>
       </c>
       <c r="E94">
-        <v>770.644</v>
+        <v>791.1010000000001</v>
       </c>
       <c r="F94">
-        <v>1882.044</v>
+        <v>1902.501</v>
       </c>
       <c r="G94">
         <v>867.7</v>
@@ -8989,28 +8989,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M94">
-        <v>393.0625133175056</v>
+        <v>397.334931940522</v>
       </c>
       <c r="N94">
-        <v>203.0150377029025</v>
+        <v>198.7426190798861</v>
       </c>
       <c r="O94">
-        <v>36.54270678652244</v>
+        <v>35.77367143437949</v>
       </c>
       <c r="P94">
-        <v>166.47233091638</v>
+        <v>162.9689476455066</v>
       </c>
       <c r="Q94">
-        <v>254.2723309163801</v>
+        <v>250.7689476455067</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.295505596157053</v>
+        <v>1.470953923243888</v>
       </c>
       <c r="T94">
-        <v>6.140268715811535</v>
+        <v>7.002311646054904</v>
       </c>
       <c r="U94">
         <v>0.2088487374989669</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.51649554669924</v>
+        <v>1.500189142971291</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2622348218437842</v>
+        <v>0.2853185884257836</v>
       </c>
       <c r="C95">
-        <v>36.37511981306329</v>
+        <v>-60.0210827940432</v>
       </c>
       <c r="D95">
-        <v>1071.176119813063</v>
+        <v>995.2369172059567</v>
       </c>
       <c r="E95">
-        <v>791.1010000000001</v>
+        <v>811.558</v>
       </c>
       <c r="F95">
-        <v>1902.501</v>
+        <v>1922.958</v>
       </c>
       <c r="G95">
         <v>867.7</v>
@@ -9071,45 +9071,45 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M95">
-        <v>397.334931940522</v>
+        <v>456.6039493635383</v>
       </c>
       <c r="N95">
-        <v>198.7426190798861</v>
+        <v>139.4736016568698</v>
       </c>
       <c r="O95">
-        <v>35.77367143437949</v>
+        <v>25.10524829823656</v>
       </c>
       <c r="P95">
-        <v>162.9689476455066</v>
+        <v>114.3683533586332</v>
       </c>
       <c r="Q95">
-        <v>250.7689476455067</v>
+        <v>202.1683533586333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.470953923243888</v>
+        <v>1.704885026026334</v>
       </c>
       <c r="T95">
-        <v>7.002311646054904</v>
+        <v>8.151702219712728</v>
       </c>
       <c r="U95">
-        <v>0.2088487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V95">
         <v>0.18</v>
       </c>
       <c r="W95">
-        <v>0.1712559647491529</v>
+        <v>0.1947079647491528</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.500189142971291</v>
+        <v>1.305458596780169</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2853185884257836</v>
+        <v>0.2865919950077831</v>
       </c>
       <c r="C96">
-        <v>-60.0210827940432</v>
+        <v>-84.35509276215566</v>
       </c>
       <c r="D96">
-        <v>995.2369172059567</v>
+        <v>991.3599072378444</v>
       </c>
       <c r="E96">
-        <v>811.558</v>
+        <v>832.0150000000001</v>
       </c>
       <c r="F96">
-        <v>1922.958</v>
+        <v>1943.415</v>
       </c>
       <c r="G96">
         <v>867.7</v>
@@ -9153,28 +9153,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M96">
-        <v>456.6039493635383</v>
+        <v>461.4614381865547</v>
       </c>
       <c r="N96">
-        <v>139.4736016568698</v>
+        <v>134.6161128338534</v>
       </c>
       <c r="O96">
-        <v>25.10524829823656</v>
+        <v>24.23090031009361</v>
       </c>
       <c r="P96">
-        <v>114.3683533586332</v>
+        <v>110.3852125237598</v>
       </c>
       <c r="Q96">
-        <v>202.1683533586333</v>
+        <v>198.1852125237598</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.704885026026334</v>
+        <v>2.03238856992176</v>
       </c>
       <c r="T96">
-        <v>8.151702219712728</v>
+        <v>9.760849022833687</v>
       </c>
       <c r="U96">
         <v>0.2374487374989669</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.305458596780169</v>
+        <v>1.291716927340378</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2865919950077831</v>
+        <v>0.2878654015897825</v>
       </c>
       <c r="C97">
-        <v>-84.35509276215566</v>
+        <v>-108.6590136565719</v>
       </c>
       <c r="D97">
-        <v>991.3599072378444</v>
+        <v>987.5129863434283</v>
       </c>
       <c r="E97">
-        <v>832.0150000000001</v>
+        <v>852.4720000000002</v>
       </c>
       <c r="F97">
-        <v>1943.415</v>
+        <v>1963.872</v>
       </c>
       <c r="G97">
         <v>867.7</v>
@@ -9235,28 +9235,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M97">
-        <v>461.4614381865547</v>
+        <v>466.3189270095711</v>
       </c>
       <c r="N97">
-        <v>134.6161128338534</v>
+        <v>129.758624010837</v>
       </c>
       <c r="O97">
-        <v>24.23090031009361</v>
+        <v>23.35655232195066</v>
       </c>
       <c r="P97">
-        <v>110.3852125237598</v>
+        <v>106.4020716888864</v>
       </c>
       <c r="Q97">
-        <v>198.1852125237598</v>
+        <v>194.2020716888864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.03238856992176</v>
+        <v>2.523643885764897</v>
       </c>
       <c r="T97">
-        <v>9.760849022833687</v>
+        <v>12.17456922751512</v>
       </c>
       <c r="U97">
         <v>0.2374487374989669</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.291716927340378</v>
+        <v>1.278261542680582</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2878654015897825</v>
+        <v>0.2891388081717819</v>
       </c>
       <c r="C98">
-        <v>-108.6590136565717</v>
+        <v>-132.9331944005996</v>
       </c>
       <c r="D98">
-        <v>987.5129863434283</v>
+        <v>983.6958055994004</v>
       </c>
       <c r="E98">
-        <v>852.472</v>
+        <v>872.9289999999999</v>
       </c>
       <c r="F98">
-        <v>1963.872</v>
+        <v>1984.329</v>
       </c>
       <c r="G98">
         <v>867.7</v>
@@ -9317,28 +9317,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M98">
-        <v>466.318927009571</v>
+        <v>471.1764158325874</v>
       </c>
       <c r="N98">
-        <v>129.7586240108371</v>
+        <v>124.9011351878207</v>
       </c>
       <c r="O98">
-        <v>23.35655232195067</v>
+        <v>22.48220433380773</v>
       </c>
       <c r="P98">
-        <v>106.4020716888864</v>
+        <v>102.418930854013</v>
       </c>
       <c r="Q98">
-        <v>194.2020716888865</v>
+        <v>190.2189308540131</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.523643885764892</v>
+        <v>3.342402745503452</v>
       </c>
       <c r="T98">
-        <v>12.17456922751509</v>
+        <v>16.19743623531746</v>
       </c>
       <c r="U98">
         <v>0.2374487374989669</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.278261542680582</v>
+        <v>1.265083588632329</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2891388081717819</v>
+        <v>0.2904122147537813</v>
       </c>
       <c r="C99">
-        <v>-132.9331944005996</v>
+        <v>-157.1779785433409</v>
       </c>
       <c r="D99">
-        <v>983.6958055994004</v>
+        <v>979.908021456659</v>
       </c>
       <c r="E99">
-        <v>872.9289999999999</v>
+        <v>893.386</v>
       </c>
       <c r="F99">
-        <v>1984.329</v>
+        <v>2004.786</v>
       </c>
       <c r="G99">
         <v>867.7</v>
@@ -9399,28 +9399,28 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M99">
-        <v>471.1764158325874</v>
+        <v>476.0339046556038</v>
       </c>
       <c r="N99">
-        <v>124.9011351878207</v>
+        <v>120.0436463648043</v>
       </c>
       <c r="O99">
-        <v>22.48220433380773</v>
+        <v>21.60785634566477</v>
       </c>
       <c r="P99">
-        <v>102.418930854013</v>
+        <v>98.43579001913955</v>
       </c>
       <c r="Q99">
-        <v>190.2189308540131</v>
+        <v>186.2357900191396</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.342402745503452</v>
+        <v>4.979920464980571</v>
       </c>
       <c r="T99">
-        <v>16.19743623531746</v>
+        <v>24.24317025092221</v>
       </c>
       <c r="U99">
         <v>0.2374487374989669</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.265083588632329</v>
+        <v>1.252174572421795</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2904122147537813</v>
+        <v>0.3145783813357807</v>
       </c>
       <c r="C100">
-        <v>-157.1779785433409</v>
+        <v>-244.3648929030851</v>
       </c>
       <c r="D100">
-        <v>979.908021456659</v>
+        <v>913.1781070969149</v>
       </c>
       <c r="E100">
-        <v>893.386</v>
+        <v>913.8429999999998</v>
       </c>
       <c r="F100">
-        <v>2004.786</v>
+        <v>2025.243</v>
       </c>
       <c r="G100">
         <v>867.7</v>
@@ -9481,129 +9481,47 @@
         <v>596.0775510204081</v>
       </c>
       <c r="M100">
-        <v>476.0339046556038</v>
+        <v>538.0032460786201</v>
       </c>
       <c r="N100">
-        <v>120.0436463648043</v>
+        <v>58.074304941788</v>
       </c>
       <c r="O100">
-        <v>21.60785634566477</v>
+        <v>10.45337488952184</v>
       </c>
       <c r="P100">
-        <v>98.43579001913955</v>
+        <v>47.62093005226616</v>
       </c>
       <c r="Q100">
-        <v>186.2357900191396</v>
+        <v>135.4209300522662</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.979920464980571</v>
+        <v>9.892473623411933</v>
       </c>
       <c r="T100">
-        <v>24.24317025092221</v>
+        <v>48.38037229773646</v>
       </c>
       <c r="U100">
-        <v>0.2374487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V100">
         <v>0.18</v>
       </c>
       <c r="W100">
-        <v>0.1947079647491528</v>
+        <v>0.2178319647491528</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.252174572421795</v>
+        <v>1.107944153432304</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3145783813357807</v>
-      </c>
-      <c r="C101">
-        <v>-244.3648929030851</v>
-      </c>
-      <c r="D101">
-        <v>913.1781070969149</v>
-      </c>
-      <c r="E101">
-        <v>913.8429999999998</v>
-      </c>
-      <c r="F101">
-        <v>2025.243</v>
-      </c>
-      <c r="G101">
-        <v>867.7</v>
-      </c>
-      <c r="H101">
-        <v>934.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>683.8775510204082</v>
-      </c>
-      <c r="K101">
-        <v>87.80000000000007</v>
-      </c>
-      <c r="L101">
-        <v>596.0775510204081</v>
-      </c>
-      <c r="M101">
-        <v>538.0032460786201</v>
-      </c>
-      <c r="N101">
-        <v>58.074304941788</v>
-      </c>
-      <c r="O101">
-        <v>10.45337488952184</v>
-      </c>
-      <c r="P101">
-        <v>47.62093005226616</v>
-      </c>
-      <c r="Q101">
-        <v>135.4209300522662</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.892473623411933</v>
-      </c>
-      <c r="T101">
-        <v>48.38037229773646</v>
-      </c>
-      <c r="U101">
-        <v>0.2656487374989668</v>
-      </c>
-      <c r="V101">
-        <v>0.18</v>
-      </c>
-      <c r="W101">
-        <v>0.2178319647491528</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.107944153432304</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
